--- a/pib_nowcast/data/impacts.xlsx
+++ b/pib_nowcast/data/impacts.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H152"/>
+  <dimension ref="A1:H357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3846,7 +3846,7 @@
       <c r="F114" t="n">
         <v>0.0008371442540284178</v>
       </c>
-      <c r="G114" s="2" t="n">
+      <c r="G114" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H114" t="inlineStr">
@@ -3876,7 +3876,7 @@
       <c r="F115" t="n">
         <v>0.0002061560543698748</v>
       </c>
-      <c r="G115" s="2" t="n">
+      <c r="G115" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H115" t="inlineStr">
@@ -3906,7 +3906,7 @@
       <c r="F116" t="n">
         <v>-0.001066126300907035</v>
       </c>
-      <c r="G116" s="2" t="n">
+      <c r="G116" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H116" t="inlineStr">
@@ -3936,7 +3936,7 @@
       <c r="F117" t="n">
         <v>0.00107140471716593</v>
       </c>
-      <c r="G117" s="2" t="n">
+      <c r="G117" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H117" t="inlineStr">
@@ -3966,7 +3966,7 @@
       <c r="F118" t="n">
         <v>-0.00321532860438565</v>
       </c>
-      <c r="G118" s="2" t="n">
+      <c r="G118" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H118" t="inlineStr">
@@ -3996,7 +3996,7 @@
       <c r="F119" t="n">
         <v>0.01197519504425258</v>
       </c>
-      <c r="G119" s="2" t="n">
+      <c r="G119" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H119" t="inlineStr">
@@ -4026,7 +4026,7 @@
       <c r="F120" t="n">
         <v>0.0001977975985540915</v>
       </c>
-      <c r="G120" s="2" t="n">
+      <c r="G120" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H120" t="inlineStr">
@@ -4056,7 +4056,7 @@
       <c r="F121" t="n">
         <v>-0.0001607581528056708</v>
       </c>
-      <c r="G121" s="2" t="n">
+      <c r="G121" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H121" t="inlineStr">
@@ -4086,7 +4086,7 @@
       <c r="F122" t="n">
         <v>0.001138858797108303</v>
       </c>
-      <c r="G122" s="2" t="n">
+      <c r="G122" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H122" t="inlineStr">
@@ -4116,7 +4116,7 @@
       <c r="F123" t="n">
         <v>-0.0002158612231156711</v>
       </c>
-      <c r="G123" s="2" t="n">
+      <c r="G123" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H123" t="inlineStr">
@@ -4146,7 +4146,7 @@
       <c r="F124" t="n">
         <v>0.001622100488611313</v>
       </c>
-      <c r="G124" s="2" t="n">
+      <c r="G124" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H124" t="inlineStr">
@@ -4176,7 +4176,7 @@
       <c r="F125" t="n">
         <v>-0.002632653799246364</v>
       </c>
-      <c r="G125" s="2" t="n">
+      <c r="G125" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H125" t="inlineStr">
@@ -4206,7 +4206,7 @@
       <c r="F126" t="n">
         <v>-0.001183639658627008</v>
       </c>
-      <c r="G126" s="2" t="n">
+      <c r="G126" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H126" t="inlineStr">
@@ -4236,7 +4236,7 @@
       <c r="F127" t="n">
         <v>0.002199275952886499</v>
       </c>
-      <c r="G127" s="2" t="n">
+      <c r="G127" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H127" t="inlineStr">
@@ -4266,7 +4266,7 @@
       <c r="F128" t="n">
         <v>-1.208855833961007e-05</v>
       </c>
-      <c r="G128" s="2" t="n">
+      <c r="G128" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H128" t="inlineStr">
@@ -4296,7 +4296,7 @@
       <c r="F129" t="n">
         <v>0.0006258250785998908</v>
       </c>
-      <c r="G129" s="2" t="n">
+      <c r="G129" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H129" t="inlineStr">
@@ -4326,7 +4326,7 @@
       <c r="F130" t="n">
         <v>0.0003969017376255259</v>
       </c>
-      <c r="G130" s="2" t="n">
+      <c r="G130" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H130" t="inlineStr">
@@ -4356,7 +4356,7 @@
       <c r="F131" t="n">
         <v>-0.002508292170583509</v>
       </c>
-      <c r="G131" s="2" t="n">
+      <c r="G131" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H131" t="inlineStr">
@@ -4386,7 +4386,7 @@
       <c r="F132" t="n">
         <v>0.0004873902267233874</v>
       </c>
-      <c r="G132" s="2" t="n">
+      <c r="G132" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H132" t="inlineStr">
@@ -4416,7 +4416,7 @@
       <c r="F133" t="n">
         <v>0.001366755871610763</v>
       </c>
-      <c r="G133" s="2" t="n">
+      <c r="G133" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H133" t="inlineStr">
@@ -4446,7 +4446,7 @@
       <c r="F134" t="n">
         <v>-0.001003759698264451</v>
       </c>
-      <c r="G134" s="2" t="n">
+      <c r="G134" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H134" t="inlineStr">
@@ -4476,7 +4476,7 @@
       <c r="F135" t="n">
         <v>-0.000115565856127505</v>
       </c>
-      <c r="G135" s="2" t="n">
+      <c r="G135" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H135" t="inlineStr">
@@ -4506,7 +4506,7 @@
       <c r="F136" t="n">
         <v>-0.0003093797836158571</v>
       </c>
-      <c r="G136" s="2" t="n">
+      <c r="G136" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H136" t="inlineStr">
@@ -4536,7 +4536,7 @@
       <c r="F137" t="n">
         <v>-0.0008341965372640714</v>
       </c>
-      <c r="G137" s="2" t="n">
+      <c r="G137" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H137" t="inlineStr">
@@ -4566,7 +4566,7 @@
       <c r="F138" t="n">
         <v>-0.0003055448199028715</v>
       </c>
-      <c r="G138" s="2" t="n">
+      <c r="G138" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H138" t="inlineStr">
@@ -4596,7 +4596,7 @@
       <c r="F139" t="n">
         <v>0.0006775429403367268</v>
       </c>
-      <c r="G139" s="2" t="n">
+      <c r="G139" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H139" t="inlineStr">
@@ -4626,7 +4626,7 @@
       <c r="F140" t="n">
         <v>0.0004560540338104466</v>
       </c>
-      <c r="G140" s="2" t="n">
+      <c r="G140" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H140" t="inlineStr">
@@ -4656,7 +4656,7 @@
       <c r="F141" t="n">
         <v>0.0007245922440728933</v>
       </c>
-      <c r="G141" s="2" t="n">
+      <c r="G141" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H141" t="inlineStr">
@@ -4686,7 +4686,7 @@
       <c r="F142" t="n">
         <v>0.0005941303599985865</v>
       </c>
-      <c r="G142" s="2" t="n">
+      <c r="G142" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H142" t="inlineStr">
@@ -4716,7 +4716,7 @@
       <c r="F143" t="n">
         <v>9.24483751813404e-07</v>
       </c>
-      <c r="G143" s="2" t="n">
+      <c r="G143" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H143" t="inlineStr">
@@ -4746,7 +4746,7 @@
       <c r="F144" t="n">
         <v>2.940192984861567e-05</v>
       </c>
-      <c r="G144" s="2" t="n">
+      <c r="G144" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H144" t="inlineStr">
@@ -4776,7 +4776,7 @@
       <c r="F145" t="n">
         <v>-0.0001643525288234067</v>
       </c>
-      <c r="G145" s="2" t="n">
+      <c r="G145" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H145" t="inlineStr">
@@ -4806,7 +4806,7 @@
       <c r="F146" t="n">
         <v>0.0004992482190337478</v>
       </c>
-      <c r="G146" s="2" t="n">
+      <c r="G146" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H146" t="inlineStr">
@@ -4836,7 +4836,7 @@
       <c r="F147" t="n">
         <v>-0.0006576530211859908</v>
       </c>
-      <c r="G147" s="2" t="n">
+      <c r="G147" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H147" t="inlineStr">
@@ -4866,7 +4866,7 @@
       <c r="F148" t="n">
         <v>-0.001954399356087626</v>
       </c>
-      <c r="G148" s="2" t="n">
+      <c r="G148" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H148" t="inlineStr">
@@ -4896,7 +4896,7 @@
       <c r="F149" t="n">
         <v>-0.0002903954392971863</v>
       </c>
-      <c r="G149" s="2" t="n">
+      <c r="G149" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H149" t="inlineStr">
@@ -4926,7 +4926,7 @@
       <c r="F150" t="n">
         <v>-0.004602345319736491</v>
       </c>
-      <c r="G150" s="2" t="n">
+      <c r="G150" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H150" t="inlineStr">
@@ -4956,7 +4956,7 @@
       <c r="F151" t="n">
         <v>0.0004248577728059621</v>
       </c>
-      <c r="G151" s="2" t="n">
+      <c r="G151" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H151" t="inlineStr">
@@ -4986,10 +4986,6160 @@
       <c r="F152" t="n">
         <v>-0.0007322904613380956</v>
       </c>
-      <c r="G152" s="2" t="n">
+      <c r="G152" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H152" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>ipca_EX3</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>86.50196959226109</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-1.461242655125584</v>
+      </c>
+      <c r="D153" t="n">
+        <v>87.96321224738668</v>
+      </c>
+      <c r="E153" t="n">
+        <v>5.424468691783046e-11</v>
+      </c>
+      <c r="F153" t="n">
+        <v>4.77153690864616e-09</v>
+      </c>
+      <c r="G153" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>-0.9854215881396113</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-0.2951918640703351</v>
+      </c>
+      <c r="D154" t="n">
+        <v>-0.6902297240692762</v>
+      </c>
+      <c r="E154" t="n">
+        <v>4.173664633054546e-10</v>
+      </c>
+      <c r="F154" t="n">
+        <v>-2.880787388030936e-10</v>
+      </c>
+      <c r="G154" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>ipca_EX3</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>88.86216632619002</v>
+      </c>
+      <c r="C155" t="n">
+        <v>9.385734344219181</v>
+      </c>
+      <c r="D155" t="n">
+        <v>79.47643198197085</v>
+      </c>
+      <c r="E155" t="n">
+        <v>6.542422965932244e-10</v>
+      </c>
+      <c r="F155" t="n">
+        <v>5.199684338491979e-08</v>
+      </c>
+      <c r="G155" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>ipca_EX3</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>67.76063461863504</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-7.965788223138032</v>
+      </c>
+      <c r="D156" t="n">
+        <v>75.72642284177307</v>
+      </c>
+      <c r="E156" t="n">
+        <v>2.246682587540124e-09</v>
+      </c>
+      <c r="F156" t="n">
+        <v>1.701332356153123e-07</v>
+      </c>
+      <c r="G156" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>ipca_EX3</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>81.13726899413625</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-1.76974508013622</v>
+      </c>
+      <c r="D157" t="n">
+        <v>82.90701407427247</v>
+      </c>
+      <c r="E157" t="n">
+        <v>1.441065094632586e-08</v>
+      </c>
+      <c r="F157" t="n">
+        <v>1.194744040826466e-06</v>
+      </c>
+      <c r="G157" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>ipca_administrados</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>-324.5138640160209</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-18.6344397851489</v>
+      </c>
+      <c r="D158" t="n">
+        <v>-305.879424230872</v>
+      </c>
+      <c r="E158" t="n">
+        <v>4.770412931783676e-09</v>
+      </c>
+      <c r="F158" t="n">
+        <v>-1.459171160917497e-06</v>
+      </c>
+      <c r="G158" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>cambio_media_mensal</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>-2.217400142430803</v>
+      </c>
+      <c r="C159" t="n">
+        <v>0.2649904283297909</v>
+      </c>
+      <c r="D159" t="n">
+        <v>-2.482390570760594</v>
+      </c>
+      <c r="E159" t="n">
+        <v>-0.01469832266440495</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.03648697758811557</v>
+      </c>
+      <c r="G159" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>fenabrave_automoveis</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>-6.532173907525873</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-1.05694922558511</v>
+      </c>
+      <c r="D160" t="n">
+        <v>-5.475224681940764</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0.00544673541190303</v>
+      </c>
+      <c r="F160" t="n">
+        <v>-0.02982210016325227</v>
+      </c>
+      <c r="G160" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>fenabrave_caminhoes</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>-0.05988950461249587</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-0.1224194581034538</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0.06252995349095788</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0.1386011676850188</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0.008666724569136683</v>
+      </c>
+      <c r="G161" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>fenabrave_comerciais_leves</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>-0.3424365805175689</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-1.475014418303397</v>
+      </c>
+      <c r="D162" t="n">
+        <v>1.132577837785828</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0.009608963858205038</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0.01088289950988803</v>
+      </c>
+      <c r="G162" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>fenabrave_onibus</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>-0.1434468750750533</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-0.173545661296142</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0.03009878622108877</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0.08031080748079088</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0.002417257825607342</v>
+      </c>
+      <c r="G163" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>fgv_nuci</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>-0.09999999999999432</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.02535354886073003</v>
+      </c>
+      <c r="D164" t="n">
+        <v>-0.07464645113926428</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0.110126218638555</v>
+      </c>
+      <c r="F164" t="n">
+        <v>-0.008220531398754833</v>
+      </c>
+      <c r="G164" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>icbr_agro</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>0.6843143401802365</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0.844929938819506</v>
+      </c>
+      <c r="D165" t="n">
+        <v>-0.1606155986392694</v>
+      </c>
+      <c r="E165" t="n">
+        <v>-0.0007838985811499539</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0.0001259063398838738</v>
+      </c>
+      <c r="G165" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>icbr_energia</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>-0.2598010997918344</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.9789760121083012</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0.7191749123164669</v>
+      </c>
+      <c r="E166" t="n">
+        <v>-0.002215335297964306</v>
+      </c>
+      <c r="F166" t="n">
+        <v>-0.001593213568665054</v>
+      </c>
+      <c r="G166" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>icbr_metal</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>2.221426097799162</v>
+      </c>
+      <c r="C167" t="n">
+        <v>0.9509120840527912</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1.27051401374637</v>
+      </c>
+      <c r="E167" t="n">
+        <v>-0.003350749835055537</v>
+      </c>
+      <c r="F167" t="n">
+        <v>-0.004257174621996399</v>
+      </c>
+      <c r="G167" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>0.02818789434369517</v>
+      </c>
+      <c r="C168" t="n">
+        <v>0.2544515122639072</v>
+      </c>
+      <c r="D168" t="n">
+        <v>-0.226263617920212</v>
+      </c>
+      <c r="E168" t="n">
+        <v>-0.01011811280724122</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0.00228936081029123</v>
+      </c>
+      <c r="G168" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>-0.6861518942244005</v>
+      </c>
+      <c r="C169" t="n">
+        <v>0.03981136973404364</v>
+      </c>
+      <c r="D169" t="n">
+        <v>-0.7259632639584441</v>
+      </c>
+      <c r="E169" t="n">
+        <v>-0.001434095520503264</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0.001041100664892734</v>
+      </c>
+      <c r="G169" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>-0.6766796575117204</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-0.03931865979080419</v>
+      </c>
+      <c r="D170" t="n">
+        <v>-0.6373609977209163</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0.002586296854398967</v>
+      </c>
+      <c r="F170" t="n">
+        <v>-0.001648404743522193</v>
+      </c>
+      <c r="G170" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>-27.23676035837958</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-1.988626106122955</v>
+      </c>
+      <c r="D171" t="n">
+        <v>-25.24813425225662</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0.0006143584641178415</v>
+      </c>
+      <c r="F171" t="n">
+        <v>-0.01551140498105744</v>
+      </c>
+      <c r="G171" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>-1.219490382003215</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-0.0827085550407073</v>
+      </c>
+      <c r="D172" t="n">
+        <v>-1.136781826962508</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0.0007690035814700886</v>
+      </c>
+      <c r="F172" t="n">
+        <v>-0.0008741892962842789</v>
+      </c>
+      <c r="G172" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>0.2427188518995873</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0.4250418726909389</v>
+      </c>
+      <c r="D173" t="n">
+        <v>-0.1823230207913516</v>
+      </c>
+      <c r="E173" t="n">
+        <v>-0.0552275476076304</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.01006925331072136</v>
+      </c>
+      <c r="G173" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>-0.1379831538514812</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-0.03280124474866725</v>
+      </c>
+      <c r="D174" t="n">
+        <v>-0.105181909102814</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0.009103328233329341</v>
+      </c>
+      <c r="F174" t="n">
+        <v>-0.0009575054427711268</v>
+      </c>
+      <c r="G174" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>ipca_DP</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>-0.03019788783614619</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.03253685279229597</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0.002338964956149785</v>
+      </c>
+      <c r="E175" t="n">
+        <v>-0.04162130147598633</v>
+      </c>
+      <c r="F175" t="n">
+        <v>-9.735076558167735e-05</v>
+      </c>
+      <c r="G175" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>ipca_EX0</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>-0.01646268306066051</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-0.01137703088948531</v>
+      </c>
+      <c r="D176" t="n">
+        <v>-0.005085652171175199</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0.05490798202839319</v>
+      </c>
+      <c r="F176" t="n">
+        <v>-0.0002792428980175466</v>
+      </c>
+      <c r="G176" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>ipca_MS</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>7.6303360184242</v>
+      </c>
+      <c r="C177" t="n">
+        <v>1.725398171079241</v>
+      </c>
+      <c r="D177" t="n">
+        <v>5.904937847344959</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0.000118277800191077</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0.0006984230588489953</v>
+      </c>
+      <c r="G177" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>ipca_P55</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>0.05190508249279413</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0.002600343099332152</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0.04930473939346198</v>
+      </c>
+      <c r="E178" t="n">
+        <v>-0.1866881630520772</v>
+      </c>
+      <c r="F178" t="n">
+        <v>-0.009204611227126801</v>
+      </c>
+      <c r="G178" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>ipca_administrados</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>-75.45211039507261</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-16.35697500527272</v>
+      </c>
+      <c r="D179" t="n">
+        <v>-59.09513538979989</v>
+      </c>
+      <c r="E179" t="n">
+        <v>6.360912407022278e-05</v>
+      </c>
+      <c r="F179" t="n">
+        <v>-0.003758989798956394</v>
+      </c>
+      <c r="G179" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>ipca_alim_domicilio</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>0.186800356460164</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0.3769197051060045</v>
+      </c>
+      <c r="D180" t="n">
+        <v>-0.1901193486458405</v>
+      </c>
+      <c r="E180" t="n">
+        <v>-0.007516360770522533</v>
+      </c>
+      <c r="F180" t="n">
+        <v>0.001429005613878892</v>
+      </c>
+      <c r="G180" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>ipca_alimentacao</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>0.2638661571835586</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0.3678721369609049</v>
+      </c>
+      <c r="D181" t="n">
+        <v>-0.1040059797773463</v>
+      </c>
+      <c r="E181" t="n">
+        <v>0.00205312172676513</v>
+      </c>
+      <c r="F181" t="n">
+        <v>-0.0002135369367943644</v>
+      </c>
+      <c r="G181" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>ipca_difusao</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>0.6485572467709773</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0.09931906409811814</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0.5492381826728591</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0.002690818104292959</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0.001477900045505092</v>
+      </c>
+      <c r="G182" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>ipca_industriais</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>0.06835025293548913</v>
+      </c>
+      <c r="C183" t="n">
+        <v>0.2919204481535913</v>
+      </c>
+      <c r="D183" t="n">
+        <v>-0.2235701952181022</v>
+      </c>
+      <c r="E183" t="n">
+        <v>-0.005091390471263737</v>
+      </c>
+      <c r="F183" t="n">
+        <v>0.001138283161592019</v>
+      </c>
+      <c r="G183" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>ipca_industriais_subjacentes</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>0.2687025250315013</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0.3863816943045892</v>
+      </c>
+      <c r="D184" t="n">
+        <v>-0.117679169273088</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0.03455556400319298</v>
+      </c>
+      <c r="F184" t="n">
+        <v>-0.004066470065658772</v>
+      </c>
+      <c r="G184" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>ipca_livres</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>0.3010813186618921</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0.458323709839274</v>
+      </c>
+      <c r="D185" t="n">
+        <v>-0.1572423911773819</v>
+      </c>
+      <c r="E185" t="n">
+        <v>-0.02400267116900232</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0.003774237409258329</v>
+      </c>
+      <c r="G185" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>ipca_servicos_subjacentes</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>0.03924681779994277</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-0.005520829511743684</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0.04476764731168645</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0.09299766490335641</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0.004163286663203861</v>
+      </c>
+      <c r="G186" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>-0.4013425984299213</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-0.006193341083298016</v>
+      </c>
+      <c r="D187" t="n">
+        <v>-0.3951492573466233</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0.01807001847014128</v>
+      </c>
+      <c r="F187" t="n">
+        <v>-0.007140354378716095</v>
+      </c>
+      <c r="G187" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>-0.4328210024792778</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-0.9816458762808369</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0.5488248738015591</v>
+      </c>
+      <c r="E188" t="n">
+        <v>-0.01140594914100132</v>
+      </c>
+      <c r="F188" t="n">
+        <v>-0.006259868597897053</v>
+      </c>
+      <c r="G188" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>-0.1909594904294654</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-0.9852975610533709</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0.7943380706239056</v>
+      </c>
+      <c r="E189" t="n">
+        <v>0.008441298364491142</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0.006705244656410624</v>
+      </c>
+      <c r="G189" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>1.505764016391207</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0.4629857496657964</v>
+      </c>
+      <c r="D190" t="n">
+        <v>1.042778266725411</v>
+      </c>
+      <c r="E190" t="n">
+        <v>2.928338100186747e-09</v>
+      </c>
+      <c r="F190" t="n">
+        <v>3.053607328498719e-09</v>
+      </c>
+      <c r="G190" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>cambio_media_mensal</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>-2.217400142430803</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0.1474460267834039</v>
+      </c>
+      <c r="D191" t="n">
+        <v>-2.364846169214207</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0.00373861700118539</v>
+      </c>
+      <c r="F191" t="n">
+        <v>-0.008841254093412377</v>
+      </c>
+      <c r="G191" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>fenabrave_automoveis</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>-5.275650780846597</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-0.8409314139943401</v>
+      </c>
+      <c r="D192" t="n">
+        <v>-4.434719366852256</v>
+      </c>
+      <c r="E192" t="n">
+        <v>0.001513094184203147</v>
+      </c>
+      <c r="F192" t="n">
+        <v>-0.006710148082557212</v>
+      </c>
+      <c r="G192" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>fenabrave_caminhoes</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>-0.05988950461249587</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-0.120164002464611</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0.06027449785211515</v>
+      </c>
+      <c r="E193" t="n">
+        <v>0.004701588517173273</v>
+      </c>
+      <c r="F193" t="n">
+        <v>0.0002833858869798897</v>
+      </c>
+      <c r="G193" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>fenabrave_comerciais_leves</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>-0.3424365805175689</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-0.991509246934744</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0.649072666417175</v>
+      </c>
+      <c r="E194" t="n">
+        <v>0.003293710358422394</v>
+      </c>
+      <c r="F194" t="n">
+        <v>0.002137857364747092</v>
+      </c>
+      <c r="G194" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>fenabrave_onibus</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>-4.153947786527201</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-4.765528904554451</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0.611581118027249</v>
+      </c>
+      <c r="E195" t="n">
+        <v>0.0009535870236536973</v>
+      </c>
+      <c r="F195" t="n">
+        <v>0.0005831958180624049</v>
+      </c>
+      <c r="G195" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>fgv_nuci</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>-0.09999999999999432</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0.0463735844155764</v>
+      </c>
+      <c r="D196" t="n">
+        <v>-0.1463735844155707</v>
+      </c>
+      <c r="E196" t="n">
+        <v>0.01066755787543907</v>
+      </c>
+      <c r="F196" t="n">
+        <v>-0.001561448683188567</v>
+      </c>
+      <c r="G196" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>icbr_agro</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>0.6843143401802365</v>
+      </c>
+      <c r="C197" t="n">
+        <v>0.8787083476764382</v>
+      </c>
+      <c r="D197" t="n">
+        <v>-0.1943940074962018</v>
+      </c>
+      <c r="E197" t="n">
+        <v>5.102623180849643e-05</v>
+      </c>
+      <c r="F197" t="n">
+        <v>-9.919193688683782e-06</v>
+      </c>
+      <c r="G197" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>icbr_energia</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>-0.2598010997918344</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.4694780125942229</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0.2096769128023885</v>
+      </c>
+      <c r="E198" t="n">
+        <v>2.604763220969112e-05</v>
+      </c>
+      <c r="F198" t="n">
+        <v>5.461587107540091e-06</v>
+      </c>
+      <c r="G198" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>icbr_metal</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>2.221426097799162</v>
+      </c>
+      <c r="C199" t="n">
+        <v>1.137972650984186</v>
+      </c>
+      <c r="D199" t="n">
+        <v>1.083453446814975</v>
+      </c>
+      <c r="E199" t="n">
+        <v>-0.0001785535788347922</v>
+      </c>
+      <c r="F199" t="n">
+        <v>-0.000193454490429705</v>
+      </c>
+      <c r="G199" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>0.02834541292932119</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0.5114264642883792</v>
+      </c>
+      <c r="D200" t="n">
+        <v>-0.483081051359058</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0.002160717800620379</v>
+      </c>
+      <c r="F200" t="n">
+        <v>-0.001043801826813924</v>
+      </c>
+      <c r="G200" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>-0.6322592568392276</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0.6177612381770341</v>
+      </c>
+      <c r="D201" t="n">
+        <v>-1.250020495016262</v>
+      </c>
+      <c r="E201" t="n">
+        <v>-0.0008813947842934812</v>
+      </c>
+      <c r="F201" t="n">
+        <v>0.001101761544567289</v>
+      </c>
+      <c r="G201" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>-0.3700623027681143</v>
+      </c>
+      <c r="C202" t="n">
+        <v>0.3739439231051954</v>
+      </c>
+      <c r="D202" t="n">
+        <v>-0.7440062258733097</v>
+      </c>
+      <c r="E202" t="n">
+        <v>-0.07221185776377066</v>
+      </c>
+      <c r="F202" t="n">
+        <v>0.05372607175812327</v>
+      </c>
+      <c r="G202" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>0.4489387037604357</v>
+      </c>
+      <c r="C203" t="n">
+        <v>0.4794857273714742</v>
+      </c>
+      <c r="D203" t="n">
+        <v>-0.03054702361103855</v>
+      </c>
+      <c r="E203" t="n">
+        <v>-0.01902434989808269</v>
+      </c>
+      <c r="F203" t="n">
+        <v>0.0005811372655213908</v>
+      </c>
+      <c r="G203" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>-0.6966185442159021</v>
+      </c>
+      <c r="C204" t="n">
+        <v>0.4384060818375886</v>
+      </c>
+      <c r="D204" t="n">
+        <v>-1.135024626053491</v>
+      </c>
+      <c r="E204" t="n">
+        <v>-0.004621208662795637</v>
+      </c>
+      <c r="F204" t="n">
+        <v>0.005245185634404769</v>
+      </c>
+      <c r="G204" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>0.2427188518995873</v>
+      </c>
+      <c r="C205" t="n">
+        <v>0.3668410098973062</v>
+      </c>
+      <c r="D205" t="n">
+        <v>-0.1241221579977189</v>
+      </c>
+      <c r="E205" t="n">
+        <v>0.03778731291601223</v>
+      </c>
+      <c r="F205" t="n">
+        <v>-0.004690242824070513</v>
+      </c>
+      <c r="G205" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>0.3109432966846084</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0.4003159163995771</v>
+      </c>
+      <c r="D206" t="n">
+        <v>-0.08937261971496875</v>
+      </c>
+      <c r="E206" t="n">
+        <v>0.03363475484958806</v>
+      </c>
+      <c r="F206" t="n">
+        <v>-0.003006026154378435</v>
+      </c>
+      <c r="G206" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>ipca_DP</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>0.30432517773155</v>
+      </c>
+      <c r="C207" t="n">
+        <v>0.3768969140576424</v>
+      </c>
+      <c r="D207" t="n">
+        <v>-0.07257173632609244</v>
+      </c>
+      <c r="E207" t="n">
+        <v>0.1500611109452526</v>
+      </c>
+      <c r="F207" t="n">
+        <v>-0.01089019537631937</v>
+      </c>
+      <c r="G207" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>ipca_EX0</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>0.3985075622549502</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0.3678169461941097</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0.03069061606084054</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0.1096965857939129</v>
+      </c>
+      <c r="F208" t="n">
+        <v>0.003366655797786034</v>
+      </c>
+      <c r="G208" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>ipca_EX3</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>0.358515394556541</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0.3767259498496069</v>
+      </c>
+      <c r="D209" t="n">
+        <v>-0.01821055529306596</v>
+      </c>
+      <c r="E209" t="n">
+        <v>-0.09260532663327273</v>
+      </c>
+      <c r="F209" t="n">
+        <v>0.001686394421087646</v>
+      </c>
+      <c r="G209" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>ipca_MS</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>0.3611275205637015</v>
+      </c>
+      <c r="C210" t="n">
+        <v>0.3527544006377226</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0.008373119925978872</v>
+      </c>
+      <c r="E210" t="n">
+        <v>0.06795110014082635</v>
+      </c>
+      <c r="F210" t="n">
+        <v>0.0005689627105813389</v>
+      </c>
+      <c r="G210" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>ipca_P55</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>0.4254132256423441</v>
+      </c>
+      <c r="C211" t="n">
+        <v>0.3808495199476165</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0.04456370569472759</v>
+      </c>
+      <c r="E211" t="n">
+        <v>0.1181771505366578</v>
+      </c>
+      <c r="F211" t="n">
+        <v>0.005266411756357135</v>
+      </c>
+      <c r="G211" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>ipca_administrados</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>0.07556839549407418</v>
+      </c>
+      <c r="C212" t="n">
+        <v>0.4071664958659742</v>
+      </c>
+      <c r="D212" t="n">
+        <v>-0.3315981003719</v>
+      </c>
+      <c r="E212" t="n">
+        <v>0.01876294856219525</v>
+      </c>
+      <c r="F212" t="n">
+        <v>-0.006221758100599618</v>
+      </c>
+      <c r="G212" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>ipca_alim_domicilio</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>0.1987814756189867</v>
+      </c>
+      <c r="C213" t="n">
+        <v>0.3631075106780369</v>
+      </c>
+      <c r="D213" t="n">
+        <v>-0.1643260350590501</v>
+      </c>
+      <c r="E213" t="n">
+        <v>0.002006443458075741</v>
+      </c>
+      <c r="F213" t="n">
+        <v>-0.000329710898035756</v>
+      </c>
+      <c r="G213" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>ipca_alimentacao</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>0.2927774211888935</v>
+      </c>
+      <c r="C214" t="n">
+        <v>0.3818266624054434</v>
+      </c>
+      <c r="D214" t="n">
+        <v>-0.08904924121654995</v>
+      </c>
+      <c r="E214" t="n">
+        <v>-0.0005036612387877519</v>
+      </c>
+      <c r="F214" t="n">
+        <v>4.485065114423688e-05</v>
+      </c>
+      <c r="G214" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>ipca_difusao</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>0.6485572467709773</v>
+      </c>
+      <c r="C215" t="n">
+        <v>0.565009455757104</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0.08354779101387316</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0.0001691889979217273</v>
+      </c>
+      <c r="F215" t="n">
+        <v>1.41353670402111e-05</v>
+      </c>
+      <c r="G215" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>ipca_industriais</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>0.0693498936122684</v>
+      </c>
+      <c r="C216" t="n">
+        <v>0.2605785852695728</v>
+      </c>
+      <c r="D216" t="n">
+        <v>-0.1912286916573044</v>
+      </c>
+      <c r="E216" t="n">
+        <v>-0.07456169235579983</v>
+      </c>
+      <c r="F216" t="n">
+        <v>0.01425833487695403</v>
+      </c>
+      <c r="G216" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>ipca_industriais_subjacentes</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>0.2687025250315013</v>
+      </c>
+      <c r="C217" t="n">
+        <v>0.3159521248632202</v>
+      </c>
+      <c r="D217" t="n">
+        <v>-0.04724959983171888</v>
+      </c>
+      <c r="E217" t="n">
+        <v>-0.01258237971235035</v>
+      </c>
+      <c r="F217" t="n">
+        <v>0.0005945124063392922</v>
+      </c>
+      <c r="G217" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>ipca_livres</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>0.3010813186618921</v>
+      </c>
+      <c r="C218" t="n">
+        <v>0.3786424265267753</v>
+      </c>
+      <c r="D218" t="n">
+        <v>-0.0775611078648832</v>
+      </c>
+      <c r="E218" t="n">
+        <v>0.04475670511088087</v>
+      </c>
+      <c r="F218" t="n">
+        <v>-0.003471379632781801</v>
+      </c>
+      <c r="G218" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>ipca_servicos_subjacentes</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>0.3602466052582748</v>
+      </c>
+      <c r="C219" t="n">
+        <v>0.4180215019004156</v>
+      </c>
+      <c r="D219" t="n">
+        <v>-0.05777489664214086</v>
+      </c>
+      <c r="E219" t="n">
+        <v>-0.02363280903334841</v>
+      </c>
+      <c r="F219" t="n">
+        <v>0.001365383099265157</v>
+      </c>
+      <c r="G219" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>0.0009189819755979767</v>
+      </c>
+      <c r="C220" t="n">
+        <v>0.3738358795011579</v>
+      </c>
+      <c r="D220" t="n">
+        <v>-0.37291689752556</v>
+      </c>
+      <c r="E220" t="n">
+        <v>0.0268369408743054</v>
+      </c>
+      <c r="F220" t="n">
+        <v>-0.01000794872992286</v>
+      </c>
+      <c r="G220" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>-0.06135948185390028</v>
+      </c>
+      <c r="C221" t="n">
+        <v>-0.08830914682513034</v>
+      </c>
+      <c r="D221" t="n">
+        <v>0.02694966497123007</v>
+      </c>
+      <c r="E221" t="n">
+        <v>0.02252682206175659</v>
+      </c>
+      <c r="F221" t="n">
+        <v>0.0006070903074308543</v>
+      </c>
+      <c r="G221" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>-0.02698732312331309</v>
+      </c>
+      <c r="C222" t="n">
+        <v>-0.08959837154262479</v>
+      </c>
+      <c r="D222" t="n">
+        <v>0.0626110484193117</v>
+      </c>
+      <c r="E222" t="n">
+        <v>0.03866924433163318</v>
+      </c>
+      <c r="F222" t="n">
+        <v>0.002421121929186079</v>
+      </c>
+      <c r="G222" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>1.505764016391207</v>
+      </c>
+      <c r="C223" t="n">
+        <v>0.451966774348647</v>
+      </c>
+      <c r="D223" t="n">
+        <v>1.05379724204256</v>
+      </c>
+      <c r="E223" t="n">
+        <v>-1.61320171491428e-06</v>
+      </c>
+      <c r="F223" t="n">
+        <v>-1.699987518034997e-06</v>
+      </c>
+      <c r="G223" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>cambio_media_mensal</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>-2.217400142430803</v>
+      </c>
+      <c r="C224" t="n">
+        <v>0.1351735573473305</v>
+      </c>
+      <c r="D224" t="n">
+        <v>-2.352573699778134</v>
+      </c>
+      <c r="E224" t="n">
+        <v>0.0001286037497732201</v>
+      </c>
+      <c r="F224" t="n">
+        <v>-0.0003025497994093258</v>
+      </c>
+      <c r="G224" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>fenabrave_automoveis</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>-5.275650780846597</v>
+      </c>
+      <c r="C225" t="n">
+        <v>-0.8027473681491363</v>
+      </c>
+      <c r="D225" t="n">
+        <v>-4.472903412697461</v>
+      </c>
+      <c r="E225" t="n">
+        <v>7.680664994932237e-05</v>
+      </c>
+      <c r="F225" t="n">
+        <v>-0.0003435487266761833</v>
+      </c>
+      <c r="G225" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>fenabrave_caminhoes</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>-0.05988950461249587</v>
+      </c>
+      <c r="C226" t="n">
+        <v>-0.1178407468513606</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0.05795124223886475</v>
+      </c>
+      <c r="E226" t="n">
+        <v>0.001599432677108996</v>
+      </c>
+      <c r="F226" t="n">
+        <v>9.268911051589936e-05</v>
+      </c>
+      <c r="G226" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>fenabrave_comerciais_leves</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>-0.3424365805175689</v>
+      </c>
+      <c r="C227" t="n">
+        <v>-0.8897783134763213</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0.5473417329587525</v>
+      </c>
+      <c r="E227" t="n">
+        <v>0.0001010594127294827</v>
+      </c>
+      <c r="F227" t="n">
+        <v>5.531403409514889e-05</v>
+      </c>
+      <c r="G227" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>fenabrave_onibus</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>-4.153947786527201</v>
+      </c>
+      <c r="C228" t="n">
+        <v>-4.633119944402748</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0.4791721578755457</v>
+      </c>
+      <c r="E228" t="n">
+        <v>2.88614514812963e-05</v>
+      </c>
+      <c r="F228" t="n">
+        <v>1.382960398571311e-05</v>
+      </c>
+      <c r="G228" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>fgv_nuci</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>-0.09999999999999432</v>
+      </c>
+      <c r="C229" t="n">
+        <v>0.0657658442132705</v>
+      </c>
+      <c r="D229" t="n">
+        <v>-0.1657658442132648</v>
+      </c>
+      <c r="E229" t="n">
+        <v>-0.0001651383463875253</v>
+      </c>
+      <c r="F229" t="n">
+        <v>2.737429740091068e-05</v>
+      </c>
+      <c r="G229" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>icbr_agro</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>0.6843143401802365</v>
+      </c>
+      <c r="C230" t="n">
+        <v>0.8894347314679907</v>
+      </c>
+      <c r="D230" t="n">
+        <v>-0.2051203912877542</v>
+      </c>
+      <c r="E230" t="n">
+        <v>-3.295064230681846e-06</v>
+      </c>
+      <c r="F230" t="n">
+        <v>6.75884864315743e-07</v>
+      </c>
+      <c r="G230" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>icbr_energia</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>-0.2598010997918344</v>
+      </c>
+      <c r="C231" t="n">
+        <v>-0.4464633116756117</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0.1866622118837773</v>
+      </c>
+      <c r="E231" t="n">
+        <v>-8.974717460761461e-07</v>
+      </c>
+      <c r="F231" t="n">
+        <v>-1.675240612257691e-07</v>
+      </c>
+      <c r="G231" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>icbr_metal</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>2.221426097799162</v>
+      </c>
+      <c r="C232" t="n">
+        <v>1.214116281400182</v>
+      </c>
+      <c r="D232" t="n">
+        <v>1.00730981639898</v>
+      </c>
+      <c r="E232" t="n">
+        <v>-1.869081292217189e-05</v>
+      </c>
+      <c r="F232" t="n">
+        <v>-1.882743933298064e-05</v>
+      </c>
+      <c r="G232" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>0.02834541292932119</v>
+      </c>
+      <c r="C233" t="n">
+        <v>0.5127510287182295</v>
+      </c>
+      <c r="D233" t="n">
+        <v>-0.4844056157889083</v>
+      </c>
+      <c r="E233" t="n">
+        <v>9.515837866934191e-05</v>
+      </c>
+      <c r="F233" t="n">
+        <v>-4.609525301679669e-05</v>
+      </c>
+      <c r="G233" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>-0.6322592568392276</v>
+      </c>
+      <c r="C234" t="n">
+        <v>0.6218943056246338</v>
+      </c>
+      <c r="D234" t="n">
+        <v>-1.254153562463861</v>
+      </c>
+      <c r="E234" t="n">
+        <v>-6.056763934720421e-05</v>
+      </c>
+      <c r="F234" t="n">
+        <v>7.59611206573225e-05</v>
+      </c>
+      <c r="G234" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>-0.3700623027681143</v>
+      </c>
+      <c r="C235" t="n">
+        <v>0.377336208244744</v>
+      </c>
+      <c r="D235" t="n">
+        <v>-0.7473985110128584</v>
+      </c>
+      <c r="E235" t="n">
+        <v>-0.001905510415739462</v>
+      </c>
+      <c r="F235" t="n">
+        <v>0.001424175647443166</v>
+      </c>
+      <c r="G235" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>0.4489387037604357</v>
+      </c>
+      <c r="C236" t="n">
+        <v>0.4782476134014958</v>
+      </c>
+      <c r="D236" t="n">
+        <v>-0.02930890964106015</v>
+      </c>
+      <c r="E236" t="n">
+        <v>-0.0005644012672528783</v>
+      </c>
+      <c r="F236" t="n">
+        <v>1.654198574321445e-05</v>
+      </c>
+      <c r="G236" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>-0.6966185442159021</v>
+      </c>
+      <c r="C237" t="n">
+        <v>0.4469537571550908</v>
+      </c>
+      <c r="D237" t="n">
+        <v>-1.143572301370993</v>
+      </c>
+      <c r="E237" t="n">
+        <v>-0.0002499905697868852</v>
+      </c>
+      <c r="F237" t="n">
+        <v>0.0002858822912122341</v>
+      </c>
+      <c r="G237" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>0.2427188518995873</v>
+      </c>
+      <c r="C238" t="n">
+        <v>0.3574954528372004</v>
+      </c>
+      <c r="D238" t="n">
+        <v>-0.1147766009376131</v>
+      </c>
+      <c r="E238" t="n">
+        <v>0.001391728644343827</v>
+      </c>
+      <c r="F238" t="n">
+        <v>-0.0001597378832252967</v>
+      </c>
+      <c r="G238" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>0.3109432966846084</v>
+      </c>
+      <c r="C239" t="n">
+        <v>0.3913812563406587</v>
+      </c>
+      <c r="D239" t="n">
+        <v>-0.08043795965605038</v>
+      </c>
+      <c r="E239" t="n">
+        <v>0.001666049251195518</v>
+      </c>
+      <c r="F239" t="n">
+        <v>-0.0001340136024526581</v>
+      </c>
+      <c r="G239" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>ipca_DP</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>0.30432517773155</v>
+      </c>
+      <c r="C240" t="n">
+        <v>0.3662675532290438</v>
+      </c>
+      <c r="D240" t="n">
+        <v>-0.0619423754974938</v>
+      </c>
+      <c r="E240" t="n">
+        <v>0.00708727695583731</v>
+      </c>
+      <c r="F240" t="n">
+        <v>-0.0004390027704532094</v>
+      </c>
+      <c r="G240" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>ipca_EX0</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>0.3985075622549502</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0.35286431596645</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0.04564324628850024</v>
+      </c>
+      <c r="E241" t="n">
+        <v>0.007567410059004227</v>
+      </c>
+      <c r="F241" t="n">
+        <v>0.0003454011610892041</v>
+      </c>
+      <c r="G241" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>ipca_EX3</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>0.358515394556541</v>
+      </c>
+      <c r="C242" t="n">
+        <v>0.3676916760843392</v>
+      </c>
+      <c r="D242" t="n">
+        <v>-0.009176281527798138</v>
+      </c>
+      <c r="E242" t="n">
+        <v>-0.002417558636436602</v>
+      </c>
+      <c r="F242" t="n">
+        <v>2.218419865790205e-05</v>
+      </c>
+      <c r="G242" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>ipca_MS</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>0.3611275205637015</v>
+      </c>
+      <c r="C243" t="n">
+        <v>0.3444773858757182</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0.01665013468798325</v>
+      </c>
+      <c r="E243" t="n">
+        <v>-0.007495250565015047</v>
+      </c>
+      <c r="F243" t="n">
+        <v>-0.0001247969314276831</v>
+      </c>
+      <c r="G243" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>ipca_P55</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>0.4254132256423441</v>
+      </c>
+      <c r="C244" t="n">
+        <v>0.3710022123498705</v>
+      </c>
+      <c r="D244" t="n">
+        <v>0.05441101329247357</v>
+      </c>
+      <c r="E244" t="n">
+        <v>0.006590512677630391</v>
+      </c>
+      <c r="F244" t="n">
+        <v>0.0003585964729067628</v>
+      </c>
+      <c r="G244" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>ipca_administrados</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>0.07556839549407418</v>
+      </c>
+      <c r="C245" t="n">
+        <v>0.3997658901177528</v>
+      </c>
+      <c r="D245" t="n">
+        <v>-0.3241974946236786</v>
+      </c>
+      <c r="E245" t="n">
+        <v>0.0007644665670470029</v>
+      </c>
+      <c r="F245" t="n">
+        <v>-0.0002478381457602027</v>
+      </c>
+      <c r="G245" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>ipca_alim_domicilio</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>0.1987814756189867</v>
+      </c>
+      <c r="C246" t="n">
+        <v>0.3544096500765428</v>
+      </c>
+      <c r="D246" t="n">
+        <v>-0.1556281744575561</v>
+      </c>
+      <c r="E246" t="n">
+        <v>-5.447459062519188e-05</v>
+      </c>
+      <c r="F246" t="n">
+        <v>8.47778109332131e-06</v>
+      </c>
+      <c r="G246" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>ipca_alimentacao</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>0.2927774211888935</v>
+      </c>
+      <c r="C247" t="n">
+        <v>0.3733989633586271</v>
+      </c>
+      <c r="D247" t="n">
+        <v>-0.08062154216973365</v>
+      </c>
+      <c r="E247" t="n">
+        <v>-0.0002580400585953114</v>
+      </c>
+      <c r="F247" t="n">
+        <v>2.080358746552244e-05</v>
+      </c>
+      <c r="G247" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>ipca_difusao</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>0.6485572467709773</v>
+      </c>
+      <c r="C248" t="n">
+        <v>0.5291866095697577</v>
+      </c>
+      <c r="D248" t="n">
+        <v>0.1193706372012195</v>
+      </c>
+      <c r="E248" t="n">
+        <v>1.299768256551457e-05</v>
+      </c>
+      <c r="F248" t="n">
+        <v>1.551541649984655e-06</v>
+      </c>
+      <c r="G248" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>ipca_industriais</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>0.0693498936122684</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0.252051879559306</v>
+      </c>
+      <c r="D249" t="n">
+        <v>-0.1827019859470375</v>
+      </c>
+      <c r="E249" t="n">
+        <v>-0.002276198113764306</v>
+      </c>
+      <c r="F249" t="n">
+        <v>0.0004158659157936396</v>
+      </c>
+      <c r="G249" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>ipca_industriais_subjacentes</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>0.2687025250315013</v>
+      </c>
+      <c r="C250" t="n">
+        <v>0.3048870689622716</v>
+      </c>
+      <c r="D250" t="n">
+        <v>-0.03618454393077036</v>
+      </c>
+      <c r="E250" t="n">
+        <v>0.0002371238131561399</v>
+      </c>
+      <c r="F250" t="n">
+        <v>-8.580217034180125e-06</v>
+      </c>
+      <c r="G250" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>ipca_livres</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>0.3010813186618921</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0.3658552947808941</v>
+      </c>
+      <c r="D251" t="n">
+        <v>-0.06477397611900203</v>
+      </c>
+      <c r="E251" t="n">
+        <v>0.001772356126649513</v>
+      </c>
+      <c r="F251" t="n">
+        <v>-0.0001148025534219625</v>
+      </c>
+      <c r="G251" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>ipca_servicos</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>0.402727181780807</v>
+      </c>
+      <c r="C252" t="n">
+        <v>0.4525872347070017</v>
+      </c>
+      <c r="D252" t="n">
+        <v>-0.04986005292619471</v>
+      </c>
+      <c r="E252" t="n">
+        <v>0.00260819716992069</v>
+      </c>
+      <c r="F252" t="n">
+        <v>-0.0001300448489341968</v>
+      </c>
+      <c r="G252" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>ipca_servicos_subjacentes</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>0.3602466052582748</v>
+      </c>
+      <c r="C253" t="n">
+        <v>0.4107531536183035</v>
+      </c>
+      <c r="D253" t="n">
+        <v>-0.0505065483600287</v>
+      </c>
+      <c r="E253" t="n">
+        <v>-0.0008182000314511995</v>
+      </c>
+      <c r="F253" t="n">
+        <v>4.132445945666701e-05</v>
+      </c>
+      <c r="G253" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>0.0009189819755979767</v>
+      </c>
+      <c r="C254" t="n">
+        <v>0.3643380105704174</v>
+      </c>
+      <c r="D254" t="n">
+        <v>-0.3634190285948194</v>
+      </c>
+      <c r="E254" t="n">
+        <v>0.001226508337041444</v>
+      </c>
+      <c r="F254" t="n">
+        <v>-0.0004457364684110488</v>
+      </c>
+      <c r="G254" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>-0.06135948185390028</v>
+      </c>
+      <c r="C255" t="n">
+        <v>-0.09691101195172984</v>
+      </c>
+      <c r="D255" t="n">
+        <v>0.03555153009782956</v>
+      </c>
+      <c r="E255" t="n">
+        <v>0.0008993719122486393</v>
+      </c>
+      <c r="F255" t="n">
+        <v>3.197404760745003e-05</v>
+      </c>
+      <c r="G255" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>-0.02698732312331309</v>
+      </c>
+      <c r="C256" t="n">
+        <v>-0.0850748517234769</v>
+      </c>
+      <c r="D256" t="n">
+        <v>0.05808752860016381</v>
+      </c>
+      <c r="E256" t="n">
+        <v>-0.0001434080045203655</v>
+      </c>
+      <c r="F256" t="n">
+        <v>-8.330216564069151e-06</v>
+      </c>
+      <c r="G256" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>1.505764016391207</v>
+      </c>
+      <c r="C257" t="n">
+        <v>0.4515615745217698</v>
+      </c>
+      <c r="D257" t="n">
+        <v>1.054202441869438</v>
+      </c>
+      <c r="E257" t="n">
+        <v>-1.010806239103762e-05</v>
+      </c>
+      <c r="F257" t="n">
+        <v>-1.065594405520048e-05</v>
+      </c>
+      <c r="G257" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>cambio_media_mensal</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>-2.217400142430803</v>
+      </c>
+      <c r="C258" t="n">
+        <v>0.2394330259234668</v>
+      </c>
+      <c r="D258" t="n">
+        <v>-2.45683316835427</v>
+      </c>
+      <c r="E258" t="n">
+        <v>0.0004412217234747757</v>
+      </c>
+      <c r="F258" t="n">
+        <v>-0.001084008164831265</v>
+      </c>
+      <c r="G258" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>fenabrave_automoveis</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>-5.275650780846597</v>
+      </c>
+      <c r="C259" t="n">
+        <v>-3.315304478210668</v>
+      </c>
+      <c r="D259" t="n">
+        <v>-1.960346302635929</v>
+      </c>
+      <c r="E259" t="n">
+        <v>0.0004487220222068755</v>
+      </c>
+      <c r="F259" t="n">
+        <v>-0.0008796505571445655</v>
+      </c>
+      <c r="G259" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>fenabrave_caminhoes</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>-0.05988950461249587</v>
+      </c>
+      <c r="C260" t="n">
+        <v>-0.1869566535082247</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0.1270671488957288</v>
+      </c>
+      <c r="E260" t="n">
+        <v>0.00922144386108433</v>
+      </c>
+      <c r="F260" t="n">
+        <v>0.001171742580130007</v>
+      </c>
+      <c r="G260" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>fenabrave_comerciais_leves</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>-0.3424365805175689</v>
+      </c>
+      <c r="C261" t="n">
+        <v>-3.674362165770156</v>
+      </c>
+      <c r="D261" t="n">
+        <v>3.331925585252587</v>
+      </c>
+      <c r="E261" t="n">
+        <v>0.000500128308639595</v>
+      </c>
+      <c r="F261" t="n">
+        <v>0.001666390307465369</v>
+      </c>
+      <c r="G261" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>fenabrave_onibus</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>-4.153947786527201</v>
+      </c>
+      <c r="C262" t="n">
+        <v>-7.383064998188746</v>
+      </c>
+      <c r="D262" t="n">
+        <v>3.229117211661544</v>
+      </c>
+      <c r="E262" t="n">
+        <v>0.00014881975820373</v>
+      </c>
+      <c r="F262" t="n">
+        <v>0.0004805564426509737</v>
+      </c>
+      <c r="G262" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>fgv_nuci</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>-0.09999999999999432</v>
+      </c>
+      <c r="C263" t="n">
+        <v>-0.0007075741726706164</v>
+      </c>
+      <c r="D263" t="n">
+        <v>-0.0992924258273237</v>
+      </c>
+      <c r="E263" t="n">
+        <v>1.507266818357222e-05</v>
+      </c>
+      <c r="F263" t="n">
+        <v>-1.496601787637207e-06</v>
+      </c>
+      <c r="G263" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>icbr_agro</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>0.6843143401802365</v>
+      </c>
+      <c r="C264" t="n">
+        <v>0.829622025542987</v>
+      </c>
+      <c r="D264" t="n">
+        <v>-0.1453076853627505</v>
+      </c>
+      <c r="E264" t="n">
+        <v>-2.506741928576245e-05</v>
+      </c>
+      <c r="F264" t="n">
+        <v>3.642488674431713e-06</v>
+      </c>
+      <c r="G264" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>icbr_energia</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>-0.2598010997918344</v>
+      </c>
+      <c r="C265" t="n">
+        <v>-0.5233105695203532</v>
+      </c>
+      <c r="D265" t="n">
+        <v>0.2635094697285189</v>
+      </c>
+      <c r="E265" t="n">
+        <v>-4.65356665124111e-06</v>
+      </c>
+      <c r="F265" t="n">
+        <v>-1.226258880614864e-06</v>
+      </c>
+      <c r="G265" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>icbr_metal</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>2.221426097799162</v>
+      </c>
+      <c r="C266" t="n">
+        <v>1.030208331322333</v>
+      </c>
+      <c r="D266" t="n">
+        <v>1.191217766476829</v>
+      </c>
+      <c r="E266" t="n">
+        <v>-8.733652496939024e-05</v>
+      </c>
+      <c r="F266" t="n">
+        <v>-0.0001040368202058849</v>
+      </c>
+      <c r="G266" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>0.02834541292932119</v>
+      </c>
+      <c r="C267" t="n">
+        <v>0.5035831033366759</v>
+      </c>
+      <c r="D267" t="n">
+        <v>-0.4752376904073546</v>
+      </c>
+      <c r="E267" t="n">
+        <v>0.0001926085445975035</v>
+      </c>
+      <c r="F267" t="n">
+        <v>-9.153483988723954e-05</v>
+      </c>
+      <c r="G267" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>-0.6322592568392276</v>
+      </c>
+      <c r="C268" t="n">
+        <v>0.6017687423318498</v>
+      </c>
+      <c r="D268" t="n">
+        <v>-1.234027999171077</v>
+      </c>
+      <c r="E268" t="n">
+        <v>-0.0002124115431185015</v>
+      </c>
+      <c r="F268" t="n">
+        <v>0.0002621217915553654</v>
+      </c>
+      <c r="G268" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>-0.3700623027681143</v>
+      </c>
+      <c r="C269" t="n">
+        <v>0.3571750251056628</v>
+      </c>
+      <c r="D269" t="n">
+        <v>-0.7272373278737772</v>
+      </c>
+      <c r="E269" t="n">
+        <v>-0.005502333388696395</v>
+      </c>
+      <c r="F269" t="n">
+        <v>0.004001502230666231</v>
+      </c>
+      <c r="G269" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>0.4489387037604357</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0.4738695514624255</v>
+      </c>
+      <c r="D270" t="n">
+        <v>-0.02493084770198987</v>
+      </c>
+      <c r="E270" t="n">
+        <v>-0.001276954347509649</v>
+      </c>
+      <c r="F270" t="n">
+        <v>3.183555436015691e-05</v>
+      </c>
+      <c r="G270" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>-0.6966185442159021</v>
+      </c>
+      <c r="C271" t="n">
+        <v>0.4120753985333546</v>
+      </c>
+      <c r="D271" t="n">
+        <v>-1.108693942749257</v>
+      </c>
+      <c r="E271" t="n">
+        <v>-0.002827052370823669</v>
+      </c>
+      <c r="F271" t="n">
+        <v>0.003134335839367127</v>
+      </c>
+      <c r="G271" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>0.2427188518995873</v>
+      </c>
+      <c r="C272" t="n">
+        <v>0.3756912255396723</v>
+      </c>
+      <c r="D272" t="n">
+        <v>-0.132972373640085</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0.005261491203990463</v>
+      </c>
+      <c r="F272" t="n">
+        <v>-0.0006996329742810406</v>
+      </c>
+      <c r="G272" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>0.3109432966846084</v>
+      </c>
+      <c r="C273" t="n">
+        <v>0.4105387516291625</v>
+      </c>
+      <c r="D273" t="n">
+        <v>-0.09959545494455421</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0.007226705844324251</v>
+      </c>
+      <c r="F273" t="n">
+        <v>-0.0007197470563159425</v>
+      </c>
+      <c r="G273" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>ipca_DP</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>0.30432517773155</v>
+      </c>
+      <c r="C274" t="n">
+        <v>0.3857555485490685</v>
+      </c>
+      <c r="D274" t="n">
+        <v>-0.08143037081751846</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0.02768902755853344</v>
+      </c>
+      <c r="F274" t="n">
+        <v>-0.002254727781667866</v>
+      </c>
+      <c r="G274" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>ipca_EX0</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>0.3985075622549502</v>
+      </c>
+      <c r="C275" t="n">
+        <v>0.3769855079368244</v>
+      </c>
+      <c r="D275" t="n">
+        <v>0.02152205431812574</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0.03291864474937934</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0.0007084768603752269</v>
+      </c>
+      <c r="G275" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>ipca_EX3</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>0.358515394556541</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0.3851849062698253</v>
+      </c>
+      <c r="D276" t="n">
+        <v>-0.02666951171328428</v>
+      </c>
+      <c r="E276" t="n">
+        <v>-0.008432628262855112</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0.0002248940782299865</v>
+      </c>
+      <c r="G276" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>ipca_MS</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>0.3611275205637015</v>
+      </c>
+      <c r="C277" t="n">
+        <v>0.3631687091734229</v>
+      </c>
+      <c r="D277" t="n">
+        <v>-0.002041188609721421</v>
+      </c>
+      <c r="E277" t="n">
+        <v>-0.04555967240359249</v>
+      </c>
+      <c r="F277" t="n">
+        <v>9.299588437285233e-05</v>
+      </c>
+      <c r="G277" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>ipca_P55</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>0.4254132256423441</v>
+      </c>
+      <c r="C278" t="n">
+        <v>0.3887562132352936</v>
+      </c>
+      <c r="D278" t="n">
+        <v>0.03665701240705044</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0.02976457256477965</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0.001091080305797681</v>
+      </c>
+      <c r="G278" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>ipca_administrados</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>0.07556839549407418</v>
+      </c>
+      <c r="C279" t="n">
+        <v>0.4210861950862472</v>
+      </c>
+      <c r="D279" t="n">
+        <v>-0.345517799592173</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0.00288804335520847</v>
+      </c>
+      <c r="F279" t="n">
+        <v>-0.0009978703852184271</v>
+      </c>
+      <c r="G279" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>ipca_alim_domicilio</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>0.1987814756189867</v>
+      </c>
+      <c r="C280" t="n">
+        <v>0.3624882723481578</v>
+      </c>
+      <c r="D280" t="n">
+        <v>-0.1637067967291711</v>
+      </c>
+      <c r="E280" t="n">
+        <v>-0.0003248551406860321</v>
+      </c>
+      <c r="F280" t="n">
+        <v>5.318099448271454e-05</v>
+      </c>
+      <c r="G280" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>ipca_alimentacao</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>0.2927774211888935</v>
+      </c>
+      <c r="C281" t="n">
+        <v>0.3829446310802052</v>
+      </c>
+      <c r="D281" t="n">
+        <v>-0.09016720989131166</v>
+      </c>
+      <c r="E281" t="n">
+        <v>-0.001210406043100839</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0.0001091389357419854</v>
+      </c>
+      <c r="G281" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>ipca_difusao</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>0.6485572467709773</v>
+      </c>
+      <c r="C282" t="n">
+        <v>0.5399911661315312</v>
+      </c>
+      <c r="D282" t="n">
+        <v>0.108566080639446</v>
+      </c>
+      <c r="E282" t="n">
+        <v>6.263680995417139e-05</v>
+      </c>
+      <c r="F282" t="n">
+        <v>6.800232960482225e-06</v>
+      </c>
+      <c r="G282" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>ipca_industriais</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>0.0693498936122684</v>
+      </c>
+      <c r="C283" t="n">
+        <v>0.2673279715207188</v>
+      </c>
+      <c r="D283" t="n">
+        <v>-0.1979780779084504</v>
+      </c>
+      <c r="E283" t="n">
+        <v>-0.009102146333030801</v>
+      </c>
+      <c r="F283" t="n">
+        <v>0.001802025435854888</v>
+      </c>
+      <c r="G283" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>ipca_industriais_subjacentes</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>0.2687025250315013</v>
+      </c>
+      <c r="C284" t="n">
+        <v>0.3228885130627736</v>
+      </c>
+      <c r="D284" t="n">
+        <v>-0.05418598803127232</v>
+      </c>
+      <c r="E284" t="n">
+        <v>0.001506355224357119</v>
+      </c>
+      <c r="F284" t="n">
+        <v>-8.16233461578594e-05</v>
+      </c>
+      <c r="G284" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>ipca_livres</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>0.3010813186618921</v>
+      </c>
+      <c r="C285" t="n">
+        <v>0.3881864677791548</v>
+      </c>
+      <c r="D285" t="n">
+        <v>-0.08710514911726268</v>
+      </c>
+      <c r="E285" t="n">
+        <v>0.006110895767346943</v>
+      </c>
+      <c r="F285" t="n">
+        <v>-0.0005322904870548048</v>
+      </c>
+      <c r="G285" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>ipca_servicos</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>0.402727181780807</v>
+      </c>
+      <c r="C286" t="n">
+        <v>0.4818993958437056</v>
+      </c>
+      <c r="D286" t="n">
+        <v>-0.07917221406289857</v>
+      </c>
+      <c r="E286" t="n">
+        <v>0.009808830968780454</v>
+      </c>
+      <c r="F286" t="n">
+        <v>-0.0007765868651670748</v>
+      </c>
+      <c r="G286" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>ipca_servicos_subjacentes</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>0.3602466052582748</v>
+      </c>
+      <c r="C287" t="n">
+        <v>0.4288097081745149</v>
+      </c>
+      <c r="D287" t="n">
+        <v>-0.06856310291624013</v>
+      </c>
+      <c r="E287" t="n">
+        <v>-0.003133862225102901</v>
+      </c>
+      <c r="F287" t="n">
+        <v>0.0002148673182650475</v>
+      </c>
+      <c r="G287" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>0.0009189819755979767</v>
+      </c>
+      <c r="C288" t="n">
+        <v>0.3828250949146511</v>
+      </c>
+      <c r="D288" t="n">
+        <v>-0.3819061129390531</v>
+      </c>
+      <c r="E288" t="n">
+        <v>0.005111320642713754</v>
+      </c>
+      <c r="F288" t="n">
+        <v>-0.001952044598643952</v>
+      </c>
+      <c r="G288" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>-0.06135948185390028</v>
+      </c>
+      <c r="C289" t="n">
+        <v>-0.0713962819169079</v>
+      </c>
+      <c r="D289" t="n">
+        <v>0.01003680006300763</v>
+      </c>
+      <c r="E289" t="n">
+        <v>0.003683463113463049</v>
+      </c>
+      <c r="F289" t="n">
+        <v>3.697018280929219e-05</v>
+      </c>
+      <c r="G289" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>-0.02698732312331309</v>
+      </c>
+      <c r="C290" t="n">
+        <v>-0.08673144510826104</v>
+      </c>
+      <c r="D290" t="n">
+        <v>0.05974412198494795</v>
+      </c>
+      <c r="E290" t="n">
+        <v>-0.002097987397439938</v>
+      </c>
+      <c r="F290" t="n">
+        <v>-0.0001253424149955351</v>
+      </c>
+      <c r="G290" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>1.505764016391207</v>
+      </c>
+      <c r="C291" t="n">
+        <v>0.4513071173810315</v>
+      </c>
+      <c r="D291" t="n">
+        <v>1.054456899010176</v>
+      </c>
+      <c r="E291" t="n">
+        <v>-1.080229835246995e-05</v>
+      </c>
+      <c r="F291" t="n">
+        <v>-1.139055802292819e-05</v>
+      </c>
+      <c r="G291" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>cambio_media_mensal</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>-2.217400142430803</v>
+      </c>
+      <c r="C292" t="n">
+        <v>0.2518101227476518</v>
+      </c>
+      <c r="D292" t="n">
+        <v>-2.469210265178455</v>
+      </c>
+      <c r="E292" t="n">
+        <v>0.0004534343811706565</v>
+      </c>
+      <c r="F292" t="n">
+        <v>-0.001119624828571425</v>
+      </c>
+      <c r="G292" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>fenabrave_automoveis</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>-5.275650780846597</v>
+      </c>
+      <c r="C293" t="n">
+        <v>-3.35059020084603</v>
+      </c>
+      <c r="D293" t="n">
+        <v>-1.925060580000566</v>
+      </c>
+      <c r="E293" t="n">
+        <v>0.0004805786038090694</v>
+      </c>
+      <c r="F293" t="n">
+        <v>-0.0009251429257845496</v>
+      </c>
+      <c r="G293" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>fenabrave_caminhoes</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>-1.828347386793894</v>
+      </c>
+      <c r="C294" t="n">
+        <v>-5.588230101529596</v>
+      </c>
+      <c r="D294" t="n">
+        <v>3.759882714735701</v>
+      </c>
+      <c r="E294" t="n">
+        <v>0.0003470812687055395</v>
+      </c>
+      <c r="F294" t="n">
+        <v>0.001304984862814496</v>
+      </c>
+      <c r="G294" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>fenabrave_comerciais_leves</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>-0.3424365805175689</v>
+      </c>
+      <c r="C295" t="n">
+        <v>-3.707150410736177</v>
+      </c>
+      <c r="D295" t="n">
+        <v>3.364713830218607</v>
+      </c>
+      <c r="E295" t="n">
+        <v>0.0004738125965285263</v>
+      </c>
+      <c r="F295" t="n">
+        <v>0.001594243796471321</v>
+      </c>
+      <c r="G295" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>fenabrave_onibus</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>-4.153947786527201</v>
+      </c>
+      <c r="C296" t="n">
+        <v>-7.385292915425697</v>
+      </c>
+      <c r="D296" t="n">
+        <v>3.231345128898495</v>
+      </c>
+      <c r="E296" t="n">
+        <v>0.0001399309435172346</v>
+      </c>
+      <c r="F296" t="n">
+        <v>0.0004521651727165865</v>
+      </c>
+      <c r="G296" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>fgv_nuci</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>-0.09999999999999432</v>
+      </c>
+      <c r="C297" t="n">
+        <v>0.008585175397283009</v>
+      </c>
+      <c r="D297" t="n">
+        <v>-0.1085851753972773</v>
+      </c>
+      <c r="E297" t="n">
+        <v>-0.0007835545345207968</v>
+      </c>
+      <c r="F297" t="n">
+        <v>8.508240656427271e-05</v>
+      </c>
+      <c r="G297" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>icbr_agro</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>0.6843143401802365</v>
+      </c>
+      <c r="C298" t="n">
+        <v>0.8396436882026466</v>
+      </c>
+      <c r="D298" t="n">
+        <v>-0.15532934802241</v>
+      </c>
+      <c r="E298" t="n">
+        <v>-1.912291440444696e-05</v>
+      </c>
+      <c r="F298" t="n">
+        <v>2.970349826731099e-06</v>
+      </c>
+      <c r="G298" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>icbr_energia</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>-0.2598010997918344</v>
+      </c>
+      <c r="C299" t="n">
+        <v>-0.5069328608833613</v>
+      </c>
+      <c r="D299" t="n">
+        <v>0.247131761091527</v>
+      </c>
+      <c r="E299" t="n">
+        <v>3.356713284123996e-07</v>
+      </c>
+      <c r="F299" t="n">
+        <v>8.295504653848864e-08</v>
+      </c>
+      <c r="G299" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>icbr_metal</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>2.221426097799162</v>
+      </c>
+      <c r="C300" t="n">
+        <v>1.052487146514025</v>
+      </c>
+      <c r="D300" t="n">
+        <v>1.168938951285136</v>
+      </c>
+      <c r="E300" t="n">
+        <v>-7.723652860592398e-05</v>
+      </c>
+      <c r="F300" t="n">
+        <v>-9.028478674951323e-05</v>
+      </c>
+      <c r="G300" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>0.02834541292932119</v>
+      </c>
+      <c r="C301" t="n">
+        <v>0.5020655485568761</v>
+      </c>
+      <c r="D301" t="n">
+        <v>-0.4737201356275549</v>
+      </c>
+      <c r="E301" t="n">
+        <v>0.0004425337513503802</v>
+      </c>
+      <c r="F301" t="n">
+        <v>-0.0002096371487094728</v>
+      </c>
+      <c r="G301" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>-0.6322592568392276</v>
+      </c>
+      <c r="C302" t="n">
+        <v>0.6021075832357647</v>
+      </c>
+      <c r="D302" t="n">
+        <v>-1.234366840074992</v>
+      </c>
+      <c r="E302" t="n">
+        <v>-0.000283857669700862</v>
+      </c>
+      <c r="F302" t="n">
+        <v>0.0003503844947797038</v>
+      </c>
+      <c r="G302" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>-0.3700623027681143</v>
+      </c>
+      <c r="C303" t="n">
+        <v>0.3569547595378958</v>
+      </c>
+      <c r="D303" t="n">
+        <v>-0.72701706230601</v>
+      </c>
+      <c r="E303" t="n">
+        <v>-0.006444918085736869</v>
+      </c>
+      <c r="F303" t="n">
+        <v>0.004685565413495292</v>
+      </c>
+      <c r="G303" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>0.4489387037604357</v>
+      </c>
+      <c r="C304" t="n">
+        <v>0.4727969449726304</v>
+      </c>
+      <c r="D304" t="n">
+        <v>-0.02385824121219476</v>
+      </c>
+      <c r="E304" t="n">
+        <v>-0.001404609780934338</v>
+      </c>
+      <c r="F304" t="n">
+        <v>3.351151896253947e-05</v>
+      </c>
+      <c r="G304" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>-0.6966185442159021</v>
+      </c>
+      <c r="C305" t="n">
+        <v>0.4125574375250848</v>
+      </c>
+      <c r="D305" t="n">
+        <v>-1.109175981740987</v>
+      </c>
+      <c r="E305" t="n">
+        <v>-0.002298448003635463</v>
+      </c>
+      <c r="F305" t="n">
+        <v>0.002549383320912976</v>
+      </c>
+      <c r="G305" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>0.2427188518995873</v>
+      </c>
+      <c r="C306" t="n">
+        <v>0.3746540475478837</v>
+      </c>
+      <c r="D306" t="n">
+        <v>-0.1319351956482964</v>
+      </c>
+      <c r="E306" t="n">
+        <v>0.005184536036890892</v>
+      </c>
+      <c r="F306" t="n">
+        <v>-0.0006840227763728434</v>
+      </c>
+      <c r="G306" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>0.3109432966846084</v>
+      </c>
+      <c r="C307" t="n">
+        <v>0.4095676665291558</v>
+      </c>
+      <c r="D307" t="n">
+        <v>-0.0986243698445475</v>
+      </c>
+      <c r="E307" t="n">
+        <v>0.007043161658104523</v>
+      </c>
+      <c r="F307" t="n">
+        <v>-0.0006946273802438369</v>
+      </c>
+      <c r="G307" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>ipca_DP</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>0.30432517773155</v>
+      </c>
+      <c r="C308" t="n">
+        <v>0.3848731318643956</v>
+      </c>
+      <c r="D308" t="n">
+        <v>-0.08054795413284564</v>
+      </c>
+      <c r="E308" t="n">
+        <v>0.02774027055568385</v>
+      </c>
+      <c r="F308" t="n">
+        <v>-0.002234422040351951</v>
+      </c>
+      <c r="G308" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>ipca_EX0</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>0.3985075622549502</v>
+      </c>
+      <c r="C309" t="n">
+        <v>0.3753434084300306</v>
+      </c>
+      <c r="D309" t="n">
+        <v>0.02316415382491958</v>
+      </c>
+      <c r="E309" t="n">
+        <v>0.03332754133461235</v>
+      </c>
+      <c r="F309" t="n">
+        <v>0.0007720042940813263</v>
+      </c>
+      <c r="G309" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>ipca_EX3</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>0.358515394556541</v>
+      </c>
+      <c r="C310" t="n">
+        <v>0.3838992054617166</v>
+      </c>
+      <c r="D310" t="n">
+        <v>-0.02538381090517553</v>
+      </c>
+      <c r="E310" t="n">
+        <v>-0.008382935784096971</v>
+      </c>
+      <c r="F310" t="n">
+        <v>0.0002127908567737469</v>
+      </c>
+      <c r="G310" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>ipca_MS</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>0.3611275205637015</v>
+      </c>
+      <c r="C311" t="n">
+        <v>0.3624109579958212</v>
+      </c>
+      <c r="D311" t="n">
+        <v>-0.001283437432119678</v>
+      </c>
+      <c r="E311" t="n">
+        <v>-0.05099159178500656</v>
+      </c>
+      <c r="F311" t="n">
+        <v>6.54445176202437e-05</v>
+      </c>
+      <c r="G311" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>ipca_P55</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>0.4254132256423441</v>
+      </c>
+      <c r="C312" t="n">
+        <v>0.3879755932806379</v>
+      </c>
+      <c r="D312" t="n">
+        <v>0.03743763236170618</v>
+      </c>
+      <c r="E312" t="n">
+        <v>0.03007209670591902</v>
+      </c>
+      <c r="F312" t="n">
+        <v>0.001125828100821872</v>
+      </c>
+      <c r="G312" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>ipca_administrados</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>0.07556839549407418</v>
+      </c>
+      <c r="C313" t="n">
+        <v>0.4217835712812715</v>
+      </c>
+      <c r="D313" t="n">
+        <v>-0.3462151757871973</v>
+      </c>
+      <c r="E313" t="n">
+        <v>0.00291604706213542</v>
+      </c>
+      <c r="F313" t="n">
+        <v>-0.001009579746220955</v>
+      </c>
+      <c r="G313" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>ipca_alim_domicilio</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>0.1987814756189867</v>
+      </c>
+      <c r="C314" t="n">
+        <v>0.3611651504365799</v>
+      </c>
+      <c r="D314" t="n">
+        <v>-0.1623836748175931</v>
+      </c>
+      <c r="E314" t="n">
+        <v>-0.0001994923550669909</v>
+      </c>
+      <c r="F314" t="n">
+        <v>3.239430171379408e-05</v>
+      </c>
+      <c r="G314" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>ipca_alimentacao</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>0.2927774211888935</v>
+      </c>
+      <c r="C315" t="n">
+        <v>0.3815990558944836</v>
+      </c>
+      <c r="D315" t="n">
+        <v>-0.08882163470559018</v>
+      </c>
+      <c r="E315" t="n">
+        <v>-0.001026329357630127</v>
+      </c>
+      <c r="F315" t="n">
+        <v>9.116025129104616e-05</v>
+      </c>
+      <c r="G315" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>ipca_difusao</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>0.6485572467709773</v>
+      </c>
+      <c r="C316" t="n">
+        <v>0.532737857485595</v>
+      </c>
+      <c r="D316" t="n">
+        <v>0.1158193892853823</v>
+      </c>
+      <c r="E316" t="n">
+        <v>6.309859069723064e-05</v>
+      </c>
+      <c r="F316" t="n">
+        <v>7.308040239321555e-06</v>
+      </c>
+      <c r="G316" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>ipca_industriais</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>0.0693498936122684</v>
+      </c>
+      <c r="C317" t="n">
+        <v>0.2665389504301717</v>
+      </c>
+      <c r="D317" t="n">
+        <v>-0.1971890568179033</v>
+      </c>
+      <c r="E317" t="n">
+        <v>-0.008255099913560609</v>
+      </c>
+      <c r="F317" t="n">
+        <v>0.001627815365892572</v>
+      </c>
+      <c r="G317" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>ipca_industriais_subjacentes</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>0.2687025250315013</v>
+      </c>
+      <c r="C318" t="n">
+        <v>0.3214342415136764</v>
+      </c>
+      <c r="D318" t="n">
+        <v>-0.05273171648217514</v>
+      </c>
+      <c r="E318" t="n">
+        <v>0.00147996676841654</v>
+      </c>
+      <c r="F318" t="n">
+        <v>-7.804118803518196e-05</v>
+      </c>
+      <c r="G318" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>ipca_livres</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>0.3010813186618921</v>
+      </c>
+      <c r="C319" t="n">
+        <v>0.3869718997536048</v>
+      </c>
+      <c r="D319" t="n">
+        <v>-0.08589058109171273</v>
+      </c>
+      <c r="E319" t="n">
+        <v>0.006076600866078403</v>
+      </c>
+      <c r="F319" t="n">
+        <v>-0.0005219227794498788</v>
+      </c>
+      <c r="G319" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>ipca_servicos</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>0.402727181780807</v>
+      </c>
+      <c r="C320" t="n">
+        <v>0.4799514762471733</v>
+      </c>
+      <c r="D320" t="n">
+        <v>-0.07722429446636629</v>
+      </c>
+      <c r="E320" t="n">
+        <v>0.009385804733560267</v>
+      </c>
+      <c r="F320" t="n">
+        <v>-0.0007248121485482727</v>
+      </c>
+      <c r="G320" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>ipca_servicos_subjacentes</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>0.3602466052582748</v>
+      </c>
+      <c r="C321" t="n">
+        <v>0.4278800571627041</v>
+      </c>
+      <c r="D321" t="n">
+        <v>-0.06763345190442931</v>
+      </c>
+      <c r="E321" t="n">
+        <v>-0.003438607833970918</v>
+      </c>
+      <c r="F321" t="n">
+        <v>0.0002325649175570659</v>
+      </c>
+      <c r="G321" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>0.0009189819755979767</v>
+      </c>
+      <c r="C322" t="n">
+        <v>0.3817800887006159</v>
+      </c>
+      <c r="D322" t="n">
+        <v>-0.3808611067250179</v>
+      </c>
+      <c r="E322" t="n">
+        <v>0.005043132197460815</v>
+      </c>
+      <c r="F322" t="n">
+        <v>-0.001920732910085497</v>
+      </c>
+      <c r="G322" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>-0.06135948185390028</v>
+      </c>
+      <c r="C323" t="n">
+        <v>-0.06957576096049814</v>
+      </c>
+      <c r="D323" t="n">
+        <v>0.008216279106597866</v>
+      </c>
+      <c r="E323" t="n">
+        <v>0.003391939773859737</v>
+      </c>
+      <c r="F323" t="n">
+        <v>2.786912389480205e-05</v>
+      </c>
+      <c r="G323" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>-0.02698732312331309</v>
+      </c>
+      <c r="C324" t="n">
+        <v>-0.0865985617982872</v>
+      </c>
+      <c r="D324" t="n">
+        <v>0.05961123867497411</v>
+      </c>
+      <c r="E324" t="n">
+        <v>-0.002532868636844239</v>
+      </c>
+      <c r="F324" t="n">
+        <v>-0.0001509874368432782</v>
+      </c>
+      <c r="G324" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>cambio_media_mensal</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>-2.217400142430803</v>
+      </c>
+      <c r="C325" t="n">
+        <v>0.3548087956445402</v>
+      </c>
+      <c r="D325" t="n">
+        <v>-2.572208938075343</v>
+      </c>
+      <c r="E325" t="n">
+        <v>0.0004284648040403338</v>
+      </c>
+      <c r="F325" t="n">
+        <v>-0.001102100998603247</v>
+      </c>
+      <c r="G325" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>fenabrave_automoveis</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>-5.275650780846597</v>
+      </c>
+      <c r="C326" t="n">
+        <v>-3.897875774955659</v>
+      </c>
+      <c r="D326" t="n">
+        <v>-1.377775005890938</v>
+      </c>
+      <c r="E326" t="n">
+        <v>0.0004373453190384129</v>
+      </c>
+      <c r="F326" t="n">
+        <v>-0.0006025634495145237</v>
+      </c>
+      <c r="G326" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>fenabrave_caminhoes</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>-1.828347386793894</v>
+      </c>
+      <c r="C327" t="n">
+        <v>-5.732597302821642</v>
+      </c>
+      <c r="D327" t="n">
+        <v>3.904249916027748</v>
+      </c>
+      <c r="E327" t="n">
+        <v>0.0003098744183496411</v>
+      </c>
+      <c r="F327" t="n">
+        <v>0.001209827171820734</v>
+      </c>
+      <c r="G327" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>fenabrave_comerciais_leves</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>-0.3424365805175689</v>
+      </c>
+      <c r="C328" t="n">
+        <v>-3.992753537015551</v>
+      </c>
+      <c r="D328" t="n">
+        <v>3.650316956497981</v>
+      </c>
+      <c r="E328" t="n">
+        <v>0.0006236810379385214</v>
+      </c>
+      <c r="F328" t="n">
+        <v>0.002276633468233246</v>
+      </c>
+      <c r="G328" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>fenabrave_onibus</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>-4.153947786527201</v>
+      </c>
+      <c r="C329" t="n">
+        <v>-7.259966161496442</v>
+      </c>
+      <c r="D329" t="n">
+        <v>3.106018374969242</v>
+      </c>
+      <c r="E329" t="n">
+        <v>0.000159689678970263</v>
+      </c>
+      <c r="F329" t="n">
+        <v>0.0004959990771745761</v>
+      </c>
+      <c r="G329" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>fgv_nuci</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>-0.09999999999999433</v>
+      </c>
+      <c r="C330" t="n">
+        <v>0.02727619625955043</v>
+      </c>
+      <c r="D330" t="n">
+        <v>-0.1272761962595448</v>
+      </c>
+      <c r="E330" t="n">
+        <v>-0.0003778315860641618</v>
+      </c>
+      <c r="F330" t="n">
+        <v>4.808896710095734e-05</v>
+      </c>
+      <c r="G330" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>icbr_agro</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>0.6843143401802365</v>
+      </c>
+      <c r="C331" t="n">
+        <v>1.378511274677356</v>
+      </c>
+      <c r="D331" t="n">
+        <v>-0.6941969344971189</v>
+      </c>
+      <c r="E331" t="n">
+        <v>-1.946143779475642e-05</v>
+      </c>
+      <c r="F331" t="n">
+        <v>1.351007045802627e-05</v>
+      </c>
+      <c r="G331" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>icbr_energia</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>-0.2598010997918342</v>
+      </c>
+      <c r="C332" t="n">
+        <v>-0.214494894685726</v>
+      </c>
+      <c r="D332" t="n">
+        <v>-0.04530620510610813</v>
+      </c>
+      <c r="E332" t="n">
+        <v>-7.726178152179337e-06</v>
+      </c>
+      <c r="F332" t="n">
+        <v>3.500438120489686e-07</v>
+      </c>
+      <c r="G332" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>icbr_metal</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>2.221426097799162</v>
+      </c>
+      <c r="C333" t="n">
+        <v>1.188959394113492</v>
+      </c>
+      <c r="D333" t="n">
+        <v>1.032466703685669</v>
+      </c>
+      <c r="E333" t="n">
+        <v>-9.061147552489107e-05</v>
+      </c>
+      <c r="F333" t="n">
+        <v>-9.355333145127898e-05</v>
+      </c>
+      <c r="G333" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>0.02834541292932125</v>
+      </c>
+      <c r="C334" t="n">
+        <v>0.4905762295404892</v>
+      </c>
+      <c r="D334" t="n">
+        <v>-0.462230816611168</v>
+      </c>
+      <c r="E334" t="n">
+        <v>0.0003048644954038542</v>
+      </c>
+      <c r="F334" t="n">
+        <v>-0.0001409177646662752</v>
+      </c>
+      <c r="G334" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>-0.6322592568392276</v>
+      </c>
+      <c r="C335" t="n">
+        <v>0.6066351519410065</v>
+      </c>
+      <c r="D335" t="n">
+        <v>-1.238894408780234</v>
+      </c>
+      <c r="E335" t="n">
+        <v>-0.0001216002193883222</v>
+      </c>
+      <c r="F335" t="n">
+        <v>0.0001506498319066422</v>
+      </c>
+      <c r="G335" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>-0.3700623027681141</v>
+      </c>
+      <c r="C336" t="n">
+        <v>0.3689082581632018</v>
+      </c>
+      <c r="D336" t="n">
+        <v>-0.738970560931316</v>
+      </c>
+      <c r="E336" t="n">
+        <v>-0.006874556168922488</v>
+      </c>
+      <c r="F336" t="n">
+        <v>0.00508009462830249</v>
+      </c>
+      <c r="G336" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>0.4489387037604357</v>
+      </c>
+      <c r="C337" t="n">
+        <v>0.516304527026153</v>
+      </c>
+      <c r="D337" t="n">
+        <v>-0.06736582326571736</v>
+      </c>
+      <c r="E337" t="n">
+        <v>-0.002705116681452554</v>
+      </c>
+      <c r="F337" t="n">
+        <v>0.0001822324122758766</v>
+      </c>
+      <c r="G337" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>-0.6966185442159022</v>
+      </c>
+      <c r="C338" t="n">
+        <v>0.4366457683698114</v>
+      </c>
+      <c r="D338" t="n">
+        <v>-1.133264312585714</v>
+      </c>
+      <c r="E338" t="n">
+        <v>-0.003880106967366236</v>
+      </c>
+      <c r="F338" t="n">
+        <v>0.004397186755131336</v>
+      </c>
+      <c r="G338" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>0.2427188518995873</v>
+      </c>
+      <c r="C339" t="n">
+        <v>0.3699813608095837</v>
+      </c>
+      <c r="D339" t="n">
+        <v>-0.1272625089099964</v>
+      </c>
+      <c r="E339" t="n">
+        <v>0.005614697563127729</v>
+      </c>
+      <c r="F339" t="n">
+        <v>-0.0007145404986544779</v>
+      </c>
+      <c r="G339" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>0.3109432966846084</v>
+      </c>
+      <c r="C340" t="n">
+        <v>0.4078244114141327</v>
+      </c>
+      <c r="D340" t="n">
+        <v>-0.09688111472952429</v>
+      </c>
+      <c r="E340" t="n">
+        <v>0.007074085329359594</v>
+      </c>
+      <c r="F340" t="n">
+        <v>-0.0006853452724001315</v>
+      </c>
+      <c r="G340" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>ipca_DP</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>0.30432517773155</v>
+      </c>
+      <c r="C341" t="n">
+        <v>0.3859083034096225</v>
+      </c>
+      <c r="D341" t="n">
+        <v>-0.08158312567807251</v>
+      </c>
+      <c r="E341" t="n">
+        <v>0.02981701139145515</v>
+      </c>
+      <c r="F341" t="n">
+        <v>-0.002432564987693606</v>
+      </c>
+      <c r="G341" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>ipca_EX0</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>0.3985075622549502</v>
+      </c>
+      <c r="C342" t="n">
+        <v>0.3838681650576055</v>
+      </c>
+      <c r="D342" t="n">
+        <v>0.01463939719734472</v>
+      </c>
+      <c r="E342" t="n">
+        <v>0.02991841174197411</v>
+      </c>
+      <c r="F342" t="n">
+        <v>0.000437987513004461</v>
+      </c>
+      <c r="G342" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>ipca_EX3</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>0.358515394556541</v>
+      </c>
+      <c r="C343" t="n">
+        <v>0.3866351750928059</v>
+      </c>
+      <c r="D343" t="n">
+        <v>-0.02811978053626488</v>
+      </c>
+      <c r="E343" t="n">
+        <v>0.004226181069135857</v>
+      </c>
+      <c r="F343" t="n">
+        <v>-0.0001188392841706176</v>
+      </c>
+      <c r="G343" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>ipca_MS</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>0.3611275205637015</v>
+      </c>
+      <c r="C344" t="n">
+        <v>0.3644383573869729</v>
+      </c>
+      <c r="D344" t="n">
+        <v>-0.003310836823271392</v>
+      </c>
+      <c r="E344" t="n">
+        <v>-0.07989794117158817</v>
+      </c>
+      <c r="F344" t="n">
+        <v>0.0002645290457344655</v>
+      </c>
+      <c r="G344" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>ipca_P55</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>0.4254132256423441</v>
+      </c>
+      <c r="C345" t="n">
+        <v>0.3895812363161286</v>
+      </c>
+      <c r="D345" t="n">
+        <v>0.03583198932621551</v>
+      </c>
+      <c r="E345" t="n">
+        <v>0.02877187029132745</v>
+      </c>
+      <c r="F345" t="n">
+        <v>0.001030953349174103</v>
+      </c>
+      <c r="G345" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>ipca_administrados</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>0.07556839549407418</v>
+      </c>
+      <c r="C346" t="n">
+        <v>0.4172332923303831</v>
+      </c>
+      <c r="D346" t="n">
+        <v>-0.341664896836309</v>
+      </c>
+      <c r="E346" t="n">
+        <v>0.0009227468858868619</v>
+      </c>
+      <c r="F346" t="n">
+        <v>-0.00031527021957256</v>
+      </c>
+      <c r="G346" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>ipca_alim_domicilio</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>0.1987814756189867</v>
+      </c>
+      <c r="C347" t="n">
+        <v>0.3447525795695772</v>
+      </c>
+      <c r="D347" t="n">
+        <v>-0.1459711039505905</v>
+      </c>
+      <c r="E347" t="n">
+        <v>0.0009866766391477492</v>
+      </c>
+      <c r="F347" t="n">
+        <v>-0.0001440262782586553</v>
+      </c>
+      <c r="G347" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>ipca_alimentacao</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>0.2927774211888935</v>
+      </c>
+      <c r="C348" t="n">
+        <v>0.3656738924759182</v>
+      </c>
+      <c r="D348" t="n">
+        <v>-0.07289647128702469</v>
+      </c>
+      <c r="E348" t="n">
+        <v>0.001116142776060021</v>
+      </c>
+      <c r="F348" t="n">
+        <v>-8.136286982727933e-05</v>
+      </c>
+      <c r="G348" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>ipca_difusao</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>0.6485572467709773</v>
+      </c>
+      <c r="C349" t="n">
+        <v>0.5172781069930474</v>
+      </c>
+      <c r="D349" t="n">
+        <v>0.1312791397779299</v>
+      </c>
+      <c r="E349" t="n">
+        <v>-1.344425098722241e-05</v>
+      </c>
+      <c r="F349" t="n">
+        <v>-1.764949704561143e-06</v>
+      </c>
+      <c r="G349" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>ipca_industriais</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>0.0693498936122684</v>
+      </c>
+      <c r="C350" t="n">
+        <v>0.2714043787524045</v>
+      </c>
+      <c r="D350" t="n">
+        <v>-0.2020544851401361</v>
+      </c>
+      <c r="E350" t="n">
+        <v>-0.006782501973311363</v>
+      </c>
+      <c r="F350" t="n">
+        <v>0.001370434944179384</v>
+      </c>
+      <c r="G350" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>ipca_industriais_subjacentes</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>0.2687025250315013</v>
+      </c>
+      <c r="C351" t="n">
+        <v>0.3432409998039667</v>
+      </c>
+      <c r="D351" t="n">
+        <v>-0.07453847477246543</v>
+      </c>
+      <c r="E351" t="n">
+        <v>-0.001494686616470563</v>
+      </c>
+      <c r="F351" t="n">
+        <v>0.0001114116606545328</v>
+      </c>
+      <c r="G351" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>ipca_livres</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>0.3010813186618921</v>
+      </c>
+      <c r="C352" t="n">
+        <v>0.3871819136509626</v>
+      </c>
+      <c r="D352" t="n">
+        <v>-0.08610059498907048</v>
+      </c>
+      <c r="E352" t="n">
+        <v>0.01096307467221383</v>
+      </c>
+      <c r="F352" t="n">
+        <v>-0.0009439272521872197</v>
+      </c>
+      <c r="G352" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>ipca_servicos</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>0.402727181780807</v>
+      </c>
+      <c r="C353" t="n">
+        <v>0.4820658330579079</v>
+      </c>
+      <c r="D353" t="n">
+        <v>-0.07933865127710088</v>
+      </c>
+      <c r="E353" t="n">
+        <v>0.01060948510968053</v>
+      </c>
+      <c r="F353" t="n">
+        <v>-0.0008417422393465382</v>
+      </c>
+      <c r="G353" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>ipca_servicos_subjacentes</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>0.3602466052582748</v>
+      </c>
+      <c r="C354" t="n">
+        <v>0.4239974757731144</v>
+      </c>
+      <c r="D354" t="n">
+        <v>-0.06375087051483957</v>
+      </c>
+      <c r="E354" t="n">
+        <v>0.004661614161938123</v>
+      </c>
+      <c r="F354" t="n">
+        <v>-0.0002971819608278597</v>
+      </c>
+      <c r="G354" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>0.0009189819755979767</v>
+      </c>
+      <c r="C355" t="n">
+        <v>0.3811403808937101</v>
+      </c>
+      <c r="D355" t="n">
+        <v>-0.3802213989181122</v>
+      </c>
+      <c r="E355" t="n">
+        <v>0.004346056295610567</v>
+      </c>
+      <c r="F355" t="n">
+        <v>-0.001652463604493918</v>
+      </c>
+      <c r="G355" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>-0.06135948185390028</v>
+      </c>
+      <c r="C356" t="n">
+        <v>-0.07227366542436833</v>
+      </c>
+      <c r="D356" t="n">
+        <v>0.01091418357046805</v>
+      </c>
+      <c r="E356" t="n">
+        <v>0.005665278901699565</v>
+      </c>
+      <c r="F356" t="n">
+        <v>6.183189391104867e-05</v>
+      </c>
+      <c r="G356" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>-0.02698732312331309</v>
+      </c>
+      <c r="C357" t="n">
+        <v>-0.1073260007029437</v>
+      </c>
+      <c r="D357" t="n">
+        <v>0.08033867757963063</v>
+      </c>
+      <c r="E357" t="n">
+        <v>-0.0001679287357520757</v>
+      </c>
+      <c r="F357" t="n">
+        <v>-1.3491172557941e-05</v>
+      </c>
+      <c r="G357" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H357" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>

--- a/pib_nowcast/data/impacts.xlsx
+++ b/pib_nowcast/data/impacts.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H357"/>
+  <dimension ref="A1:H590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10176,7 +10176,7 @@
       <c r="F325" t="n">
         <v>-0.001102100998603247</v>
       </c>
-      <c r="G325" s="2" t="n">
+      <c r="G325" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H325" t="inlineStr">
@@ -10206,7 +10206,7 @@
       <c r="F326" t="n">
         <v>-0.0006025634495145237</v>
       </c>
-      <c r="G326" s="2" t="n">
+      <c r="G326" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H326" t="inlineStr">
@@ -10236,7 +10236,7 @@
       <c r="F327" t="n">
         <v>0.001209827171820734</v>
       </c>
-      <c r="G327" s="2" t="n">
+      <c r="G327" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H327" t="inlineStr">
@@ -10266,7 +10266,7 @@
       <c r="F328" t="n">
         <v>0.002276633468233246</v>
       </c>
-      <c r="G328" s="2" t="n">
+      <c r="G328" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H328" t="inlineStr">
@@ -10296,7 +10296,7 @@
       <c r="F329" t="n">
         <v>0.0004959990771745761</v>
       </c>
-      <c r="G329" s="2" t="n">
+      <c r="G329" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H329" t="inlineStr">
@@ -10326,7 +10326,7 @@
       <c r="F330" t="n">
         <v>4.808896710095734e-05</v>
       </c>
-      <c r="G330" s="2" t="n">
+      <c r="G330" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H330" t="inlineStr">
@@ -10356,7 +10356,7 @@
       <c r="F331" t="n">
         <v>1.351007045802627e-05</v>
       </c>
-      <c r="G331" s="2" t="n">
+      <c r="G331" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H331" t="inlineStr">
@@ -10386,7 +10386,7 @@
       <c r="F332" t="n">
         <v>3.500438120489686e-07</v>
       </c>
-      <c r="G332" s="2" t="n">
+      <c r="G332" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H332" t="inlineStr">
@@ -10416,7 +10416,7 @@
       <c r="F333" t="n">
         <v>-9.355333145127898e-05</v>
       </c>
-      <c r="G333" s="2" t="n">
+      <c r="G333" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H333" t="inlineStr">
@@ -10446,7 +10446,7 @@
       <c r="F334" t="n">
         <v>-0.0001409177646662752</v>
       </c>
-      <c r="G334" s="2" t="n">
+      <c r="G334" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H334" t="inlineStr">
@@ -10476,7 +10476,7 @@
       <c r="F335" t="n">
         <v>0.0001506498319066422</v>
       </c>
-      <c r="G335" s="2" t="n">
+      <c r="G335" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H335" t="inlineStr">
@@ -10506,7 +10506,7 @@
       <c r="F336" t="n">
         <v>0.00508009462830249</v>
       </c>
-      <c r="G336" s="2" t="n">
+      <c r="G336" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H336" t="inlineStr">
@@ -10536,7 +10536,7 @@
       <c r="F337" t="n">
         <v>0.0001822324122758766</v>
       </c>
-      <c r="G337" s="2" t="n">
+      <c r="G337" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H337" t="inlineStr">
@@ -10566,7 +10566,7 @@
       <c r="F338" t="n">
         <v>0.004397186755131336</v>
       </c>
-      <c r="G338" s="2" t="n">
+      <c r="G338" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H338" t="inlineStr">
@@ -10596,7 +10596,7 @@
       <c r="F339" t="n">
         <v>-0.0007145404986544779</v>
       </c>
-      <c r="G339" s="2" t="n">
+      <c r="G339" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H339" t="inlineStr">
@@ -10626,7 +10626,7 @@
       <c r="F340" t="n">
         <v>-0.0006853452724001315</v>
       </c>
-      <c r="G340" s="2" t="n">
+      <c r="G340" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H340" t="inlineStr">
@@ -10656,7 +10656,7 @@
       <c r="F341" t="n">
         <v>-0.002432564987693606</v>
       </c>
-      <c r="G341" s="2" t="n">
+      <c r="G341" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H341" t="inlineStr">
@@ -10686,7 +10686,7 @@
       <c r="F342" t="n">
         <v>0.000437987513004461</v>
       </c>
-      <c r="G342" s="2" t="n">
+      <c r="G342" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H342" t="inlineStr">
@@ -10716,7 +10716,7 @@
       <c r="F343" t="n">
         <v>-0.0001188392841706176</v>
       </c>
-      <c r="G343" s="2" t="n">
+      <c r="G343" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H343" t="inlineStr">
@@ -10746,7 +10746,7 @@
       <c r="F344" t="n">
         <v>0.0002645290457344655</v>
       </c>
-      <c r="G344" s="2" t="n">
+      <c r="G344" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H344" t="inlineStr">
@@ -10776,7 +10776,7 @@
       <c r="F345" t="n">
         <v>0.001030953349174103</v>
       </c>
-      <c r="G345" s="2" t="n">
+      <c r="G345" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H345" t="inlineStr">
@@ -10806,7 +10806,7 @@
       <c r="F346" t="n">
         <v>-0.00031527021957256</v>
       </c>
-      <c r="G346" s="2" t="n">
+      <c r="G346" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H346" t="inlineStr">
@@ -10836,7 +10836,7 @@
       <c r="F347" t="n">
         <v>-0.0001440262782586553</v>
       </c>
-      <c r="G347" s="2" t="n">
+      <c r="G347" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H347" t="inlineStr">
@@ -10866,7 +10866,7 @@
       <c r="F348" t="n">
         <v>-8.136286982727933e-05</v>
       </c>
-      <c r="G348" s="2" t="n">
+      <c r="G348" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H348" t="inlineStr">
@@ -10896,7 +10896,7 @@
       <c r="F349" t="n">
         <v>-1.764949704561143e-06</v>
       </c>
-      <c r="G349" s="2" t="n">
+      <c r="G349" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H349" t="inlineStr">
@@ -10926,7 +10926,7 @@
       <c r="F350" t="n">
         <v>0.001370434944179384</v>
       </c>
-      <c r="G350" s="2" t="n">
+      <c r="G350" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H350" t="inlineStr">
@@ -10956,7 +10956,7 @@
       <c r="F351" t="n">
         <v>0.0001114116606545328</v>
       </c>
-      <c r="G351" s="2" t="n">
+      <c r="G351" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H351" t="inlineStr">
@@ -10986,7 +10986,7 @@
       <c r="F352" t="n">
         <v>-0.0009439272521872197</v>
       </c>
-      <c r="G352" s="2" t="n">
+      <c r="G352" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H352" t="inlineStr">
@@ -11016,7 +11016,7 @@
       <c r="F353" t="n">
         <v>-0.0008417422393465382</v>
       </c>
-      <c r="G353" s="2" t="n">
+      <c r="G353" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H353" t="inlineStr">
@@ -11046,7 +11046,7 @@
       <c r="F354" t="n">
         <v>-0.0002971819608278597</v>
       </c>
-      <c r="G354" s="2" t="n">
+      <c r="G354" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H354" t="inlineStr">
@@ -11076,7 +11076,7 @@
       <c r="F355" t="n">
         <v>-0.001652463604493918</v>
       </c>
-      <c r="G355" s="2" t="n">
+      <c r="G355" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H355" t="inlineStr">
@@ -11106,7 +11106,7 @@
       <c r="F356" t="n">
         <v>6.183189391104867e-05</v>
       </c>
-      <c r="G356" s="2" t="n">
+      <c r="G356" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H356" t="inlineStr">
@@ -11136,10 +11136,7000 @@
       <c r="F357" t="n">
         <v>-1.3491172557941e-05</v>
       </c>
-      <c r="G357" s="2" t="n">
+      <c r="G357" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="H357" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>cambio_media_mensal</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>-2.217400142430803</v>
+      </c>
+      <c r="C358" t="n">
+        <v>0.3548087956445402</v>
+      </c>
+      <c r="D358" t="n">
+        <v>-2.572208938075343</v>
+      </c>
+      <c r="E358" t="n">
+        <v>0.0004284648040403338</v>
+      </c>
+      <c r="F358" t="n">
+        <v>-0.001102100998603247</v>
+      </c>
+      <c r="G358" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>fenabrave_automoveis</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>-5.275650780846597</v>
+      </c>
+      <c r="C359" t="n">
+        <v>-3.897875774955659</v>
+      </c>
+      <c r="D359" t="n">
+        <v>-1.377775005890938</v>
+      </c>
+      <c r="E359" t="n">
+        <v>0.0004373453190384129</v>
+      </c>
+      <c r="F359" t="n">
+        <v>-0.0006025634495145237</v>
+      </c>
+      <c r="G359" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>fenabrave_caminhoes</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>-1.828347386793894</v>
+      </c>
+      <c r="C360" t="n">
+        <v>-5.732597302821642</v>
+      </c>
+      <c r="D360" t="n">
+        <v>3.904249916027748</v>
+      </c>
+      <c r="E360" t="n">
+        <v>0.0003098744183496411</v>
+      </c>
+      <c r="F360" t="n">
+        <v>0.001209827171820734</v>
+      </c>
+      <c r="G360" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>fenabrave_comerciais_leves</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>-0.3424365805175689</v>
+      </c>
+      <c r="C361" t="n">
+        <v>-3.992753537015551</v>
+      </c>
+      <c r="D361" t="n">
+        <v>3.650316956497981</v>
+      </c>
+      <c r="E361" t="n">
+        <v>0.0006236810379385214</v>
+      </c>
+      <c r="F361" t="n">
+        <v>0.002276633468233246</v>
+      </c>
+      <c r="G361" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>fenabrave_onibus</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>-4.153947786527201</v>
+      </c>
+      <c r="C362" t="n">
+        <v>-7.259966161496442</v>
+      </c>
+      <c r="D362" t="n">
+        <v>3.106018374969242</v>
+      </c>
+      <c r="E362" t="n">
+        <v>0.000159689678970263</v>
+      </c>
+      <c r="F362" t="n">
+        <v>0.0004959990771745761</v>
+      </c>
+      <c r="G362" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>fgv_nuci</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>-0.09999999999999433</v>
+      </c>
+      <c r="C363" t="n">
+        <v>0.02727619625955043</v>
+      </c>
+      <c r="D363" t="n">
+        <v>-0.1272761962595448</v>
+      </c>
+      <c r="E363" t="n">
+        <v>-0.0003778315860641618</v>
+      </c>
+      <c r="F363" t="n">
+        <v>4.808896710095734e-05</v>
+      </c>
+      <c r="G363" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>icbr_agro</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>0.6843143401802365</v>
+      </c>
+      <c r="C364" t="n">
+        <v>1.378511274677356</v>
+      </c>
+      <c r="D364" t="n">
+        <v>-0.6941969344971189</v>
+      </c>
+      <c r="E364" t="n">
+        <v>-1.946143779475642e-05</v>
+      </c>
+      <c r="F364" t="n">
+        <v>1.351007045802627e-05</v>
+      </c>
+      <c r="G364" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>icbr_energia</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>-0.2598010997918342</v>
+      </c>
+      <c r="C365" t="n">
+        <v>-0.214494894685726</v>
+      </c>
+      <c r="D365" t="n">
+        <v>-0.04530620510610813</v>
+      </c>
+      <c r="E365" t="n">
+        <v>-7.726178152179337e-06</v>
+      </c>
+      <c r="F365" t="n">
+        <v>3.500438120489686e-07</v>
+      </c>
+      <c r="G365" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>icbr_metal</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>2.221426097799162</v>
+      </c>
+      <c r="C366" t="n">
+        <v>1.188959394113492</v>
+      </c>
+      <c r="D366" t="n">
+        <v>1.032466703685669</v>
+      </c>
+      <c r="E366" t="n">
+        <v>-9.061147552489107e-05</v>
+      </c>
+      <c r="F366" t="n">
+        <v>-9.355333145127898e-05</v>
+      </c>
+      <c r="G366" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>0.02834541292932125</v>
+      </c>
+      <c r="C367" t="n">
+        <v>0.4905762295404892</v>
+      </c>
+      <c r="D367" t="n">
+        <v>-0.462230816611168</v>
+      </c>
+      <c r="E367" t="n">
+        <v>0.0003048644954038542</v>
+      </c>
+      <c r="F367" t="n">
+        <v>-0.0001409177646662752</v>
+      </c>
+      <c r="G367" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>-0.6322592568392276</v>
+      </c>
+      <c r="C368" t="n">
+        <v>0.6066351519410065</v>
+      </c>
+      <c r="D368" t="n">
+        <v>-1.238894408780234</v>
+      </c>
+      <c r="E368" t="n">
+        <v>-0.0001216002193883222</v>
+      </c>
+      <c r="F368" t="n">
+        <v>0.0001506498319066422</v>
+      </c>
+      <c r="G368" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>-0.3700623027681141</v>
+      </c>
+      <c r="C369" t="n">
+        <v>0.3689082581632018</v>
+      </c>
+      <c r="D369" t="n">
+        <v>-0.738970560931316</v>
+      </c>
+      <c r="E369" t="n">
+        <v>-0.006874556168922488</v>
+      </c>
+      <c r="F369" t="n">
+        <v>0.00508009462830249</v>
+      </c>
+      <c r="G369" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>0.4489387037604357</v>
+      </c>
+      <c r="C370" t="n">
+        <v>0.516304527026153</v>
+      </c>
+      <c r="D370" t="n">
+        <v>-0.06736582326571736</v>
+      </c>
+      <c r="E370" t="n">
+        <v>-0.002705116681452554</v>
+      </c>
+      <c r="F370" t="n">
+        <v>0.0001822324122758766</v>
+      </c>
+      <c r="G370" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>-0.6966185442159022</v>
+      </c>
+      <c r="C371" t="n">
+        <v>0.4366457683698114</v>
+      </c>
+      <c r="D371" t="n">
+        <v>-1.133264312585714</v>
+      </c>
+      <c r="E371" t="n">
+        <v>-0.003880106967366236</v>
+      </c>
+      <c r="F371" t="n">
+        <v>0.004397186755131336</v>
+      </c>
+      <c r="G371" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>0.2427188518995873</v>
+      </c>
+      <c r="C372" t="n">
+        <v>0.3699813608095837</v>
+      </c>
+      <c r="D372" t="n">
+        <v>-0.1272625089099964</v>
+      </c>
+      <c r="E372" t="n">
+        <v>0.005614697563127729</v>
+      </c>
+      <c r="F372" t="n">
+        <v>-0.0007145404986544779</v>
+      </c>
+      <c r="G372" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>0.3109432966846084</v>
+      </c>
+      <c r="C373" t="n">
+        <v>0.4078244114141327</v>
+      </c>
+      <c r="D373" t="n">
+        <v>-0.09688111472952429</v>
+      </c>
+      <c r="E373" t="n">
+        <v>0.007074085329359594</v>
+      </c>
+      <c r="F373" t="n">
+        <v>-0.0006853452724001315</v>
+      </c>
+      <c r="G373" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>ipca_DP</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>0.30432517773155</v>
+      </c>
+      <c r="C374" t="n">
+        <v>0.3859083034096225</v>
+      </c>
+      <c r="D374" t="n">
+        <v>-0.08158312567807251</v>
+      </c>
+      <c r="E374" t="n">
+        <v>0.02981701139145515</v>
+      </c>
+      <c r="F374" t="n">
+        <v>-0.002432564987693606</v>
+      </c>
+      <c r="G374" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>ipca_EX0</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>0.3985075622549502</v>
+      </c>
+      <c r="C375" t="n">
+        <v>0.3838681650576055</v>
+      </c>
+      <c r="D375" t="n">
+        <v>0.01463939719734472</v>
+      </c>
+      <c r="E375" t="n">
+        <v>0.02991841174197411</v>
+      </c>
+      <c r="F375" t="n">
+        <v>0.000437987513004461</v>
+      </c>
+      <c r="G375" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>ipca_EX3</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>0.358515394556541</v>
+      </c>
+      <c r="C376" t="n">
+        <v>0.3866351750928059</v>
+      </c>
+      <c r="D376" t="n">
+        <v>-0.02811978053626488</v>
+      </c>
+      <c r="E376" t="n">
+        <v>0.004226181069135857</v>
+      </c>
+      <c r="F376" t="n">
+        <v>-0.0001188392841706176</v>
+      </c>
+      <c r="G376" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>ipca_MS</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>0.3611275205637015</v>
+      </c>
+      <c r="C377" t="n">
+        <v>0.3644383573869729</v>
+      </c>
+      <c r="D377" t="n">
+        <v>-0.003310836823271392</v>
+      </c>
+      <c r="E377" t="n">
+        <v>-0.07989794117158817</v>
+      </c>
+      <c r="F377" t="n">
+        <v>0.0002645290457344655</v>
+      </c>
+      <c r="G377" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>ipca_P55</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>0.4254132256423441</v>
+      </c>
+      <c r="C378" t="n">
+        <v>0.3895812363161286</v>
+      </c>
+      <c r="D378" t="n">
+        <v>0.03583198932621551</v>
+      </c>
+      <c r="E378" t="n">
+        <v>0.02877187029132745</v>
+      </c>
+      <c r="F378" t="n">
+        <v>0.001030953349174103</v>
+      </c>
+      <c r="G378" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>ipca_administrados</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>0.07556839549407418</v>
+      </c>
+      <c r="C379" t="n">
+        <v>0.4172332923303831</v>
+      </c>
+      <c r="D379" t="n">
+        <v>-0.341664896836309</v>
+      </c>
+      <c r="E379" t="n">
+        <v>0.0009227468858868619</v>
+      </c>
+      <c r="F379" t="n">
+        <v>-0.00031527021957256</v>
+      </c>
+      <c r="G379" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>ipca_alim_domicilio</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>0.1987814756189867</v>
+      </c>
+      <c r="C380" t="n">
+        <v>0.3447525795695772</v>
+      </c>
+      <c r="D380" t="n">
+        <v>-0.1459711039505905</v>
+      </c>
+      <c r="E380" t="n">
+        <v>0.0009866766391477492</v>
+      </c>
+      <c r="F380" t="n">
+        <v>-0.0001440262782586553</v>
+      </c>
+      <c r="G380" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>ipca_alimentacao</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>0.2927774211888935</v>
+      </c>
+      <c r="C381" t="n">
+        <v>0.3656738924759182</v>
+      </c>
+      <c r="D381" t="n">
+        <v>-0.07289647128702469</v>
+      </c>
+      <c r="E381" t="n">
+        <v>0.001116142776060021</v>
+      </c>
+      <c r="F381" t="n">
+        <v>-8.136286982727933e-05</v>
+      </c>
+      <c r="G381" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>ipca_difusao</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>0.6485572467709773</v>
+      </c>
+      <c r="C382" t="n">
+        <v>0.5172781069930474</v>
+      </c>
+      <c r="D382" t="n">
+        <v>0.1312791397779299</v>
+      </c>
+      <c r="E382" t="n">
+        <v>-1.344425098722241e-05</v>
+      </c>
+      <c r="F382" t="n">
+        <v>-1.764949704561143e-06</v>
+      </c>
+      <c r="G382" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>ipca_industriais</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>0.0693498936122684</v>
+      </c>
+      <c r="C383" t="n">
+        <v>0.2714043787524045</v>
+      </c>
+      <c r="D383" t="n">
+        <v>-0.2020544851401361</v>
+      </c>
+      <c r="E383" t="n">
+        <v>-0.006782501973311363</v>
+      </c>
+      <c r="F383" t="n">
+        <v>0.001370434944179384</v>
+      </c>
+      <c r="G383" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>ipca_industriais_subjacentes</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>0.2687025250315013</v>
+      </c>
+      <c r="C384" t="n">
+        <v>0.3432409998039667</v>
+      </c>
+      <c r="D384" t="n">
+        <v>-0.07453847477246543</v>
+      </c>
+      <c r="E384" t="n">
+        <v>-0.001494686616470563</v>
+      </c>
+      <c r="F384" t="n">
+        <v>0.0001114116606545328</v>
+      </c>
+      <c r="G384" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>ipca_livres</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>0.3010813186618921</v>
+      </c>
+      <c r="C385" t="n">
+        <v>0.3871819136509626</v>
+      </c>
+      <c r="D385" t="n">
+        <v>-0.08610059498907048</v>
+      </c>
+      <c r="E385" t="n">
+        <v>0.01096307467221383</v>
+      </c>
+      <c r="F385" t="n">
+        <v>-0.0009439272521872197</v>
+      </c>
+      <c r="G385" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>ipca_servicos</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>0.402727181780807</v>
+      </c>
+      <c r="C386" t="n">
+        <v>0.4820658330579079</v>
+      </c>
+      <c r="D386" t="n">
+        <v>-0.07933865127710088</v>
+      </c>
+      <c r="E386" t="n">
+        <v>0.01060948510968053</v>
+      </c>
+      <c r="F386" t="n">
+        <v>-0.0008417422393465382</v>
+      </c>
+      <c r="G386" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>ipca_servicos_subjacentes</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>0.3602466052582748</v>
+      </c>
+      <c r="C387" t="n">
+        <v>0.4239974757731144</v>
+      </c>
+      <c r="D387" t="n">
+        <v>-0.06375087051483957</v>
+      </c>
+      <c r="E387" t="n">
+        <v>0.004661614161938123</v>
+      </c>
+      <c r="F387" t="n">
+        <v>-0.0002971819608278597</v>
+      </c>
+      <c r="G387" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>0.0009189819755979767</v>
+      </c>
+      <c r="C388" t="n">
+        <v>0.3811403808937101</v>
+      </c>
+      <c r="D388" t="n">
+        <v>-0.3802213989181122</v>
+      </c>
+      <c r="E388" t="n">
+        <v>0.004346056295610567</v>
+      </c>
+      <c r="F388" t="n">
+        <v>-0.001652463604493918</v>
+      </c>
+      <c r="G388" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>-0.06135948185390028</v>
+      </c>
+      <c r="C389" t="n">
+        <v>-0.07227366542436833</v>
+      </c>
+      <c r="D389" t="n">
+        <v>0.01091418357046805</v>
+      </c>
+      <c r="E389" t="n">
+        <v>0.005665278901699565</v>
+      </c>
+      <c r="F389" t="n">
+        <v>6.183189391104867e-05</v>
+      </c>
+      <c r="G389" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>-0.02698732312331309</v>
+      </c>
+      <c r="C390" t="n">
+        <v>-0.1073260007029437</v>
+      </c>
+      <c r="D390" t="n">
+        <v>0.08033867757963063</v>
+      </c>
+      <c r="E390" t="n">
+        <v>-0.0001679287357520757</v>
+      </c>
+      <c r="F390" t="n">
+        <v>-1.3491172557941e-05</v>
+      </c>
+      <c r="G390" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="C391" t="n">
+        <v>-0.9724185198327511</v>
+      </c>
+      <c r="D391" t="n">
+        <v>-0.5675814801672489</v>
+      </c>
+      <c r="E391" t="n">
+        <v>-7.80264612854188e-09</v>
+      </c>
+      <c r="F391" t="n">
+        <v>4.428637438859054e-09</v>
+      </c>
+      <c r="G391" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>cambio_media_mensal</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>-12.14242014687221</v>
+      </c>
+      <c r="C392" t="n">
+        <v>-10.77128018802637</v>
+      </c>
+      <c r="D392" t="n">
+        <v>-1.371139958845842</v>
+      </c>
+      <c r="E392" t="n">
+        <v>-0.0001355418928999605</v>
+      </c>
+      <c r="F392" t="n">
+        <v>0.0001858469054527394</v>
+      </c>
+      <c r="G392" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>fenabrave_automoveis</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>15.71257642366568</v>
+      </c>
+      <c r="C393" t="n">
+        <v>14.48165278444639</v>
+      </c>
+      <c r="D393" t="n">
+        <v>1.230923639219287</v>
+      </c>
+      <c r="E393" t="n">
+        <v>0.0002893030521887114</v>
+      </c>
+      <c r="F393" t="n">
+        <v>0.0003561099658373758</v>
+      </c>
+      <c r="G393" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>fenabrave_caminhoes</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>6.878866482910517</v>
+      </c>
+      <c r="C394" t="n">
+        <v>7.713513317455304</v>
+      </c>
+      <c r="D394" t="n">
+        <v>-0.8346468345447863</v>
+      </c>
+      <c r="E394" t="n">
+        <v>0.0004021543010334682</v>
+      </c>
+      <c r="F394" t="n">
+        <v>-0.0003356568143561553</v>
+      </c>
+      <c r="G394" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>fenabrave_comerciais_leves</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>9.436541455345804</v>
+      </c>
+      <c r="C395" t="n">
+        <v>6.628878703820174</v>
+      </c>
+      <c r="D395" t="n">
+        <v>2.807662751525628</v>
+      </c>
+      <c r="E395" t="n">
+        <v>0.0002935126679408413</v>
+      </c>
+      <c r="F395" t="n">
+        <v>0.0008240845848784105</v>
+      </c>
+      <c r="G395" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>fenabrave_onibus</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>-2.314152856169382</v>
+      </c>
+      <c r="C396" t="n">
+        <v>5.205192413578368</v>
+      </c>
+      <c r="D396" t="n">
+        <v>-7.51934526974775</v>
+      </c>
+      <c r="E396" t="n">
+        <v>0.0001699107012219573</v>
+      </c>
+      <c r="F396" t="n">
+        <v>-0.001277617227512848</v>
+      </c>
+      <c r="G396" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>fgv_nuci</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>0.7000000000000028</v>
+      </c>
+      <c r="C397" t="n">
+        <v>-0.4508532433345457</v>
+      </c>
+      <c r="D397" t="n">
+        <v>1.150853243334549</v>
+      </c>
+      <c r="E397" t="n">
+        <v>0.002893592696530848</v>
+      </c>
+      <c r="F397" t="n">
+        <v>0.003330100539691689</v>
+      </c>
+      <c r="G397" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>icbr_agro</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>-5.851692715816004</v>
+      </c>
+      <c r="C398" t="n">
+        <v>-4.899512352272755</v>
+      </c>
+      <c r="D398" t="n">
+        <v>-0.9521803635432483</v>
+      </c>
+      <c r="E398" t="n">
+        <v>-0.0001108705281821039</v>
+      </c>
+      <c r="F398" t="n">
+        <v>0.0001055687398306677</v>
+      </c>
+      <c r="G398" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>icbr_energia</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>1.370397764392717</v>
+      </c>
+      <c r="C399" t="n">
+        <v>3.942674648725695</v>
+      </c>
+      <c r="D399" t="n">
+        <v>-2.572276884332978</v>
+      </c>
+      <c r="E399" t="n">
+        <v>-3.48266580356842e-05</v>
+      </c>
+      <c r="F399" t="n">
+        <v>8.958380742375984e-05</v>
+      </c>
+      <c r="G399" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>icbr_metal</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>27.04099090050098</v>
+      </c>
+      <c r="C400" t="n">
+        <v>33.18369903088132</v>
+      </c>
+      <c r="D400" t="n">
+        <v>-6.142708130380337</v>
+      </c>
+      <c r="E400" t="n">
+        <v>-0.0001034139356430563</v>
+      </c>
+      <c r="F400" t="n">
+        <v>0.000635241623269231</v>
+      </c>
+      <c r="G400" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="C401" t="n">
+        <v>0.3907900226964168</v>
+      </c>
+      <c r="D401" t="n">
+        <v>0.1292099773035831</v>
+      </c>
+      <c r="E401" t="n">
+        <v>-4.174075314554467e-05</v>
+      </c>
+      <c r="F401" t="n">
+        <v>-5.393321766570293e-06</v>
+      </c>
+      <c r="G401" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="C402" t="n">
+        <v>0.635181832930295</v>
+      </c>
+      <c r="D402" t="n">
+        <v>-1.425181832930295</v>
+      </c>
+      <c r="E402" t="n">
+        <v>-9.919765456205147e-05</v>
+      </c>
+      <c r="F402" t="n">
+        <v>0.0001413746951511308</v>
+      </c>
+      <c r="G402" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>-0.3899999999999999</v>
+      </c>
+      <c r="C403" t="n">
+        <v>0.7821767943069146</v>
+      </c>
+      <c r="D403" t="n">
+        <v>-1.172176794306915</v>
+      </c>
+      <c r="E403" t="n">
+        <v>-0.0001333486905126099</v>
+      </c>
+      <c r="F403" t="n">
+        <v>0.0001563082405700959</v>
+      </c>
+      <c r="G403" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C404" t="n">
+        <v>-0.01028215907283622</v>
+      </c>
+      <c r="D404" t="n">
+        <v>-0.2897178409271638</v>
+      </c>
+      <c r="E404" t="n">
+        <v>0.002810798340210516</v>
+      </c>
+      <c r="F404" t="n">
+        <v>-0.0008143384264074463</v>
+      </c>
+      <c r="G404" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="C405" t="n">
+        <v>1.048312271607374</v>
+      </c>
+      <c r="D405" t="n">
+        <v>-1.498312271607374</v>
+      </c>
+      <c r="E405" t="n">
+        <v>-0.0001088225903079212</v>
+      </c>
+      <c r="F405" t="n">
+        <v>0.0001630502224864599</v>
+      </c>
+      <c r="G405" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>-0.3100000000000001</v>
+      </c>
+      <c r="C406" t="n">
+        <v>0.0861741846726664</v>
+      </c>
+      <c r="D406" t="n">
+        <v>-0.3961741846726664</v>
+      </c>
+      <c r="E406" t="n">
+        <v>-0.001693353142450953</v>
+      </c>
+      <c r="F406" t="n">
+        <v>0.0006708628005734039</v>
+      </c>
+      <c r="G406" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="C407" t="n">
+        <v>0.04918751907907689</v>
+      </c>
+      <c r="D407" t="n">
+        <v>-0.3191875190790769</v>
+      </c>
+      <c r="E407" t="n">
+        <v>0.0008059316352146703</v>
+      </c>
+      <c r="F407" t="n">
+        <v>-0.0002572433191915142</v>
+      </c>
+      <c r="G407" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>ipca_DP</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>-0.07999999999999999</v>
+      </c>
+      <c r="C408" t="n">
+        <v>-0.01378207364241075</v>
+      </c>
+      <c r="D408" t="n">
+        <v>-0.06621792635758925</v>
+      </c>
+      <c r="E408" t="n">
+        <v>-0.004008494789329963</v>
+      </c>
+      <c r="F408" t="n">
+        <v>0.0002654342127646317</v>
+      </c>
+      <c r="G408" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>ipca_EX0</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="C409" t="n">
+        <v>-0.001318159459046594</v>
+      </c>
+      <c r="D409" t="n">
+        <v>-0.03868184054095344</v>
+      </c>
+      <c r="E409" t="n">
+        <v>0.006182748720082151</v>
+      </c>
+      <c r="F409" t="n">
+        <v>-0.0002391601000950018</v>
+      </c>
+      <c r="G409" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>ipca_EX3</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="C410" t="n">
+        <v>-0.007151668349970839</v>
+      </c>
+      <c r="D410" t="n">
+        <v>-0.05284833165002915</v>
+      </c>
+      <c r="E410" t="n">
+        <v>0.007760053255621715</v>
+      </c>
+      <c r="F410" t="n">
+        <v>-0.0004101058680749849</v>
+      </c>
+      <c r="G410" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>ipca_MS</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>0.01999999999999997</v>
+      </c>
+      <c r="C411" t="n">
+        <v>-0.09127606238402816</v>
+      </c>
+      <c r="D411" t="n">
+        <v>0.1112760623840281</v>
+      </c>
+      <c r="E411" t="n">
+        <v>-0.004165999026365146</v>
+      </c>
+      <c r="F411" t="n">
+        <v>-0.0004635759675496084</v>
+      </c>
+      <c r="G411" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>ipca_P55</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C412" t="n">
+        <v>0.005068465824590696</v>
+      </c>
+      <c r="D412" t="n">
+        <v>0.09493153417540932</v>
+      </c>
+      <c r="E412" t="n">
+        <v>0.003219351962379864</v>
+      </c>
+      <c r="F412" t="n">
+        <v>0.0003056180208393351</v>
+      </c>
+      <c r="G412" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>ipca_administrados</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="C413" t="n">
+        <v>-0.07445660545946073</v>
+      </c>
+      <c r="D413" t="n">
+        <v>-0.3255433945405393</v>
+      </c>
+      <c r="E413" t="n">
+        <v>-0.0001944644372664417</v>
+      </c>
+      <c r="F413" t="n">
+        <v>6.33066130251332e-05</v>
+      </c>
+      <c r="G413" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>ipca_alim_domicilio</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>-0.4499999999999999</v>
+      </c>
+      <c r="C414" t="n">
+        <v>0.08246597912822075</v>
+      </c>
+      <c r="D414" t="n">
+        <v>-0.5324659791282207</v>
+      </c>
+      <c r="E414" t="n">
+        <v>-0.0006082426075162642</v>
+      </c>
+      <c r="F414" t="n">
+        <v>0.0003238684955586497</v>
+      </c>
+      <c r="G414" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>ipca_alimentacao</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="C415" t="n">
+        <v>0.001550586946542669</v>
+      </c>
+      <c r="D415" t="n">
+        <v>-0.4015505869465427</v>
+      </c>
+      <c r="E415" t="n">
+        <v>-0.0006786155359945773</v>
+      </c>
+      <c r="F415" t="n">
+        <v>0.0002724984667896652</v>
+      </c>
+      <c r="G415" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>ipca_difusao</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>0</v>
+      </c>
+      <c r="C416" t="n">
+        <v>0.2018982901409984</v>
+      </c>
+      <c r="D416" t="n">
+        <v>-0.2018982901409984</v>
+      </c>
+      <c r="E416" t="n">
+        <v>-3.293956433159957e-05</v>
+      </c>
+      <c r="F416" t="n">
+        <v>6.650441716539371e-06</v>
+      </c>
+      <c r="G416" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>ipca_industriais</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>-0.06000000000000001</v>
+      </c>
+      <c r="C417" t="n">
+        <v>0.00316714947530033</v>
+      </c>
+      <c r="D417" t="n">
+        <v>-0.06316714947530033</v>
+      </c>
+      <c r="E417" t="n">
+        <v>0.000327208566699589</v>
+      </c>
+      <c r="F417" t="n">
+        <v>-2.066883244231172e-05</v>
+      </c>
+      <c r="G417" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>ipca_industriais_subjacentes</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="C418" t="n">
+        <v>0.03655183955408033</v>
+      </c>
+      <c r="D418" t="n">
+        <v>-0.1065518395540803</v>
+      </c>
+      <c r="E418" t="n">
+        <v>0.0005506240253079245</v>
+      </c>
+      <c r="F418" t="n">
+        <v>-5.867000279923185e-05</v>
+      </c>
+      <c r="G418" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>ipca_livres</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="C419" t="n">
+        <v>0.01584670319481888</v>
+      </c>
+      <c r="D419" t="n">
+        <v>-0.1458467031948189</v>
+      </c>
+      <c r="E419" t="n">
+        <v>-0.001574369864122747</v>
+      </c>
+      <c r="F419" t="n">
+        <v>0.0002296166542915777</v>
+      </c>
+      <c r="G419" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>ipca_servicos</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>-0.04999999999999993</v>
+      </c>
+      <c r="C420" t="n">
+        <v>0.01849980791025936</v>
+      </c>
+      <c r="D420" t="n">
+        <v>-0.06849980791025929</v>
+      </c>
+      <c r="E420" t="n">
+        <v>0.005195603914628139</v>
+      </c>
+      <c r="F420" t="n">
+        <v>-0.0003558978701298188</v>
+      </c>
+      <c r="G420" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>ipca_servicos_subjacentes</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="C421" t="n">
+        <v>-0.02127527769291695</v>
+      </c>
+      <c r="D421" t="n">
+        <v>-0.04872472230708307</v>
+      </c>
+      <c r="E421" t="n">
+        <v>0.01190688163279596</v>
+      </c>
+      <c r="F421" t="n">
+        <v>-0.000580159501101291</v>
+      </c>
+      <c r="G421" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="C422" t="n">
+        <v>0.03945442582688249</v>
+      </c>
+      <c r="D422" t="n">
+        <v>-0.4894544258268825</v>
+      </c>
+      <c r="E422" t="n">
+        <v>-0.0004336432442776609</v>
+      </c>
+      <c r="F422" t="n">
+        <v>0.0002122486051416291</v>
+      </c>
+      <c r="G422" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="C423" t="n">
+        <v>-0.5878529932479718</v>
+      </c>
+      <c r="D423" t="n">
+        <v>-0.1621470067520282</v>
+      </c>
+      <c r="E423" t="n">
+        <v>0.0002599272437744061</v>
+      </c>
+      <c r="F423" t="n">
+        <v>-4.21464245513247e-05</v>
+      </c>
+      <c r="G423" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>-0.9100000000000001</v>
+      </c>
+      <c r="C424" t="n">
+        <v>-0.7459131854555494</v>
+      </c>
+      <c r="D424" t="n">
+        <v>-0.1640868145444508</v>
+      </c>
+      <c r="E424" t="n">
+        <v>0.001555621144165632</v>
+      </c>
+      <c r="F424" t="n">
+        <v>-0.0002552569181841324</v>
+      </c>
+      <c r="G424" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>cambio_media_mensal</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>-2.217400142430803</v>
+      </c>
+      <c r="C425" t="n">
+        <v>0.3577858527026068</v>
+      </c>
+      <c r="D425" t="n">
+        <v>-2.57518599513341</v>
+      </c>
+      <c r="E425" t="n">
+        <v>0.0004554752475663253</v>
+      </c>
+      <c r="F425" t="n">
+        <v>-0.001172933478662724</v>
+      </c>
+      <c r="G425" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>fenabrave_automoveis</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>-5.275650780846597</v>
+      </c>
+      <c r="C426" t="n">
+        <v>-3.731053948521765</v>
+      </c>
+      <c r="D426" t="n">
+        <v>-1.544596832324832</v>
+      </c>
+      <c r="E426" t="n">
+        <v>0.0003954107141033342</v>
+      </c>
+      <c r="F426" t="n">
+        <v>-0.0006107501364713097</v>
+      </c>
+      <c r="G426" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>fenabrave_caminhoes</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>-1.828347386793894</v>
+      </c>
+      <c r="C427" t="n">
+        <v>-5.552876625613468</v>
+      </c>
+      <c r="D427" t="n">
+        <v>3.724529238819574</v>
+      </c>
+      <c r="E427" t="n">
+        <v>0.00027744565748276</v>
+      </c>
+      <c r="F427" t="n">
+        <v>0.00103335446347806</v>
+      </c>
+      <c r="G427" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>fenabrave_comerciais_leves</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>-0.3424365805175689</v>
+      </c>
+      <c r="C428" t="n">
+        <v>-3.782215170838191</v>
+      </c>
+      <c r="D428" t="n">
+        <v>3.439778590320622</v>
+      </c>
+      <c r="E428" t="n">
+        <v>0.0005872281134158546</v>
+      </c>
+      <c r="F428" t="n">
+        <v>0.002019934692162227</v>
+      </c>
+      <c r="G428" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>fenabrave_onibus</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>-4.153947786527201</v>
+      </c>
+      <c r="C429" t="n">
+        <v>-6.942783251439161</v>
+      </c>
+      <c r="D429" t="n">
+        <v>2.788835464911959</v>
+      </c>
+      <c r="E429" t="n">
+        <v>0.000147249383661064</v>
+      </c>
+      <c r="F429" t="n">
+        <v>0.000410654303340403</v>
+      </c>
+      <c r="G429" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>fgv_nuci</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>-0.09999999999999433</v>
+      </c>
+      <c r="C430" t="n">
+        <v>0.03783713475978258</v>
+      </c>
+      <c r="D430" t="n">
+        <v>-0.1378371347597769</v>
+      </c>
+      <c r="E430" t="n">
+        <v>-0.0006679122515123653</v>
+      </c>
+      <c r="F430" t="n">
+        <v>9.20631110194159e-05</v>
+      </c>
+      <c r="G430" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>icbr_agro</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>0.6843143401802365</v>
+      </c>
+      <c r="C431" t="n">
+        <v>1.377151035174295</v>
+      </c>
+      <c r="D431" t="n">
+        <v>-0.6928366949940583</v>
+      </c>
+      <c r="E431" t="n">
+        <v>-1.021024187666553e-05</v>
+      </c>
+      <c r="F431" t="n">
+        <v>7.074030236918878e-06</v>
+      </c>
+      <c r="G431" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>icbr_energia</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>-0.2598010997918342</v>
+      </c>
+      <c r="C432" t="n">
+        <v>-0.2208427289265565</v>
+      </c>
+      <c r="D432" t="n">
+        <v>-0.03895837086527758</v>
+      </c>
+      <c r="E432" t="n">
+        <v>-6.426623688629339e-06</v>
+      </c>
+      <c r="F432" t="n">
+        <v>2.503707890732e-07</v>
+      </c>
+      <c r="G432" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>icbr_metal</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>2.221426097799162</v>
+      </c>
+      <c r="C433" t="n">
+        <v>1.194921683195299</v>
+      </c>
+      <c r="D433" t="n">
+        <v>1.026504414603862</v>
+      </c>
+      <c r="E433" t="n">
+        <v>-7.905060052685692e-05</v>
+      </c>
+      <c r="F433" t="n">
+        <v>-8.114579041790502e-05</v>
+      </c>
+      <c r="G433" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>0.02834541292932125</v>
+      </c>
+      <c r="C434" t="n">
+        <v>0.4869422766517838</v>
+      </c>
+      <c r="D434" t="n">
+        <v>-0.4585968637224625</v>
+      </c>
+      <c r="E434" t="n">
+        <v>0.0005327246799222483</v>
+      </c>
+      <c r="F434" t="n">
+        <v>-0.0002443058674398958</v>
+      </c>
+      <c r="G434" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>-0.6322592568392276</v>
+      </c>
+      <c r="C435" t="n">
+        <v>0.6053547195929374</v>
+      </c>
+      <c r="D435" t="n">
+        <v>-1.237613976432165</v>
+      </c>
+      <c r="E435" t="n">
+        <v>-0.0002507044443189165</v>
+      </c>
+      <c r="F435" t="n">
+        <v>0.0003102753242427506</v>
+      </c>
+      <c r="G435" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>-0.3700623027681141</v>
+      </c>
+      <c r="C436" t="n">
+        <v>0.3665553221809525</v>
+      </c>
+      <c r="D436" t="n">
+        <v>-0.7366176249490667</v>
+      </c>
+      <c r="E436" t="n">
+        <v>-0.009098973822547585</v>
+      </c>
+      <c r="F436" t="n">
+        <v>0.006702464486638733</v>
+      </c>
+      <c r="G436" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>0.4489387037604357</v>
+      </c>
+      <c r="C437" t="n">
+        <v>0.5157173956020883</v>
+      </c>
+      <c r="D437" t="n">
+        <v>-0.06677869184165258</v>
+      </c>
+      <c r="E437" t="n">
+        <v>-0.002955155886294499</v>
+      </c>
+      <c r="F437" t="n">
+        <v>0.0001973414442749061</v>
+      </c>
+      <c r="G437" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>-0.6966185442159022</v>
+      </c>
+      <c r="C438" t="n">
+        <v>0.4336541393271561</v>
+      </c>
+      <c r="D438" t="n">
+        <v>-1.130272683543058</v>
+      </c>
+      <c r="E438" t="n">
+        <v>-0.002548057553547368</v>
+      </c>
+      <c r="F438" t="n">
+        <v>0.002879999848870143</v>
+      </c>
+      <c r="G438" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>0.2427188518995873</v>
+      </c>
+      <c r="C439" t="n">
+        <v>0.3705787020290924</v>
+      </c>
+      <c r="D439" t="n">
+        <v>-0.1278598501295051</v>
+      </c>
+      <c r="E439" t="n">
+        <v>0.005786306215647553</v>
+      </c>
+      <c r="F439" t="n">
+        <v>-0.0007398362455361201</v>
+      </c>
+      <c r="G439" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>0.3109432966846084</v>
+      </c>
+      <c r="C440" t="n">
+        <v>0.4080926360139059</v>
+      </c>
+      <c r="D440" t="n">
+        <v>-0.09714933932929749</v>
+      </c>
+      <c r="E440" t="n">
+        <v>0.006832911389319718</v>
+      </c>
+      <c r="F440" t="n">
+        <v>-0.0006638128271680428</v>
+      </c>
+      <c r="G440" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>ipca_DP</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>0.30432517773155</v>
+      </c>
+      <c r="C441" t="n">
+        <v>0.3866239108446666</v>
+      </c>
+      <c r="D441" t="n">
+        <v>-0.08229873311311667</v>
+      </c>
+      <c r="E441" t="n">
+        <v>0.02910814785510695</v>
+      </c>
+      <c r="F441" t="n">
+        <v>-0.002395563691744586</v>
+      </c>
+      <c r="G441" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>ipca_EX0</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>0.3985075622549502</v>
+      </c>
+      <c r="C442" t="n">
+        <v>0.3852793536004601</v>
+      </c>
+      <c r="D442" t="n">
+        <v>0.01322820865449012</v>
+      </c>
+      <c r="E442" t="n">
+        <v>0.02995727947461505</v>
+      </c>
+      <c r="F442" t="n">
+        <v>0.000396281143611082</v>
+      </c>
+      <c r="G442" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>ipca_EX3</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>0.358515394556541</v>
+      </c>
+      <c r="C443" t="n">
+        <v>0.3876752617953985</v>
+      </c>
+      <c r="D443" t="n">
+        <v>-0.02915986723885743</v>
+      </c>
+      <c r="E443" t="n">
+        <v>0.00395925161688946</v>
+      </c>
+      <c r="F443" t="n">
+        <v>-0.0001154512515137283</v>
+      </c>
+      <c r="G443" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>ipca_MS</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>0.3611275205637015</v>
+      </c>
+      <c r="C444" t="n">
+        <v>0.364913320962533</v>
+      </c>
+      <c r="D444" t="n">
+        <v>-0.003785800398831504</v>
+      </c>
+      <c r="E444" t="n">
+        <v>-0.07993077649692548</v>
+      </c>
+      <c r="F444" t="n">
+        <v>0.0003026019655409723</v>
+      </c>
+      <c r="G444" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>ipca_P55</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>0.4254132256423441</v>
+      </c>
+      <c r="C445" t="n">
+        <v>0.3903237986218056</v>
+      </c>
+      <c r="D445" t="n">
+        <v>0.0350894270205385</v>
+      </c>
+      <c r="E445" t="n">
+        <v>0.02811129565045709</v>
+      </c>
+      <c r="F445" t="n">
+        <v>0.0009864092571794955</v>
+      </c>
+      <c r="G445" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>ipca_administrados</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>0.07556839549407418</v>
+      </c>
+      <c r="C446" t="n">
+        <v>0.4172321209683663</v>
+      </c>
+      <c r="D446" t="n">
+        <v>-0.341663725474292</v>
+      </c>
+      <c r="E446" t="n">
+        <v>0.0008800396556739457</v>
+      </c>
+      <c r="F446" t="n">
+        <v>-0.0003006776273226735</v>
+      </c>
+      <c r="G446" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>ipca_alim_domicilio</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>0.1987814756189867</v>
+      </c>
+      <c r="C447" t="n">
+        <v>0.3449558768455182</v>
+      </c>
+      <c r="D447" t="n">
+        <v>-0.1461744012265315</v>
+      </c>
+      <c r="E447" t="n">
+        <v>0.001124948511873864</v>
+      </c>
+      <c r="F447" t="n">
+        <v>-0.0001644386751338397</v>
+      </c>
+      <c r="G447" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>ipca_alimentacao</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>0.2927774211888935</v>
+      </c>
+      <c r="C448" t="n">
+        <v>0.3659794121318628</v>
+      </c>
+      <c r="D448" t="n">
+        <v>-0.07320199094296932</v>
+      </c>
+      <c r="E448" t="n">
+        <v>0.001333100258709167</v>
+      </c>
+      <c r="F448" t="n">
+        <v>-9.758559306409852e-05</v>
+      </c>
+      <c r="G448" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>ipca_difusao</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>0.6485572467709773</v>
+      </c>
+      <c r="C449" t="n">
+        <v>0.5202121472263557</v>
+      </c>
+      <c r="D449" t="n">
+        <v>0.1283450995446217</v>
+      </c>
+      <c r="E449" t="n">
+        <v>-1.324693597063737e-05</v>
+      </c>
+      <c r="F449" t="n">
+        <v>-1.700179315812684e-06</v>
+      </c>
+      <c r="G449" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>ipca_industriais</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>0.0693498936122684</v>
+      </c>
+      <c r="C450" t="n">
+        <v>0.2720210461020802</v>
+      </c>
+      <c r="D450" t="n">
+        <v>-0.2026711524898118</v>
+      </c>
+      <c r="E450" t="n">
+        <v>-0.006683692811419758</v>
+      </c>
+      <c r="F450" t="n">
+        <v>0.001354591724978313</v>
+      </c>
+      <c r="G450" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>ipca_industriais_subjacentes</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>0.2687025250315013</v>
+      </c>
+      <c r="C451" t="n">
+        <v>0.3441464977168015</v>
+      </c>
+      <c r="D451" t="n">
+        <v>-0.07544397268530023</v>
+      </c>
+      <c r="E451" t="n">
+        <v>-0.001498194924163373</v>
+      </c>
+      <c r="F451" t="n">
+        <v>0.000113029776935837</v>
+      </c>
+      <c r="G451" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>ipca_livres</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>0.3010813186618921</v>
+      </c>
+      <c r="C452" t="n">
+        <v>0.3881523349178451</v>
+      </c>
+      <c r="D452" t="n">
+        <v>-0.08707101625595304</v>
+      </c>
+      <c r="E452" t="n">
+        <v>0.01154118596517738</v>
+      </c>
+      <c r="F452" t="n">
+        <v>-0.001004902790786936</v>
+      </c>
+      <c r="G452" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>ipca_servicos</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>0.402727181780807</v>
+      </c>
+      <c r="C453" t="n">
+        <v>0.4829318815356064</v>
+      </c>
+      <c r="D453" t="n">
+        <v>-0.08020469975479937</v>
+      </c>
+      <c r="E453" t="n">
+        <v>0.01079855593312194</v>
+      </c>
+      <c r="F453" t="n">
+        <v>-0.0008660949364014528</v>
+      </c>
+      <c r="G453" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>ipca_servicos_subjacentes</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>0.3602466052582748</v>
+      </c>
+      <c r="C454" t="n">
+        <v>0.4248783337177655</v>
+      </c>
+      <c r="D454" t="n">
+        <v>-0.06463172845949068</v>
+      </c>
+      <c r="E454" t="n">
+        <v>0.004560023539661494</v>
+      </c>
+      <c r="F454" t="n">
+        <v>-0.0002947222031842872</v>
+      </c>
+      <c r="G454" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>0.0009189819755979767</v>
+      </c>
+      <c r="C455" t="n">
+        <v>0.3809358031367604</v>
+      </c>
+      <c r="D455" t="n">
+        <v>-0.3800168211611624</v>
+      </c>
+      <c r="E455" t="n">
+        <v>0.004254078063187842</v>
+      </c>
+      <c r="F455" t="n">
+        <v>-0.001616621222544078</v>
+      </c>
+      <c r="G455" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>-0.06161676177191211</v>
+      </c>
+      <c r="C456" t="n">
+        <v>-0.07096858227813567</v>
+      </c>
+      <c r="D456" t="n">
+        <v>0.009351820506223555</v>
+      </c>
+      <c r="E456" t="n">
+        <v>0.005218269290205272</v>
+      </c>
+      <c r="F456" t="n">
+        <v>4.88003177551383e-05</v>
+      </c>
+      <c r="G456" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>-0.03834332901925741</v>
+      </c>
+      <c r="C457" t="n">
+        <v>-0.1045242431611518</v>
+      </c>
+      <c r="D457" t="n">
+        <v>0.06618091414189443</v>
+      </c>
+      <c r="E457" t="n">
+        <v>-0.0001934282151929713</v>
+      </c>
+      <c r="F457" t="n">
+        <v>-1.280125610230592e-05</v>
+      </c>
+      <c r="G457" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>cambio_media_mensal</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>-2.217400142430803</v>
+      </c>
+      <c r="C458" t="n">
+        <v>0.3509907506064289</v>
+      </c>
+      <c r="D458" t="n">
+        <v>-2.568390893037232</v>
+      </c>
+      <c r="E458" t="n">
+        <v>0.0006137524047339995</v>
+      </c>
+      <c r="F458" t="n">
+        <v>-0.001576356086898506</v>
+      </c>
+      <c r="G458" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>fenabrave_automoveis</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>-5.275650780846597</v>
+      </c>
+      <c r="C459" t="n">
+        <v>-3.782252149888656</v>
+      </c>
+      <c r="D459" t="n">
+        <v>-1.493398630957941</v>
+      </c>
+      <c r="E459" t="n">
+        <v>-1.727211618353539e-05</v>
+      </c>
+      <c r="F459" t="n">
+        <v>2.579415466223824e-05</v>
+      </c>
+      <c r="G459" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>fenabrave_caminhoes</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>-1.828347386793894</v>
+      </c>
+      <c r="C460" t="n">
+        <v>-5.623383435403373</v>
+      </c>
+      <c r="D460" t="n">
+        <v>3.795036048609479</v>
+      </c>
+      <c r="E460" t="n">
+        <v>-0.0006709340071621301</v>
+      </c>
+      <c r="F460" t="n">
+        <v>-0.002546218743418294</v>
+      </c>
+      <c r="G460" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>fenabrave_comerciais_leves</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>-0.3424365805175689</v>
+      </c>
+      <c r="C461" t="n">
+        <v>-3.872116184227398</v>
+      </c>
+      <c r="D461" t="n">
+        <v>3.529679603709829</v>
+      </c>
+      <c r="E461" t="n">
+        <v>0.001275063122507101</v>
+      </c>
+      <c r="F461" t="n">
+        <v>0.004500564296955883</v>
+      </c>
+      <c r="G461" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>fenabrave_onibus</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>-4.153947786527201</v>
+      </c>
+      <c r="C462" t="n">
+        <v>-7.145081408168695</v>
+      </c>
+      <c r="D462" t="n">
+        <v>2.991133621641494</v>
+      </c>
+      <c r="E462" t="n">
+        <v>0.000260945361429045</v>
+      </c>
+      <c r="F462" t="n">
+        <v>0.0007805224439818079</v>
+      </c>
+      <c r="G462" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>fgv_nuci</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>-0.09999999999999433</v>
+      </c>
+      <c r="C463" t="n">
+        <v>0.02795729074314344</v>
+      </c>
+      <c r="D463" t="n">
+        <v>-0.1279572907431378</v>
+      </c>
+      <c r="E463" t="n">
+        <v>0.009658555260322686</v>
+      </c>
+      <c r="F463" t="n">
+        <v>-0.001235882563603773</v>
+      </c>
+      <c r="G463" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>icbr_agro</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>0.6843143401802365</v>
+      </c>
+      <c r="C464" t="n">
+        <v>1.38127289427832</v>
+      </c>
+      <c r="D464" t="n">
+        <v>-0.6969585540980838</v>
+      </c>
+      <c r="E464" t="n">
+        <v>-1.846100976274278e-05</v>
+      </c>
+      <c r="F464" t="n">
+        <v>1.286655867143182e-05</v>
+      </c>
+      <c r="G464" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>icbr_energia</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>-0.2598010997918342</v>
+      </c>
+      <c r="C465" t="n">
+        <v>-0.2107111875017323</v>
+      </c>
+      <c r="D465" t="n">
+        <v>-0.04908991229010192</v>
+      </c>
+      <c r="E465" t="n">
+        <v>-8.76367893213088e-06</v>
+      </c>
+      <c r="F465" t="n">
+        <v>4.302082301169189e-07</v>
+      </c>
+      <c r="G465" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>icbr_metal</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>2.221426097799162</v>
+      </c>
+      <c r="C466" t="n">
+        <v>1.193587598835665</v>
+      </c>
+      <c r="D466" t="n">
+        <v>1.027838498963497</v>
+      </c>
+      <c r="E466" t="n">
+        <v>-0.0001041327359100049</v>
+      </c>
+      <c r="F466" t="n">
+        <v>-0.0001070316349707017</v>
+      </c>
+      <c r="G466" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>0.02834541292932125</v>
+      </c>
+      <c r="C467" t="n">
+        <v>0.4916820676428346</v>
+      </c>
+      <c r="D467" t="n">
+        <v>-0.4633366547135133</v>
+      </c>
+      <c r="E467" t="n">
+        <v>-0.0006126388828142978</v>
+      </c>
+      <c r="F467" t="n">
+        <v>0.0002838580505106008</v>
+      </c>
+      <c r="G467" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>-0.6322592568392276</v>
+      </c>
+      <c r="C468" t="n">
+        <v>0.6079406250732379</v>
+      </c>
+      <c r="D468" t="n">
+        <v>-1.240199881912466</v>
+      </c>
+      <c r="E468" t="n">
+        <v>-4.460120793211344e-05</v>
+      </c>
+      <c r="F468" t="n">
+        <v>5.531441281056041e-05</v>
+      </c>
+      <c r="G468" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>-0.3700623027681141</v>
+      </c>
+      <c r="C469" t="n">
+        <v>0.3702835535659302</v>
+      </c>
+      <c r="D469" t="n">
+        <v>-0.7403458563340445</v>
+      </c>
+      <c r="E469" t="n">
+        <v>-0.006674606863463544</v>
+      </c>
+      <c r="F469" t="n">
+        <v>0.004941517534024008</v>
+      </c>
+      <c r="G469" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>0.4489387037604357</v>
+      </c>
+      <c r="C470" t="n">
+        <v>0.5167537371316928</v>
+      </c>
+      <c r="D470" t="n">
+        <v>-0.06781503337125712</v>
+      </c>
+      <c r="E470" t="n">
+        <v>-0.003927205711445847</v>
+      </c>
+      <c r="F470" t="n">
+        <v>0.0002663235863774917</v>
+      </c>
+      <c r="G470" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>-0.6966185442159022</v>
+      </c>
+      <c r="C471" t="n">
+        <v>0.4385729829713193</v>
+      </c>
+      <c r="D471" t="n">
+        <v>-1.135191527187221</v>
+      </c>
+      <c r="E471" t="n">
+        <v>-0.005084016732597463</v>
+      </c>
+      <c r="F471" t="n">
+        <v>0.005771332718922701</v>
+      </c>
+      <c r="G471" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>0.2427188518995873</v>
+      </c>
+      <c r="C472" t="n">
+        <v>0.3699023766025531</v>
+      </c>
+      <c r="D472" t="n">
+        <v>-0.1271835247029658</v>
+      </c>
+      <c r="E472" t="n">
+        <v>0.007685154611765345</v>
+      </c>
+      <c r="F472" t="n">
+        <v>-0.0009774250514115697</v>
+      </c>
+      <c r="G472" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>0.3109432966846084</v>
+      </c>
+      <c r="C473" t="n">
+        <v>0.4076822295217156</v>
+      </c>
+      <c r="D473" t="n">
+        <v>-0.09673893283710719</v>
+      </c>
+      <c r="E473" t="n">
+        <v>0.008686214372060247</v>
+      </c>
+      <c r="F473" t="n">
+        <v>-0.0008402951087474514</v>
+      </c>
+      <c r="G473" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>ipca_DP</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>0.30432517773155</v>
+      </c>
+      <c r="C474" t="n">
+        <v>0.3858014658344831</v>
+      </c>
+      <c r="D474" t="n">
+        <v>-0.08147628810293311</v>
+      </c>
+      <c r="E474" t="n">
+        <v>0.04327744456644091</v>
+      </c>
+      <c r="F474" t="n">
+        <v>-0.003526085541854056</v>
+      </c>
+      <c r="G474" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>ipca_EX0</t>
+        </is>
+      </c>
+      <c r="B475" t="n">
+        <v>0.3985075622549502</v>
+      </c>
+      <c r="C475" t="n">
+        <v>0.3835980777291803</v>
+      </c>
+      <c r="D475" t="n">
+        <v>0.01490948452576988</v>
+      </c>
+      <c r="E475" t="n">
+        <v>0.03137325988384927</v>
+      </c>
+      <c r="F475" t="n">
+        <v>0.0004677591327612077</v>
+      </c>
+      <c r="G475" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>ipca_EX3</t>
+        </is>
+      </c>
+      <c r="B476" t="n">
+        <v>0.358515394556541</v>
+      </c>
+      <c r="C476" t="n">
+        <v>0.3864420585282745</v>
+      </c>
+      <c r="D476" t="n">
+        <v>-0.02792666397173346</v>
+      </c>
+      <c r="E476" t="n">
+        <v>0.00391167221167347</v>
+      </c>
+      <c r="F476" t="n">
+        <v>-0.0001092399554229724</v>
+      </c>
+      <c r="G476" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>ipca_MS</t>
+        </is>
+      </c>
+      <c r="B477" t="n">
+        <v>0.3611275205637015</v>
+      </c>
+      <c r="C477" t="n">
+        <v>0.3643320005068958</v>
+      </c>
+      <c r="D477" t="n">
+        <v>-0.003204479943194276</v>
+      </c>
+      <c r="E477" t="n">
+        <v>-0.05954111292254497</v>
+      </c>
+      <c r="F477" t="n">
+        <v>0.0001907983021557609</v>
+      </c>
+      <c r="G477" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>ipca_P55</t>
+        </is>
+      </c>
+      <c r="B478" t="n">
+        <v>0.4254132256423441</v>
+      </c>
+      <c r="C478" t="n">
+        <v>0.3894035558668774</v>
+      </c>
+      <c r="D478" t="n">
+        <v>0.03600966977546664</v>
+      </c>
+      <c r="E478" t="n">
+        <v>0.03152352417743404</v>
+      </c>
+      <c r="F478" t="n">
+        <v>0.001135151695788338</v>
+      </c>
+      <c r="G478" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>ipca_administrados</t>
+        </is>
+      </c>
+      <c r="B479" t="n">
+        <v>0.07556839549407418</v>
+      </c>
+      <c r="C479" t="n">
+        <v>0.4171376312455007</v>
+      </c>
+      <c r="D479" t="n">
+        <v>-0.3415692357514265</v>
+      </c>
+      <c r="E479" t="n">
+        <v>0.001268053965583846</v>
+      </c>
+      <c r="F479" t="n">
+        <v>-0.0004331282239160401</v>
+      </c>
+      <c r="G479" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>ipca_alim_domicilio</t>
+        </is>
+      </c>
+      <c r="B480" t="n">
+        <v>0.1987814756189867</v>
+      </c>
+      <c r="C480" t="n">
+        <v>0.3453690577781109</v>
+      </c>
+      <c r="D480" t="n">
+        <v>-0.1465875821591241</v>
+      </c>
+      <c r="E480" t="n">
+        <v>0.001595541804528074</v>
+      </c>
+      <c r="F480" t="n">
+        <v>-0.0002338866153595762</v>
+      </c>
+      <c r="G480" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>ipca_alimentacao</t>
+        </is>
+      </c>
+      <c r="B481" t="n">
+        <v>0.2927774211888935</v>
+      </c>
+      <c r="C481" t="n">
+        <v>0.3660987057141073</v>
+      </c>
+      <c r="D481" t="n">
+        <v>-0.0733212845252138</v>
+      </c>
+      <c r="E481" t="n">
+        <v>0.001976208653844362</v>
+      </c>
+      <c r="F481" t="n">
+        <v>-0.0001448981569897122</v>
+      </c>
+      <c r="G481" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>ipca_difusao</t>
+        </is>
+      </c>
+      <c r="B482" t="n">
+        <v>0.6485572467709773</v>
+      </c>
+      <c r="C482" t="n">
+        <v>0.5183103543295193</v>
+      </c>
+      <c r="D482" t="n">
+        <v>0.1302468924414579</v>
+      </c>
+      <c r="E482" t="n">
+        <v>-5.639690335434299e-05</v>
+      </c>
+      <c r="F482" t="n">
+        <v>-7.345521405224406e-06</v>
+      </c>
+      <c r="G482" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>ipca_industriais</t>
+        </is>
+      </c>
+      <c r="B483" t="n">
+        <v>0.0693498936122684</v>
+      </c>
+      <c r="C483" t="n">
+        <v>0.2715817792233686</v>
+      </c>
+      <c r="D483" t="n">
+        <v>-0.2022318856111001</v>
+      </c>
+      <c r="E483" t="n">
+        <v>-0.009149938910802968</v>
+      </c>
+      <c r="F483" t="n">
+        <v>0.00185040939915806</v>
+      </c>
+      <c r="G483" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>ipca_industriais_subjacentes</t>
+        </is>
+      </c>
+      <c r="B484" t="n">
+        <v>0.2687025250315013</v>
+      </c>
+      <c r="C484" t="n">
+        <v>0.3433598483405994</v>
+      </c>
+      <c r="D484" t="n">
+        <v>-0.07465732330909811</v>
+      </c>
+      <c r="E484" t="n">
+        <v>-0.002457198351611605</v>
+      </c>
+      <c r="F484" t="n">
+        <v>0.0001834478517708505</v>
+      </c>
+      <c r="G484" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>ipca_livres</t>
+        </is>
+      </c>
+      <c r="B485" t="n">
+        <v>0.3010813186618921</v>
+      </c>
+      <c r="C485" t="n">
+        <v>0.3870590966599899</v>
+      </c>
+      <c r="D485" t="n">
+        <v>-0.08597777799809786</v>
+      </c>
+      <c r="E485" t="n">
+        <v>0.01638404925591416</v>
+      </c>
+      <c r="F485" t="n">
+        <v>-0.001408664149634888</v>
+      </c>
+      <c r="G485" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>ipca_servicos</t>
+        </is>
+      </c>
+      <c r="B486" t="n">
+        <v>0.402727181780807</v>
+      </c>
+      <c r="C486" t="n">
+        <v>0.4814796762555508</v>
+      </c>
+      <c r="D486" t="n">
+        <v>-0.07875249447474375</v>
+      </c>
+      <c r="E486" t="n">
+        <v>0.01246177268436663</v>
+      </c>
+      <c r="F486" t="n">
+        <v>-0.0009813956844710956</v>
+      </c>
+      <c r="G486" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>ipca_servicos_subjacentes</t>
+        </is>
+      </c>
+      <c r="B487" t="n">
+        <v>0.3602466052582748</v>
+      </c>
+      <c r="C487" t="n">
+        <v>0.423712742606678</v>
+      </c>
+      <c r="D487" t="n">
+        <v>-0.06346613734840324</v>
+      </c>
+      <c r="E487" t="n">
+        <v>0.006989429553843543</v>
+      </c>
+      <c r="F487" t="n">
+        <v>-0.0004435920960512231</v>
+      </c>
+      <c r="G487" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="B488" t="n">
+        <v>0.0009189819755979767</v>
+      </c>
+      <c r="C488" t="n">
+        <v>0.3810796700256629</v>
+      </c>
+      <c r="D488" t="n">
+        <v>-0.3801606880500649</v>
+      </c>
+      <c r="E488" t="n">
+        <v>0.004960943637533433</v>
+      </c>
+      <c r="F488" t="n">
+        <v>-0.001885955746622302</v>
+      </c>
+      <c r="G488" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>-0.06161676177191211</v>
+      </c>
+      <c r="C489" t="n">
+        <v>-0.07280703435368358</v>
+      </c>
+      <c r="D489" t="n">
+        <v>0.01119027258177146</v>
+      </c>
+      <c r="E489" t="n">
+        <v>0.008291013057031631</v>
+      </c>
+      <c r="F489" t="n">
+        <v>9.277869608721021e-05</v>
+      </c>
+      <c r="G489" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>-0.03834332901925741</v>
+      </c>
+      <c r="C490" t="n">
+        <v>-0.107456397052147</v>
+      </c>
+      <c r="D490" t="n">
+        <v>0.06911306803288957</v>
+      </c>
+      <c r="E490" t="n">
+        <v>0.002070800315614454</v>
+      </c>
+      <c r="F490" t="n">
+        <v>0.0001431193630955909</v>
+      </c>
+      <c r="G490" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>cambio_media_mensal</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>-2.217400142430803</v>
+      </c>
+      <c r="C491" t="n">
+        <v>0.3548539108443168</v>
+      </c>
+      <c r="D491" t="n">
+        <v>-2.57225405327512</v>
+      </c>
+      <c r="E491" t="n">
+        <v>0.000107346212555138</v>
+      </c>
+      <c r="F491" t="n">
+        <v>-0.0002761217303486864</v>
+      </c>
+      <c r="G491" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>fenabrave_automoveis</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>-5.275650780846597</v>
+      </c>
+      <c r="C492" t="n">
+        <v>-3.899734206735032</v>
+      </c>
+      <c r="D492" t="n">
+        <v>-1.375916574111565</v>
+      </c>
+      <c r="E492" t="n">
+        <v>0.0001067262255167591</v>
+      </c>
+      <c r="F492" t="n">
+        <v>-0.0001468463825808774</v>
+      </c>
+      <c r="G492" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>fenabrave_caminhoes</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>-1.828347386793894</v>
+      </c>
+      <c r="C493" t="n">
+        <v>-5.734334680489965</v>
+      </c>
+      <c r="D493" t="n">
+        <v>3.905987293696072</v>
+      </c>
+      <c r="E493" t="n">
+        <v>7.289465736284898e-05</v>
+      </c>
+      <c r="F493" t="n">
+        <v>0.0002847256054376169</v>
+      </c>
+      <c r="G493" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>fenabrave_comerciais_leves</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>-0.3424365805175689</v>
+      </c>
+      <c r="C494" t="n">
+        <v>-3.994720127246466</v>
+      </c>
+      <c r="D494" t="n">
+        <v>3.652283546728897</v>
+      </c>
+      <c r="E494" t="n">
+        <v>0.0001574334888863774</v>
+      </c>
+      <c r="F494" t="n">
+        <v>0.0005749917411638427</v>
+      </c>
+      <c r="G494" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>fenabrave_onibus</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>-4.153947786527201</v>
+      </c>
+      <c r="C495" t="n">
+        <v>-7.26216838969459</v>
+      </c>
+      <c r="D495" t="n">
+        <v>3.108220603167389</v>
+      </c>
+      <c r="E495" t="n">
+        <v>4.009522902566559e-05</v>
+      </c>
+      <c r="F495" t="n">
+        <v>0.0001246248169462889</v>
+      </c>
+      <c r="G495" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>fgv_nuci</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>-0.09999999999999433</v>
+      </c>
+      <c r="C496" t="n">
+        <v>0.02730971828724809</v>
+      </c>
+      <c r="D496" t="n">
+        <v>-0.1273097182872424</v>
+      </c>
+      <c r="E496" t="n">
+        <v>-5.153807380663923e-05</v>
+      </c>
+      <c r="F496" t="n">
+        <v>6.561297657390349e-06</v>
+      </c>
+      <c r="G496" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>icbr_agro</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>0.6843143401802365</v>
+      </c>
+      <c r="C497" t="n">
+        <v>1.378508916187712</v>
+      </c>
+      <c r="D497" t="n">
+        <v>-0.6941945760074758</v>
+      </c>
+      <c r="E497" t="n">
+        <v>-4.435565419841058e-06</v>
+      </c>
+      <c r="F497" t="n">
+        <v>3.079145455979985e-06</v>
+      </c>
+      <c r="G497" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>icbr_energia</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>-0.2598010997918342</v>
+      </c>
+      <c r="C498" t="n">
+        <v>-0.2145054181840919</v>
+      </c>
+      <c r="D498" t="n">
+        <v>-0.04529568160774242</v>
+      </c>
+      <c r="E498" t="n">
+        <v>-1.811517824521156e-06</v>
+      </c>
+      <c r="F498" t="n">
+        <v>8.205393460626048e-08</v>
+      </c>
+      <c r="G498" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>icbr_metal</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>2.221426097799162</v>
+      </c>
+      <c r="C499" t="n">
+        <v>1.188979059734962</v>
+      </c>
+      <c r="D499" t="n">
+        <v>1.032447038064199</v>
+      </c>
+      <c r="E499" t="n">
+        <v>-2.19101818622387e-05</v>
+      </c>
+      <c r="F499" t="n">
+        <v>-2.262110236711629e-05</v>
+      </c>
+      <c r="G499" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>0.02834541292932125</v>
+      </c>
+      <c r="C500" t="n">
+        <v>0.4905703005003593</v>
+      </c>
+      <c r="D500" t="n">
+        <v>-0.462224887571038</v>
+      </c>
+      <c r="E500" t="n">
+        <v>5.908259244463216e-05</v>
+      </c>
+      <c r="F500" t="n">
+        <v>-2.730944465012556e-05</v>
+      </c>
+      <c r="G500" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>-0.6322592568392276</v>
+      </c>
+      <c r="C501" t="n">
+        <v>0.6066284751378132</v>
+      </c>
+      <c r="D501" t="n">
+        <v>-1.238887731977041</v>
+      </c>
+      <c r="E501" t="n">
+        <v>-2.889587194446208e-05</v>
+      </c>
+      <c r="F501" t="n">
+        <v>3.579874125677363e-05</v>
+      </c>
+      <c r="G501" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>-0.3700623027681141</v>
+      </c>
+      <c r="C502" t="n">
+        <v>0.3689024484529884</v>
+      </c>
+      <c r="D502" t="n">
+        <v>-0.7389647512211025</v>
+      </c>
+      <c r="E502" t="n">
+        <v>-0.001718562353067339</v>
+      </c>
+      <c r="F502" t="n">
+        <v>0.001269957001692359</v>
+      </c>
+      <c r="G502" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>0.4489387037604357</v>
+      </c>
+      <c r="C503" t="n">
+        <v>0.5163007500084187</v>
+      </c>
+      <c r="D503" t="n">
+        <v>-0.06736204624798299</v>
+      </c>
+      <c r="E503" t="n">
+        <v>-0.0006873977837355014</v>
+      </c>
+      <c r="F503" t="n">
+        <v>4.630452129875186e-05</v>
+      </c>
+      <c r="G503" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>-0.6966185442159022</v>
+      </c>
+      <c r="C504" t="n">
+        <v>0.4366373890370208</v>
+      </c>
+      <c r="D504" t="n">
+        <v>-1.133255933252923</v>
+      </c>
+      <c r="E504" t="n">
+        <v>-0.0009414893442449707</v>
+      </c>
+      <c r="F504" t="n">
+        <v>0.001066948385460017</v>
+      </c>
+      <c r="G504" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>0.2427188518995873</v>
+      </c>
+      <c r="C505" t="n">
+        <v>0.369977689399113</v>
+      </c>
+      <c r="D505" t="n">
+        <v>-0.1272588374995257</v>
+      </c>
+      <c r="E505" t="n">
+        <v>0.001387312298470292</v>
+      </c>
+      <c r="F505" t="n">
+        <v>-0.0001765477503521244</v>
+      </c>
+      <c r="G505" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>0.3109432966846084</v>
+      </c>
+      <c r="C506" t="n">
+        <v>0.4078173748701227</v>
+      </c>
+      <c r="D506" t="n">
+        <v>-0.09687407818551436</v>
+      </c>
+      <c r="E506" t="n">
+        <v>0.001721863310512347</v>
+      </c>
+      <c r="F506" t="n">
+        <v>-0.0001668039209673417</v>
+      </c>
+      <c r="G506" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>ipca_DP</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>0.30432517773155</v>
+      </c>
+      <c r="C507" t="n">
+        <v>0.3859102137019673</v>
+      </c>
+      <c r="D507" t="n">
+        <v>-0.08158503597041733</v>
+      </c>
+      <c r="E507" t="n">
+        <v>0.00732251632932066</v>
+      </c>
+      <c r="F507" t="n">
+        <v>-0.0005974077581215943</v>
+      </c>
+      <c r="G507" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>ipca_EX0</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>0.3985075622549502</v>
+      </c>
+      <c r="C508" t="n">
+        <v>0.3838677594788177</v>
+      </c>
+      <c r="D508" t="n">
+        <v>0.01463980277613248</v>
+      </c>
+      <c r="E508" t="n">
+        <v>0.007168682542039668</v>
+      </c>
+      <c r="F508" t="n">
+        <v>0.0001049480985801648</v>
+      </c>
+      <c r="G508" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>ipca_EX3</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>0.358515394556541</v>
+      </c>
+      <c r="C509" t="n">
+        <v>0.3866263725629114</v>
+      </c>
+      <c r="D509" t="n">
+        <v>-0.02811097800637036</v>
+      </c>
+      <c r="E509" t="n">
+        <v>0.0009287725750404522</v>
+      </c>
+      <c r="F509" t="n">
+        <v>-2.610870542988212e-05</v>
+      </c>
+      <c r="G509" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>ipca_MS</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>0.3611275205637015</v>
+      </c>
+      <c r="C510" t="n">
+        <v>0.3644410985691636</v>
+      </c>
+      <c r="D510" t="n">
+        <v>-0.003313578005462117</v>
+      </c>
+      <c r="E510" t="n">
+        <v>-0.01893149077075029</v>
+      </c>
+      <c r="F510" t="n">
+        <v>6.27309714285672e-05</v>
+      </c>
+      <c r="G510" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>ipca_P55</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>0.4254132256423441</v>
+      </c>
+      <c r="C511" t="n">
+        <v>0.3895794434639496</v>
+      </c>
+      <c r="D511" t="n">
+        <v>0.03583378217839444</v>
+      </c>
+      <c r="E511" t="n">
+        <v>0.006910783112874351</v>
+      </c>
+      <c r="F511" t="n">
+        <v>0.0002476394967488662</v>
+      </c>
+      <c r="G511" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>ipca_administrados</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>0.07556839549407418</v>
+      </c>
+      <c r="C512" t="n">
+        <v>0.4172323196248096</v>
+      </c>
+      <c r="D512" t="n">
+        <v>-0.3416639241307354</v>
+      </c>
+      <c r="E512" t="n">
+        <v>0.0002280679210638613</v>
+      </c>
+      <c r="F512" t="n">
+        <v>-7.792258087901765e-05</v>
+      </c>
+      <c r="G512" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>ipca_alim_domicilio</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>0.1987814756189867</v>
+      </c>
+      <c r="C513" t="n">
+        <v>0.3447469817056115</v>
+      </c>
+      <c r="D513" t="n">
+        <v>-0.1459655060866247</v>
+      </c>
+      <c r="E513" t="n">
+        <v>0.0002477235054735611</v>
+      </c>
+      <c r="F513" t="n">
+        <v>-3.61590868460011e-05</v>
+      </c>
+      <c r="G513" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>ipca_alimentacao</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>0.2927774211888935</v>
+      </c>
+      <c r="C514" t="n">
+        <v>0.365669404184212</v>
+      </c>
+      <c r="D514" t="n">
+        <v>-0.07289198299531854</v>
+      </c>
+      <c r="E514" t="n">
+        <v>0.0002823093180705668</v>
+      </c>
+      <c r="F514" t="n">
+        <v>-2.057808601221973e-05</v>
+      </c>
+      <c r="G514" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>ipca_difusao</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>0.6485572467709773</v>
+      </c>
+      <c r="C515" t="n">
+        <v>0.5172629511451068</v>
+      </c>
+      <c r="D515" t="n">
+        <v>0.1312942956258705</v>
+      </c>
+      <c r="E515" t="n">
+        <v>-3.797427809936424e-06</v>
+      </c>
+      <c r="F515" t="n">
+        <v>-4.985806094956947e-07</v>
+      </c>
+      <c r="G515" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>ipca_industriais</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>0.0693498936122684</v>
+      </c>
+      <c r="C516" t="n">
+        <v>0.2713999016909931</v>
+      </c>
+      <c r="D516" t="n">
+        <v>-0.2020500080787247</v>
+      </c>
+      <c r="E516" t="n">
+        <v>-0.001697446934779905</v>
+      </c>
+      <c r="F516" t="n">
+        <v>0.0003429691668854862</v>
+      </c>
+      <c r="G516" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>ipca_industriais_subjacentes</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>0.2687025250315013</v>
+      </c>
+      <c r="C517" t="n">
+        <v>0.3432392531618335</v>
+      </c>
+      <c r="D517" t="n">
+        <v>-0.07453672813033226</v>
+      </c>
+      <c r="E517" t="n">
+        <v>-0.0004051805932383902</v>
+      </c>
+      <c r="F517" t="n">
+        <v>3.020083572189663e-05</v>
+      </c>
+      <c r="G517" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>ipca_livres</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>0.3010813186618921</v>
+      </c>
+      <c r="C518" t="n">
+        <v>0.3871783996646891</v>
+      </c>
+      <c r="D518" t="n">
+        <v>-0.08609708100279702</v>
+      </c>
+      <c r="E518" t="n">
+        <v>0.002719999892071349</v>
+      </c>
+      <c r="F518" t="n">
+        <v>-0.0002341840510352661</v>
+      </c>
+      <c r="G518" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>ipca_servicos</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>0.402727181780807</v>
+      </c>
+      <c r="C519" t="n">
+        <v>0.4820626947120183</v>
+      </c>
+      <c r="D519" t="n">
+        <v>-0.07933551293121127</v>
+      </c>
+      <c r="E519" t="n">
+        <v>0.002584537544626224</v>
+      </c>
+      <c r="F519" t="n">
+        <v>-0.0002050456117928949</v>
+      </c>
+      <c r="G519" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>ipca_servicos_subjacentes</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>0.3602466052582748</v>
+      </c>
+      <c r="C520" t="n">
+        <v>0.4239897348641923</v>
+      </c>
+      <c r="D520" t="n">
+        <v>-0.06374312960591756</v>
+      </c>
+      <c r="E520" t="n">
+        <v>0.001140079184028395</v>
+      </c>
+      <c r="F520" t="n">
+        <v>-7.26722151885307e-05</v>
+      </c>
+      <c r="G520" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>0.0009189819755979767</v>
+      </c>
+      <c r="C521" t="n">
+        <v>0.3811351285464974</v>
+      </c>
+      <c r="D521" t="n">
+        <v>-0.3802161465708995</v>
+      </c>
+      <c r="E521" t="n">
+        <v>0.001055338005871198</v>
+      </c>
+      <c r="F521" t="n">
+        <v>-0.0004012565499221641</v>
+      </c>
+      <c r="G521" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>-0.06161676177191211</v>
+      </c>
+      <c r="C522" t="n">
+        <v>-0.0723755592138388</v>
+      </c>
+      <c r="D522" t="n">
+        <v>0.01075879744192668</v>
+      </c>
+      <c r="E522" t="n">
+        <v>0.001427135619577426</v>
+      </c>
+      <c r="F522" t="n">
+        <v>1.535426305319206e-05</v>
+      </c>
+      <c r="G522" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>-0.03834332901925741</v>
+      </c>
+      <c r="C523" t="n">
+        <v>-0.1073944829588649</v>
+      </c>
+      <c r="D523" t="n">
+        <v>0.06905115393960747</v>
+      </c>
+      <c r="E523" t="n">
+        <v>-4.485888088930877e-05</v>
+      </c>
+      <c r="F523" t="n">
+        <v>-3.097557489846175e-06</v>
+      </c>
+      <c r="G523" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>cambio_media_mensal</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>-2.217400142430803</v>
+      </c>
+      <c r="C524" t="n">
+        <v>0.3548539108443168</v>
+      </c>
+      <c r="D524" t="n">
+        <v>-2.57225405327512</v>
+      </c>
+      <c r="E524" t="n">
+        <v>0.000107346212555138</v>
+      </c>
+      <c r="F524" t="n">
+        <v>-0.0002761217303486864</v>
+      </c>
+      <c r="G524" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>fenabrave_automoveis</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>-5.275650780846597</v>
+      </c>
+      <c r="C525" t="n">
+        <v>-3.899734206735032</v>
+      </c>
+      <c r="D525" t="n">
+        <v>-1.375916574111565</v>
+      </c>
+      <c r="E525" t="n">
+        <v>0.0001067262255167591</v>
+      </c>
+      <c r="F525" t="n">
+        <v>-0.0001468463825808774</v>
+      </c>
+      <c r="G525" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>fenabrave_caminhoes</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>-1.828347386793894</v>
+      </c>
+      <c r="C526" t="n">
+        <v>-5.734334680489965</v>
+      </c>
+      <c r="D526" t="n">
+        <v>3.905987293696072</v>
+      </c>
+      <c r="E526" t="n">
+        <v>7.289465736284898e-05</v>
+      </c>
+      <c r="F526" t="n">
+        <v>0.0002847256054376169</v>
+      </c>
+      <c r="G526" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>fenabrave_comerciais_leves</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>-0.3424365805175689</v>
+      </c>
+      <c r="C527" t="n">
+        <v>-3.994720127246466</v>
+      </c>
+      <c r="D527" t="n">
+        <v>3.652283546728897</v>
+      </c>
+      <c r="E527" t="n">
+        <v>0.0001574334888863774</v>
+      </c>
+      <c r="F527" t="n">
+        <v>0.0005749917411638427</v>
+      </c>
+      <c r="G527" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>fenabrave_onibus</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>-4.153947786527201</v>
+      </c>
+      <c r="C528" t="n">
+        <v>-7.26216838969459</v>
+      </c>
+      <c r="D528" t="n">
+        <v>3.108220603167389</v>
+      </c>
+      <c r="E528" t="n">
+        <v>4.009522902566559e-05</v>
+      </c>
+      <c r="F528" t="n">
+        <v>0.0001246248169462889</v>
+      </c>
+      <c r="G528" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>fgv_nuci</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>-0.09999999999999433</v>
+      </c>
+      <c r="C529" t="n">
+        <v>0.02730971828724809</v>
+      </c>
+      <c r="D529" t="n">
+        <v>-0.1273097182872424</v>
+      </c>
+      <c r="E529" t="n">
+        <v>-5.153807380663923e-05</v>
+      </c>
+      <c r="F529" t="n">
+        <v>6.561297657390349e-06</v>
+      </c>
+      <c r="G529" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>icbr_agro</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>0.6843143401802365</v>
+      </c>
+      <c r="C530" t="n">
+        <v>1.378508916187712</v>
+      </c>
+      <c r="D530" t="n">
+        <v>-0.6941945760074758</v>
+      </c>
+      <c r="E530" t="n">
+        <v>-4.435565419841058e-06</v>
+      </c>
+      <c r="F530" t="n">
+        <v>3.079145455979985e-06</v>
+      </c>
+      <c r="G530" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>icbr_energia</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>-0.2598010997918342</v>
+      </c>
+      <c r="C531" t="n">
+        <v>-0.2145054181840919</v>
+      </c>
+      <c r="D531" t="n">
+        <v>-0.04529568160774242</v>
+      </c>
+      <c r="E531" t="n">
+        <v>-1.811517824521156e-06</v>
+      </c>
+      <c r="F531" t="n">
+        <v>8.205393460626048e-08</v>
+      </c>
+      <c r="G531" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>icbr_metal</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>2.221426097799162</v>
+      </c>
+      <c r="C532" t="n">
+        <v>1.188979059734962</v>
+      </c>
+      <c r="D532" t="n">
+        <v>1.032447038064199</v>
+      </c>
+      <c r="E532" t="n">
+        <v>-2.19101818622387e-05</v>
+      </c>
+      <c r="F532" t="n">
+        <v>-2.262110236711629e-05</v>
+      </c>
+      <c r="G532" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>0.02834541292932125</v>
+      </c>
+      <c r="C533" t="n">
+        <v>0.4905703005003593</v>
+      </c>
+      <c r="D533" t="n">
+        <v>-0.462224887571038</v>
+      </c>
+      <c r="E533" t="n">
+        <v>5.908259244463216e-05</v>
+      </c>
+      <c r="F533" t="n">
+        <v>-2.730944465012556e-05</v>
+      </c>
+      <c r="G533" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>-0.6322592568392276</v>
+      </c>
+      <c r="C534" t="n">
+        <v>0.6066284751378132</v>
+      </c>
+      <c r="D534" t="n">
+        <v>-1.238887731977041</v>
+      </c>
+      <c r="E534" t="n">
+        <v>-2.889587194446208e-05</v>
+      </c>
+      <c r="F534" t="n">
+        <v>3.579874125677363e-05</v>
+      </c>
+      <c r="G534" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>-0.3700623027681141</v>
+      </c>
+      <c r="C535" t="n">
+        <v>0.3689024484529884</v>
+      </c>
+      <c r="D535" t="n">
+        <v>-0.7389647512211025</v>
+      </c>
+      <c r="E535" t="n">
+        <v>-0.001718562353067339</v>
+      </c>
+      <c r="F535" t="n">
+        <v>0.001269957001692359</v>
+      </c>
+      <c r="G535" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>0.4489387037604357</v>
+      </c>
+      <c r="C536" t="n">
+        <v>0.5163007500084187</v>
+      </c>
+      <c r="D536" t="n">
+        <v>-0.06736204624798299</v>
+      </c>
+      <c r="E536" t="n">
+        <v>-0.0006873977837355014</v>
+      </c>
+      <c r="F536" t="n">
+        <v>4.630452129875186e-05</v>
+      </c>
+      <c r="G536" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>-0.6966185442159022</v>
+      </c>
+      <c r="C537" t="n">
+        <v>0.4366373890370208</v>
+      </c>
+      <c r="D537" t="n">
+        <v>-1.133255933252923</v>
+      </c>
+      <c r="E537" t="n">
+        <v>-0.0009414893442449707</v>
+      </c>
+      <c r="F537" t="n">
+        <v>0.001066948385460017</v>
+      </c>
+      <c r="G537" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>0.2427188518995873</v>
+      </c>
+      <c r="C538" t="n">
+        <v>0.369977689399113</v>
+      </c>
+      <c r="D538" t="n">
+        <v>-0.1272588374995257</v>
+      </c>
+      <c r="E538" t="n">
+        <v>0.001387312298470292</v>
+      </c>
+      <c r="F538" t="n">
+        <v>-0.0001765477503521244</v>
+      </c>
+      <c r="G538" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>0.3109432966846084</v>
+      </c>
+      <c r="C539" t="n">
+        <v>0.4078173748701227</v>
+      </c>
+      <c r="D539" t="n">
+        <v>-0.09687407818551436</v>
+      </c>
+      <c r="E539" t="n">
+        <v>0.001721863310512347</v>
+      </c>
+      <c r="F539" t="n">
+        <v>-0.0001668039209673417</v>
+      </c>
+      <c r="G539" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>ipca_DP</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>0.30432517773155</v>
+      </c>
+      <c r="C540" t="n">
+        <v>0.3859102137019673</v>
+      </c>
+      <c r="D540" t="n">
+        <v>-0.08158503597041733</v>
+      </c>
+      <c r="E540" t="n">
+        <v>0.00732251632932066</v>
+      </c>
+      <c r="F540" t="n">
+        <v>-0.0005974077581215943</v>
+      </c>
+      <c r="G540" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>ipca_EX0</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>0.3985075622549502</v>
+      </c>
+      <c r="C541" t="n">
+        <v>0.3838677594788177</v>
+      </c>
+      <c r="D541" t="n">
+        <v>0.01463980277613248</v>
+      </c>
+      <c r="E541" t="n">
+        <v>0.007168682542039668</v>
+      </c>
+      <c r="F541" t="n">
+        <v>0.0001049480985801648</v>
+      </c>
+      <c r="G541" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>ipca_EX3</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>0.358515394556541</v>
+      </c>
+      <c r="C542" t="n">
+        <v>0.3866263725629114</v>
+      </c>
+      <c r="D542" t="n">
+        <v>-0.02811097800637036</v>
+      </c>
+      <c r="E542" t="n">
+        <v>0.0009287725750404522</v>
+      </c>
+      <c r="F542" t="n">
+        <v>-2.610870542988212e-05</v>
+      </c>
+      <c r="G542" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>ipca_MS</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>0.3611275205637015</v>
+      </c>
+      <c r="C543" t="n">
+        <v>0.3644410985691636</v>
+      </c>
+      <c r="D543" t="n">
+        <v>-0.003313578005462117</v>
+      </c>
+      <c r="E543" t="n">
+        <v>-0.01893149077075029</v>
+      </c>
+      <c r="F543" t="n">
+        <v>6.27309714285672e-05</v>
+      </c>
+      <c r="G543" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>ipca_P55</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>0.4254132256423441</v>
+      </c>
+      <c r="C544" t="n">
+        <v>0.3895794434639496</v>
+      </c>
+      <c r="D544" t="n">
+        <v>0.03583378217839444</v>
+      </c>
+      <c r="E544" t="n">
+        <v>0.006910783112874351</v>
+      </c>
+      <c r="F544" t="n">
+        <v>0.0002476394967488662</v>
+      </c>
+      <c r="G544" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>ipca_administrados</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>0.07556839549407418</v>
+      </c>
+      <c r="C545" t="n">
+        <v>0.4172323196248096</v>
+      </c>
+      <c r="D545" t="n">
+        <v>-0.3416639241307354</v>
+      </c>
+      <c r="E545" t="n">
+        <v>0.0002280679210638613</v>
+      </c>
+      <c r="F545" t="n">
+        <v>-7.792258087901765e-05</v>
+      </c>
+      <c r="G545" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>ipca_alim_domicilio</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>0.1987814756189867</v>
+      </c>
+      <c r="C546" t="n">
+        <v>0.3447469817056115</v>
+      </c>
+      <c r="D546" t="n">
+        <v>-0.1459655060866247</v>
+      </c>
+      <c r="E546" t="n">
+        <v>0.0002477235054735611</v>
+      </c>
+      <c r="F546" t="n">
+        <v>-3.61590868460011e-05</v>
+      </c>
+      <c r="G546" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>ipca_alimentacao</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>0.2927774211888935</v>
+      </c>
+      <c r="C547" t="n">
+        <v>0.365669404184212</v>
+      </c>
+      <c r="D547" t="n">
+        <v>-0.07289198299531854</v>
+      </c>
+      <c r="E547" t="n">
+        <v>0.0002823093180705668</v>
+      </c>
+      <c r="F547" t="n">
+        <v>-2.057808601221973e-05</v>
+      </c>
+      <c r="G547" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>ipca_difusao</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>0.6485572467709773</v>
+      </c>
+      <c r="C548" t="n">
+        <v>0.5172629511451068</v>
+      </c>
+      <c r="D548" t="n">
+        <v>0.1312942956258705</v>
+      </c>
+      <c r="E548" t="n">
+        <v>-3.797427809936424e-06</v>
+      </c>
+      <c r="F548" t="n">
+        <v>-4.985806094956947e-07</v>
+      </c>
+      <c r="G548" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>ipca_industriais</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>0.0693498936122684</v>
+      </c>
+      <c r="C549" t="n">
+        <v>0.2713999016909931</v>
+      </c>
+      <c r="D549" t="n">
+        <v>-0.2020500080787247</v>
+      </c>
+      <c r="E549" t="n">
+        <v>-0.001697446934779905</v>
+      </c>
+      <c r="F549" t="n">
+        <v>0.0003429691668854862</v>
+      </c>
+      <c r="G549" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>ipca_industriais_subjacentes</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>0.2687025250315013</v>
+      </c>
+      <c r="C550" t="n">
+        <v>0.3432392531618335</v>
+      </c>
+      <c r="D550" t="n">
+        <v>-0.07453672813033226</v>
+      </c>
+      <c r="E550" t="n">
+        <v>-0.0004051805932383902</v>
+      </c>
+      <c r="F550" t="n">
+        <v>3.020083572189663e-05</v>
+      </c>
+      <c r="G550" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>ipca_livres</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>0.3010813186618921</v>
+      </c>
+      <c r="C551" t="n">
+        <v>0.3871783996646891</v>
+      </c>
+      <c r="D551" t="n">
+        <v>-0.08609708100279702</v>
+      </c>
+      <c r="E551" t="n">
+        <v>0.002719999892071349</v>
+      </c>
+      <c r="F551" t="n">
+        <v>-0.0002341840510352661</v>
+      </c>
+      <c r="G551" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>ipca_servicos</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>0.402727181780807</v>
+      </c>
+      <c r="C552" t="n">
+        <v>0.4820626947120183</v>
+      </c>
+      <c r="D552" t="n">
+        <v>-0.07933551293121127</v>
+      </c>
+      <c r="E552" t="n">
+        <v>0.002584537544626224</v>
+      </c>
+      <c r="F552" t="n">
+        <v>-0.0002050456117928949</v>
+      </c>
+      <c r="G552" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>ipca_servicos_subjacentes</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>0.3602466052582748</v>
+      </c>
+      <c r="C553" t="n">
+        <v>0.4239897348641923</v>
+      </c>
+      <c r="D553" t="n">
+        <v>-0.06374312960591756</v>
+      </c>
+      <c r="E553" t="n">
+        <v>0.001140079184028395</v>
+      </c>
+      <c r="F553" t="n">
+        <v>-7.26722151885307e-05</v>
+      </c>
+      <c r="G553" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>0.0009189819755979767</v>
+      </c>
+      <c r="C554" t="n">
+        <v>0.3811351285464974</v>
+      </c>
+      <c r="D554" t="n">
+        <v>-0.3802161465708995</v>
+      </c>
+      <c r="E554" t="n">
+        <v>0.001055338005871198</v>
+      </c>
+      <c r="F554" t="n">
+        <v>-0.0004012565499221641</v>
+      </c>
+      <c r="G554" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>-0.06161676177191211</v>
+      </c>
+      <c r="C555" t="n">
+        <v>-0.0723755592138388</v>
+      </c>
+      <c r="D555" t="n">
+        <v>0.01075879744192668</v>
+      </c>
+      <c r="E555" t="n">
+        <v>0.001427135619577426</v>
+      </c>
+      <c r="F555" t="n">
+        <v>1.535426305319206e-05</v>
+      </c>
+      <c r="G555" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>-0.03834332901925741</v>
+      </c>
+      <c r="C556" t="n">
+        <v>-0.1073944829588649</v>
+      </c>
+      <c r="D556" t="n">
+        <v>0.06905115393960747</v>
+      </c>
+      <c r="E556" t="n">
+        <v>-4.485888088930877e-05</v>
+      </c>
+      <c r="F556" t="n">
+        <v>-3.097557489846175e-06</v>
+      </c>
+      <c r="G556" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="C557" t="n">
+        <v>-0.8992672180581573</v>
+      </c>
+      <c r="D557" t="n">
+        <v>-0.6407327819418426</v>
+      </c>
+      <c r="E557" t="n">
+        <v>-1.09330019330995e-08</v>
+      </c>
+      <c r="F557" t="n">
+        <v>7.005132743570389e-09</v>
+      </c>
+      <c r="G557" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>cambio_media_mensal</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>-12.14242014687221</v>
+      </c>
+      <c r="C558" t="n">
+        <v>-10.261923073731</v>
+      </c>
+      <c r="D558" t="n">
+        <v>-1.880497073141209</v>
+      </c>
+      <c r="E558" t="n">
+        <v>-0.0001565550606387973</v>
+      </c>
+      <c r="F558" t="n">
+        <v>0.0002944013333167028</v>
+      </c>
+      <c r="G558" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>fenabrave_automoveis</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>15.71257642366568</v>
+      </c>
+      <c r="C559" t="n">
+        <v>11.86720576191355</v>
+      </c>
+      <c r="D559" t="n">
+        <v>3.845370661752129</v>
+      </c>
+      <c r="E559" t="n">
+        <v>0.0003302574417176828</v>
+      </c>
+      <c r="F559" t="n">
+        <v>0.001269962277206491</v>
+      </c>
+      <c r="G559" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>fenabrave_caminhoes</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>6.878866482910517</v>
+      </c>
+      <c r="C560" t="n">
+        <v>9.049616580904919</v>
+      </c>
+      <c r="D560" t="n">
+        <v>-2.170750097994403</v>
+      </c>
+      <c r="E560" t="n">
+        <v>0.000412676181467752</v>
+      </c>
+      <c r="F560" t="n">
+        <v>-0.0008958168613610785</v>
+      </c>
+      <c r="G560" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>fenabrave_comerciais_leves</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>9.436541455345804</v>
+      </c>
+      <c r="C561" t="n">
+        <v>6.296218939313958</v>
+      </c>
+      <c r="D561" t="n">
+        <v>3.140322516031845</v>
+      </c>
+      <c r="E561" t="n">
+        <v>0.0003094480630020412</v>
+      </c>
+      <c r="F561" t="n">
+        <v>0.000971766719787751</v>
+      </c>
+      <c r="G561" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>fenabrave_onibus</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>-2.314152856169382</v>
+      </c>
+      <c r="C562" t="n">
+        <v>4.711289358671463</v>
+      </c>
+      <c r="D562" t="n">
+        <v>-7.025442214840845</v>
+      </c>
+      <c r="E562" t="n">
+        <v>0.0002030253776006668</v>
+      </c>
+      <c r="F562" t="n">
+        <v>-0.001426343058479727</v>
+      </c>
+      <c r="G562" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>fgv_nuci</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>0.7000000000000028</v>
+      </c>
+      <c r="C563" t="n">
+        <v>-0.3977263898994078</v>
+      </c>
+      <c r="D563" t="n">
+        <v>1.097726389899411</v>
+      </c>
+      <c r="E563" t="n">
+        <v>0.003918836367308126</v>
+      </c>
+      <c r="F563" t="n">
+        <v>0.00430181009809167</v>
+      </c>
+      <c r="G563" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>icbr_agro</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>-5.851692715816004</v>
+      </c>
+      <c r="C564" t="n">
+        <v>-4.228638740400678</v>
+      </c>
+      <c r="D564" t="n">
+        <v>-1.623053975415326</v>
+      </c>
+      <c r="E564" t="n">
+        <v>-0.0001418047469334703</v>
+      </c>
+      <c r="F564" t="n">
+        <v>0.0002301567582431332</v>
+      </c>
+      <c r="G564" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>icbr_energia</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>1.370397764392717</v>
+      </c>
+      <c r="C565" t="n">
+        <v>4.74810754130444</v>
+      </c>
+      <c r="D565" t="n">
+        <v>-3.377709776911725</v>
+      </c>
+      <c r="E565" t="n">
+        <v>-8.207949178379749e-05</v>
+      </c>
+      <c r="F565" t="n">
+        <v>0.0002772407018820784</v>
+      </c>
+      <c r="G565" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>icbr_metal</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>27.04099090050098</v>
+      </c>
+      <c r="C566" t="n">
+        <v>34.00327044454658</v>
+      </c>
+      <c r="D566" t="n">
+        <v>-6.962279544045595</v>
+      </c>
+      <c r="E566" t="n">
+        <v>-0.0001589773052768916</v>
+      </c>
+      <c r="F566" t="n">
+        <v>0.001106844440496794</v>
+      </c>
+      <c r="G566" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="C567" t="n">
+        <v>0.4390388388881623</v>
+      </c>
+      <c r="D567" t="n">
+        <v>0.0809611611118377</v>
+      </c>
+      <c r="E567" t="n">
+        <v>0.001136265291202215</v>
+      </c>
+      <c r="F567" t="n">
+        <v>9.199335730681171e-05</v>
+      </c>
+      <c r="G567" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>igpdi</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="C568" t="n">
+        <v>0.663152231079871</v>
+      </c>
+      <c r="D568" t="n">
+        <v>-1.453152231079871</v>
+      </c>
+      <c r="E568" t="n">
+        <v>0.0009849386812098607</v>
+      </c>
+      <c r="F568" t="n">
+        <v>-0.001431265842076975</v>
+      </c>
+      <c r="G568" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>igpm</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>-0.3899999999999999</v>
+      </c>
+      <c r="C569" t="n">
+        <v>0.8105230517130673</v>
+      </c>
+      <c r="D569" t="n">
+        <v>-1.200523051713067</v>
+      </c>
+      <c r="E569" t="n">
+        <v>0.000937375191666111</v>
+      </c>
+      <c r="F569" t="n">
+        <v>-0.001125340525699121</v>
+      </c>
+      <c r="G569" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>incc</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C570" t="n">
+        <v>0.007779430060259399</v>
+      </c>
+      <c r="D570" t="n">
+        <v>-0.3077794300602594</v>
+      </c>
+      <c r="E570" t="n">
+        <v>0.007817485162408915</v>
+      </c>
+      <c r="F570" t="n">
+        <v>-0.00240606112779075</v>
+      </c>
+      <c r="G570" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>ipam</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="C571" t="n">
+        <v>1.083658569166971</v>
+      </c>
+      <c r="D571" t="n">
+        <v>-1.533658569166971</v>
+      </c>
+      <c r="E571" t="n">
+        <v>0.0006080655729038819</v>
+      </c>
+      <c r="F571" t="n">
+        <v>-0.0009325649764994621</v>
+      </c>
+      <c r="G571" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>ipc_fipe</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>-0.3100000000000001</v>
+      </c>
+      <c r="C572" t="n">
+        <v>0.09654227292340524</v>
+      </c>
+      <c r="D572" t="n">
+        <v>-0.4065422729234052</v>
+      </c>
+      <c r="E572" t="n">
+        <v>-0.0007364854478242351</v>
+      </c>
+      <c r="F572" t="n">
+        <v>0.0002994124679334765</v>
+      </c>
+      <c r="G572" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="C573" t="n">
+        <v>0.05555924787612677</v>
+      </c>
+      <c r="D573" t="n">
+        <v>-0.3255592478761268</v>
+      </c>
+      <c r="E573" t="n">
+        <v>0.002168408287061361</v>
+      </c>
+      <c r="F573" t="n">
+        <v>-0.0007059453710240569</v>
+      </c>
+      <c r="G573" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>ipca_DP</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>-0.07999999999999999</v>
+      </c>
+      <c r="C574" t="n">
+        <v>-0.01507349267096359</v>
+      </c>
+      <c r="D574" t="n">
+        <v>-0.0649265073290364</v>
+      </c>
+      <c r="E574" t="n">
+        <v>-0.009565226368492743</v>
+      </c>
+      <c r="F574" t="n">
+        <v>0.0006210367399178364</v>
+      </c>
+      <c r="G574" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>ipca_EX0</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="C575" t="n">
+        <v>-7.233877726692912e-05</v>
+      </c>
+      <c r="D575" t="n">
+        <v>-0.03992766122273311</v>
+      </c>
+      <c r="E575" t="n">
+        <v>0.009219182886119346</v>
+      </c>
+      <c r="F575" t="n">
+        <v>-0.0003681004110273921</v>
+      </c>
+      <c r="G575" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>ipca_EX3</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="C576" t="n">
+        <v>-0.005600816950454715</v>
+      </c>
+      <c r="D576" t="n">
+        <v>-0.05439918304954527</v>
+      </c>
+      <c r="E576" t="n">
+        <v>0.007997123254086577</v>
+      </c>
+      <c r="F576" t="n">
+        <v>-0.0004350369717688309</v>
+      </c>
+      <c r="G576" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>ipca_MS</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>0.01999999999999997</v>
+      </c>
+      <c r="C577" t="n">
+        <v>-0.08645447824483339</v>
+      </c>
+      <c r="D577" t="n">
+        <v>0.1064544782448334</v>
+      </c>
+      <c r="E577" t="n">
+        <v>-0.012664702774998</v>
+      </c>
+      <c r="F577" t="n">
+        <v>-0.001348214326038305</v>
+      </c>
+      <c r="G577" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>ipca_P55</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C578" t="n">
+        <v>0.003612337486139287</v>
+      </c>
+      <c r="D578" t="n">
+        <v>0.09638766251386073</v>
+      </c>
+      <c r="E578" t="n">
+        <v>0.001202134307213687</v>
+      </c>
+      <c r="F578" t="n">
+        <v>0.0001158709159000466</v>
+      </c>
+      <c r="G578" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>ipca_administrados</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="C579" t="n">
+        <v>-0.06928815219137245</v>
+      </c>
+      <c r="D579" t="n">
+        <v>-0.3307118478086276</v>
+      </c>
+      <c r="E579" t="n">
+        <v>-9.61922871668501e-05</v>
+      </c>
+      <c r="F579" t="n">
+        <v>3.181192903388714e-05</v>
+      </c>
+      <c r="G579" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>ipca_alim_domicilio</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>-0.4499999999999999</v>
+      </c>
+      <c r="C580" t="n">
+        <v>0.1007175563442706</v>
+      </c>
+      <c r="D580" t="n">
+        <v>-0.5507175563442706</v>
+      </c>
+      <c r="E580" t="n">
+        <v>-0.0008114984852941657</v>
+      </c>
+      <c r="F580" t="n">
+        <v>0.0004469064627982799</v>
+      </c>
+      <c r="G580" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>ipca_alimentacao</t>
+        </is>
+      </c>
+      <c r="B581" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="C581" t="n">
+        <v>0.01762962619977062</v>
+      </c>
+      <c r="D581" t="n">
+        <v>-0.4176296261997707</v>
+      </c>
+      <c r="E581" t="n">
+        <v>-0.0008987680140478031</v>
+      </c>
+      <c r="F581" t="n">
+        <v>0.0003753521497470942</v>
+      </c>
+      <c r="G581" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>ipca_difusao</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>0</v>
+      </c>
+      <c r="C582" t="n">
+        <v>0.3243198416414368</v>
+      </c>
+      <c r="D582" t="n">
+        <v>-0.3243198416414368</v>
+      </c>
+      <c r="E582" t="n">
+        <v>-3.508815351789286e-05</v>
+      </c>
+      <c r="F582" t="n">
+        <v>1.137978439241344e-05</v>
+      </c>
+      <c r="G582" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>ipca_industriais</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>-0.06000000000000001</v>
+      </c>
+      <c r="C583" t="n">
+        <v>0.02106976516501349</v>
+      </c>
+      <c r="D583" t="n">
+        <v>-0.08106976516501349</v>
+      </c>
+      <c r="E583" t="n">
+        <v>0.005152659223780539</v>
+      </c>
+      <c r="F583" t="n">
+        <v>-0.000417724873247229</v>
+      </c>
+      <c r="G583" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>ipca_industriais_subjacentes</t>
+        </is>
+      </c>
+      <c r="B584" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="C584" t="n">
+        <v>0.03854592620941479</v>
+      </c>
+      <c r="D584" t="n">
+        <v>-0.1085459262094148</v>
+      </c>
+      <c r="E584" t="n">
+        <v>0.001347879268277503</v>
+      </c>
+      <c r="F584" t="n">
+        <v>-0.0001463068035936498</v>
+      </c>
+      <c r="G584" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>ipca_livres</t>
+        </is>
+      </c>
+      <c r="B585" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="C585" t="n">
+        <v>0.02266797775848263</v>
+      </c>
+      <c r="D585" t="n">
+        <v>-0.1526679777584826</v>
+      </c>
+      <c r="E585" t="n">
+        <v>-0.001823189586878419</v>
+      </c>
+      <c r="F585" t="n">
+        <v>0.0002783426672990516</v>
+      </c>
+      <c r="G585" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>ipca_servicos</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>-0.04999999999999993</v>
+      </c>
+      <c r="C586" t="n">
+        <v>0.008942045983792703</v>
+      </c>
+      <c r="D586" t="n">
+        <v>-0.05894204598379264</v>
+      </c>
+      <c r="E586" t="n">
+        <v>0.001811334757536778</v>
+      </c>
+      <c r="F586" t="n">
+        <v>-0.0001067637765707747</v>
+      </c>
+      <c r="G586" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>ipca_servicos_subjacentes</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="C587" t="n">
+        <v>-0.02433142069495069</v>
+      </c>
+      <c r="D587" t="n">
+        <v>-0.04566857930504931</v>
+      </c>
+      <c r="E587" t="n">
+        <v>0.01286263166347963</v>
+      </c>
+      <c r="F587" t="n">
+        <v>-0.0005874181141952579</v>
+      </c>
+      <c r="G587" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>ipcbr</t>
+        </is>
+      </c>
+      <c r="B588" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="C588" t="n">
+        <v>0.04097610690021136</v>
+      </c>
+      <c r="D588" t="n">
+        <v>-0.4909761069002114</v>
+      </c>
+      <c r="E588" t="n">
+        <v>-0.0001536085759985914</v>
+      </c>
+      <c r="F588" t="n">
+        <v>7.541814063027368e-05</v>
+      </c>
+      <c r="G588" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B589" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="C589" t="n">
+        <v>-0.5242235488846929</v>
+      </c>
+      <c r="D589" t="n">
+        <v>-0.2257764511153071</v>
+      </c>
+      <c r="E589" t="n">
+        <v>0.0002800168696210296</v>
+      </c>
+      <c r="F589" t="n">
+        <v>-6.322121507545371e-05</v>
+      </c>
+      <c r="G589" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B590" t="n">
+        <v>-0.9100000000000001</v>
+      </c>
+      <c r="C590" t="n">
+        <v>-0.6137814957772277</v>
+      </c>
+      <c r="D590" t="n">
+        <v>-0.2962185042227725</v>
+      </c>
+      <c r="E590" t="n">
+        <v>0.001574033729203653</v>
+      </c>
+      <c r="F590" t="n">
+        <v>-0.0004662579168608985</v>
+      </c>
+      <c r="G590" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H590" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>

--- a/pib_nowcast/data/impacts.xlsx
+++ b/pib_nowcast/data/impacts.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H590"/>
+  <dimension ref="A1:H615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17136,7 +17136,7 @@
       <c r="F557" t="n">
         <v>7.005132743570389e-09</v>
       </c>
-      <c r="G557" s="2" t="n">
+      <c r="G557" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H557" t="inlineStr">
@@ -17166,7 +17166,7 @@
       <c r="F558" t="n">
         <v>0.0002944013333167028</v>
       </c>
-      <c r="G558" s="2" t="n">
+      <c r="G558" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H558" t="inlineStr">
@@ -17196,7 +17196,7 @@
       <c r="F559" t="n">
         <v>0.001269962277206491</v>
       </c>
-      <c r="G559" s="2" t="n">
+      <c r="G559" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H559" t="inlineStr">
@@ -17226,7 +17226,7 @@
       <c r="F560" t="n">
         <v>-0.0008958168613610785</v>
       </c>
-      <c r="G560" s="2" t="n">
+      <c r="G560" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H560" t="inlineStr">
@@ -17256,7 +17256,7 @@
       <c r="F561" t="n">
         <v>0.000971766719787751</v>
       </c>
-      <c r="G561" s="2" t="n">
+      <c r="G561" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H561" t="inlineStr">
@@ -17286,7 +17286,7 @@
       <c r="F562" t="n">
         <v>-0.001426343058479727</v>
       </c>
-      <c r="G562" s="2" t="n">
+      <c r="G562" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H562" t="inlineStr">
@@ -17316,7 +17316,7 @@
       <c r="F563" t="n">
         <v>0.00430181009809167</v>
       </c>
-      <c r="G563" s="2" t="n">
+      <c r="G563" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H563" t="inlineStr">
@@ -17346,7 +17346,7 @@
       <c r="F564" t="n">
         <v>0.0002301567582431332</v>
       </c>
-      <c r="G564" s="2" t="n">
+      <c r="G564" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H564" t="inlineStr">
@@ -17376,7 +17376,7 @@
       <c r="F565" t="n">
         <v>0.0002772407018820784</v>
       </c>
-      <c r="G565" s="2" t="n">
+      <c r="G565" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H565" t="inlineStr">
@@ -17406,7 +17406,7 @@
       <c r="F566" t="n">
         <v>0.001106844440496794</v>
       </c>
-      <c r="G566" s="2" t="n">
+      <c r="G566" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H566" t="inlineStr">
@@ -17436,7 +17436,7 @@
       <c r="F567" t="n">
         <v>9.199335730681171e-05</v>
       </c>
-      <c r="G567" s="2" t="n">
+      <c r="G567" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H567" t="inlineStr">
@@ -17466,7 +17466,7 @@
       <c r="F568" t="n">
         <v>-0.001431265842076975</v>
       </c>
-      <c r="G568" s="2" t="n">
+      <c r="G568" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H568" t="inlineStr">
@@ -17496,7 +17496,7 @@
       <c r="F569" t="n">
         <v>-0.001125340525699121</v>
       </c>
-      <c r="G569" s="2" t="n">
+      <c r="G569" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H569" t="inlineStr">
@@ -17526,7 +17526,7 @@
       <c r="F570" t="n">
         <v>-0.00240606112779075</v>
       </c>
-      <c r="G570" s="2" t="n">
+      <c r="G570" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H570" t="inlineStr">
@@ -17556,7 +17556,7 @@
       <c r="F571" t="n">
         <v>-0.0009325649764994621</v>
       </c>
-      <c r="G571" s="2" t="n">
+      <c r="G571" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H571" t="inlineStr">
@@ -17586,7 +17586,7 @@
       <c r="F572" t="n">
         <v>0.0002994124679334765</v>
       </c>
-      <c r="G572" s="2" t="n">
+      <c r="G572" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H572" t="inlineStr">
@@ -17616,7 +17616,7 @@
       <c r="F573" t="n">
         <v>-0.0007059453710240569</v>
       </c>
-      <c r="G573" s="2" t="n">
+      <c r="G573" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H573" t="inlineStr">
@@ -17646,7 +17646,7 @@
       <c r="F574" t="n">
         <v>0.0006210367399178364</v>
       </c>
-      <c r="G574" s="2" t="n">
+      <c r="G574" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H574" t="inlineStr">
@@ -17676,7 +17676,7 @@
       <c r="F575" t="n">
         <v>-0.0003681004110273921</v>
       </c>
-      <c r="G575" s="2" t="n">
+      <c r="G575" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H575" t="inlineStr">
@@ -17706,7 +17706,7 @@
       <c r="F576" t="n">
         <v>-0.0004350369717688309</v>
       </c>
-      <c r="G576" s="2" t="n">
+      <c r="G576" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H576" t="inlineStr">
@@ -17736,7 +17736,7 @@
       <c r="F577" t="n">
         <v>-0.001348214326038305</v>
       </c>
-      <c r="G577" s="2" t="n">
+      <c r="G577" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H577" t="inlineStr">
@@ -17766,7 +17766,7 @@
       <c r="F578" t="n">
         <v>0.0001158709159000466</v>
       </c>
-      <c r="G578" s="2" t="n">
+      <c r="G578" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H578" t="inlineStr">
@@ -17796,7 +17796,7 @@
       <c r="F579" t="n">
         <v>3.181192903388714e-05</v>
       </c>
-      <c r="G579" s="2" t="n">
+      <c r="G579" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H579" t="inlineStr">
@@ -17826,7 +17826,7 @@
       <c r="F580" t="n">
         <v>0.0004469064627982799</v>
       </c>
-      <c r="G580" s="2" t="n">
+      <c r="G580" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H580" t="inlineStr">
@@ -17856,7 +17856,7 @@
       <c r="F581" t="n">
         <v>0.0003753521497470942</v>
       </c>
-      <c r="G581" s="2" t="n">
+      <c r="G581" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H581" t="inlineStr">
@@ -17886,7 +17886,7 @@
       <c r="F582" t="n">
         <v>1.137978439241344e-05</v>
       </c>
-      <c r="G582" s="2" t="n">
+      <c r="G582" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H582" t="inlineStr">
@@ -17916,7 +17916,7 @@
       <c r="F583" t="n">
         <v>-0.000417724873247229</v>
       </c>
-      <c r="G583" s="2" t="n">
+      <c r="G583" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H583" t="inlineStr">
@@ -17946,7 +17946,7 @@
       <c r="F584" t="n">
         <v>-0.0001463068035936498</v>
       </c>
-      <c r="G584" s="2" t="n">
+      <c r="G584" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H584" t="inlineStr">
@@ -17976,7 +17976,7 @@
       <c r="F585" t="n">
         <v>0.0002783426672990516</v>
       </c>
-      <c r="G585" s="2" t="n">
+      <c r="G585" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H585" t="inlineStr">
@@ -18006,7 +18006,7 @@
       <c r="F586" t="n">
         <v>-0.0001067637765707747</v>
       </c>
-      <c r="G586" s="2" t="n">
+      <c r="G586" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H586" t="inlineStr">
@@ -18036,7 +18036,7 @@
       <c r="F587" t="n">
         <v>-0.0005874181141952579</v>
       </c>
-      <c r="G587" s="2" t="n">
+      <c r="G587" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H587" t="inlineStr">
@@ -18066,7 +18066,7 @@
       <c r="F588" t="n">
         <v>7.541814063027368e-05</v>
       </c>
-      <c r="G588" s="2" t="n">
+      <c r="G588" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H588" t="inlineStr">
@@ -18096,7 +18096,7 @@
       <c r="F589" t="n">
         <v>-6.322121507545371e-05</v>
       </c>
-      <c r="G589" s="2" t="n">
+      <c r="G589" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H589" t="inlineStr">
@@ -18126,10 +18126,760 @@
       <c r="F590" t="n">
         <v>-0.0004662579168608985</v>
       </c>
-      <c r="G590" s="2" t="n">
+      <c r="G590" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="H590" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B591" t="n">
+        <v>-0.9100000000000001</v>
+      </c>
+      <c r="C591" t="n">
+        <v>-1.52813937968081e+52</v>
+      </c>
+      <c r="D591" t="n">
+        <v>1.52813937968081e+52</v>
+      </c>
+      <c r="E591" t="n">
+        <v>2.92323474999082</v>
+      </c>
+      <c r="F591" t="n">
+        <v>4.46711013751236e+52</v>
+      </c>
+      <c r="G591" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B592" t="n">
+        <v>-0.9100000000000001</v>
+      </c>
+      <c r="C592" t="n">
+        <v>-1.52813937968081e+52</v>
+      </c>
+      <c r="D592" t="n">
+        <v>1.52813937968081e+52</v>
+      </c>
+      <c r="E592" t="n">
+        <v>2.92323474999082</v>
+      </c>
+      <c r="F592" t="n">
+        <v>4.46711013751236e+52</v>
+      </c>
+      <c r="G592" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B593" t="n">
+        <v>-0.9100000000000001</v>
+      </c>
+      <c r="C593" t="n">
+        <v>-0.7773796198237494</v>
+      </c>
+      <c r="D593" t="n">
+        <v>-0.1326203801762508</v>
+      </c>
+      <c r="E593" t="n">
+        <v>0.001385330037573559</v>
+      </c>
+      <c r="F593" t="n">
+        <v>-0.0001837229962525853</v>
+      </c>
+      <c r="G593" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>ibcbr_agro</t>
+        </is>
+      </c>
+      <c r="B594" t="n">
+        <v>5.646084772351934</v>
+      </c>
+      <c r="C594" t="n">
+        <v>2.326723919333911</v>
+      </c>
+      <c r="D594" t="n">
+        <v>3.319360853018023</v>
+      </c>
+      <c r="E594" t="n">
+        <v>-0.0003065613841200869</v>
+      </c>
+      <c r="F594" t="n">
+        <v>-0.001017587857495238</v>
+      </c>
+      <c r="G594" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>ibcbr_ind</t>
+        </is>
+      </c>
+      <c r="B595" t="n">
+        <v>0.4547219832392813</v>
+      </c>
+      <c r="C595" t="n">
+        <v>0.2635775054855475</v>
+      </c>
+      <c r="D595" t="n">
+        <v>0.1911444777537337</v>
+      </c>
+      <c r="E595" t="n">
+        <v>0.005421855894785088</v>
+      </c>
+      <c r="F595" t="n">
+        <v>0.001036357813464698</v>
+      </c>
+      <c r="G595" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>ibcbr_servicos</t>
+        </is>
+      </c>
+      <c r="B596" t="n">
+        <v>1.103086600768766</v>
+      </c>
+      <c r="C596" t="n">
+        <v>1.858611279898135</v>
+      </c>
+      <c r="D596" t="n">
+        <v>-0.7555246791293697</v>
+      </c>
+      <c r="E596" t="n">
+        <v>0.00992098744151702</v>
+      </c>
+      <c r="F596" t="n">
+        <v>-0.007495550853398653</v>
+      </c>
+      <c r="G596" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>pmc_automoveis</t>
+        </is>
+      </c>
+      <c r="B597" t="n">
+        <v>5.981111022566488</v>
+      </c>
+      <c r="C597" t="n">
+        <v>3.266614685506439</v>
+      </c>
+      <c r="D597" t="n">
+        <v>2.714496337060048</v>
+      </c>
+      <c r="E597" t="n">
+        <v>0.0006210670283945659</v>
+      </c>
+      <c r="F597" t="n">
+        <v>0.001685884173645818</v>
+      </c>
+      <c r="G597" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>pmc_combustiveis</t>
+        </is>
+      </c>
+      <c r="B598" t="n">
+        <v>0.9696926955239604</v>
+      </c>
+      <c r="C598" t="n">
+        <v>3.048211119959545</v>
+      </c>
+      <c r="D598" t="n">
+        <v>-2.078518424435584</v>
+      </c>
+      <c r="E598" t="n">
+        <v>0.0008162765249893189</v>
+      </c>
+      <c r="F598" t="n">
+        <v>-0.001696645796624553</v>
+      </c>
+      <c r="G598" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>pmc_comercio_ampliado</t>
+        </is>
+      </c>
+      <c r="B599" t="n">
+        <v>3.107083066648642</v>
+      </c>
+      <c r="C599" t="n">
+        <v>1.191663941962305</v>
+      </c>
+      <c r="D599" t="n">
+        <v>1.915419124686336</v>
+      </c>
+      <c r="E599" t="n">
+        <v>0.002571741237339406</v>
+      </c>
+      <c r="F599" t="n">
+        <v>0.0049259623497444</v>
+      </c>
+      <c r="G599" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>pmc_eqp_material_escritorio</t>
+        </is>
+      </c>
+      <c r="B600" t="n">
+        <v>-0.1718377511143565</v>
+      </c>
+      <c r="C600" t="n">
+        <v>1.3211639613224</v>
+      </c>
+      <c r="D600" t="n">
+        <v>-1.493001712436756</v>
+      </c>
+      <c r="E600" t="n">
+        <v>0.0004262532745532592</v>
+      </c>
+      <c r="F600" t="n">
+        <v>-0.0006363968688397908</v>
+      </c>
+      <c r="G600" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>pmc_farmaceuticos</t>
+        </is>
+      </c>
+      <c r="B601" t="n">
+        <v>4.57519469778056</v>
+      </c>
+      <c r="C601" t="n">
+        <v>5.125830958176772</v>
+      </c>
+      <c r="D601" t="n">
+        <v>-0.5506362603962127</v>
+      </c>
+      <c r="E601" t="n">
+        <v>0.002537195578368547</v>
+      </c>
+      <c r="F601" t="n">
+        <v>-0.001397071885166663</v>
+      </c>
+      <c r="G601" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>pmc_hiper_supermercados</t>
+        </is>
+      </c>
+      <c r="B602" t="n">
+        <v>2.332362633446561</v>
+      </c>
+      <c r="C602" t="n">
+        <v>0.5702815266808736</v>
+      </c>
+      <c r="D602" t="n">
+        <v>1.762081106765687</v>
+      </c>
+      <c r="E602" t="n">
+        <v>0.00060759703185287</v>
+      </c>
+      <c r="F602" t="n">
+        <v>0.001070635250354852</v>
+      </c>
+      <c r="G602" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>pmc_livros_jornais</t>
+        </is>
+      </c>
+      <c r="B603" t="n">
+        <v>9.075066934388776</v>
+      </c>
+      <c r="C603" t="n">
+        <v>9.634015343043359</v>
+      </c>
+      <c r="D603" t="n">
+        <v>-0.5589484086545823</v>
+      </c>
+      <c r="E603" t="n">
+        <v>0.0006555622485873431</v>
+      </c>
+      <c r="F603" t="n">
+        <v>-0.0003664254756219151</v>
+      </c>
+      <c r="G603" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>pmc_material_construcao</t>
+        </is>
+      </c>
+      <c r="B604" t="n">
+        <v>-2.240409523988518</v>
+      </c>
+      <c r="C604" t="n">
+        <v>0.3388080285288453</v>
+      </c>
+      <c r="D604" t="n">
+        <v>-2.579217552517363</v>
+      </c>
+      <c r="E604" t="n">
+        <v>0.0001542315124754905</v>
+      </c>
+      <c r="F604" t="n">
+        <v>-0.0003977966241280857</v>
+      </c>
+      <c r="G604" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>pmc_moveis_eletrodomesticos</t>
+        </is>
+      </c>
+      <c r="B605" t="n">
+        <v>5.050410937395089</v>
+      </c>
+      <c r="C605" t="n">
+        <v>1.95468371691842</v>
+      </c>
+      <c r="D605" t="n">
+        <v>3.095727220476669</v>
+      </c>
+      <c r="E605" t="n">
+        <v>9.326253035672935e-05</v>
+      </c>
+      <c r="F605" t="n">
+        <v>0.0002887153538758587</v>
+      </c>
+      <c r="G605" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>pmc_outros_pessoal</t>
+        </is>
+      </c>
+      <c r="B606" t="n">
+        <v>2.614195555334398</v>
+      </c>
+      <c r="C606" t="n">
+        <v>0.01362226851589377</v>
+      </c>
+      <c r="D606" t="n">
+        <v>2.600573286818504</v>
+      </c>
+      <c r="E606" t="n">
+        <v>0.0007407534272077227</v>
+      </c>
+      <c r="F606" t="n">
+        <v>0.001926383574915659</v>
+      </c>
+      <c r="G606" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>pmc_vestuário</t>
+        </is>
+      </c>
+      <c r="B607" t="n">
+        <v>-1.82599099412224</v>
+      </c>
+      <c r="C607" t="n">
+        <v>1.043059596499246</v>
+      </c>
+      <c r="D607" t="n">
+        <v>-2.869050590621486</v>
+      </c>
+      <c r="E607" t="n">
+        <v>0.001223130504338933</v>
+      </c>
+      <c r="F607" t="n">
+        <v>-0.003509223295880773</v>
+      </c>
+      <c r="G607" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>pms_outros</t>
+        </is>
+      </c>
+      <c r="B608" t="n">
+        <v>-1.237942078758536</v>
+      </c>
+      <c r="C608" t="n">
+        <v>-1.157169896470377</v>
+      </c>
+      <c r="D608" t="n">
+        <v>-0.08077218228815924</v>
+      </c>
+      <c r="E608" t="n">
+        <v>0.0004798569786887756</v>
+      </c>
+      <c r="F608" t="n">
+        <v>-3.875909535489513e-05</v>
+      </c>
+      <c r="G608" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>pms_servicos_familias</t>
+        </is>
+      </c>
+      <c r="B609" t="n">
+        <v>2.917898510900141</v>
+      </c>
+      <c r="C609" t="n">
+        <v>4.700251450527617</v>
+      </c>
+      <c r="D609" t="n">
+        <v>-1.782352939627475</v>
+      </c>
+      <c r="E609" t="n">
+        <v>0.002151094901650017</v>
+      </c>
+      <c r="F609" t="n">
+        <v>-0.003834010321373583</v>
+      </c>
+      <c r="G609" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>pms_servicos_profissionais</t>
+        </is>
+      </c>
+      <c r="B610" t="n">
+        <v>3.854320832639235</v>
+      </c>
+      <c r="C610" t="n">
+        <v>2.818000104621338</v>
+      </c>
+      <c r="D610" t="n">
+        <v>1.036320728017898</v>
+      </c>
+      <c r="E610" t="n">
+        <v>0.002450543573671595</v>
+      </c>
+      <c r="F610" t="n">
+        <v>0.002539549100306928</v>
+      </c>
+      <c r="G610" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>pms_tic</t>
+        </is>
+      </c>
+      <c r="B611" t="n">
+        <v>6.760986960349501</v>
+      </c>
+      <c r="C611" t="n">
+        <v>1.531496432174335</v>
+      </c>
+      <c r="D611" t="n">
+        <v>5.229490528175166</v>
+      </c>
+      <c r="E611" t="n">
+        <v>0.003230582010421203</v>
+      </c>
+      <c r="F611" t="n">
+        <v>0.01689429802399076</v>
+      </c>
+      <c r="G611" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>pms_transportes</t>
+        </is>
+      </c>
+      <c r="B612" t="n">
+        <v>3.133620215815913</v>
+      </c>
+      <c r="C612" t="n">
+        <v>1.081515205168492</v>
+      </c>
+      <c r="D612" t="n">
+        <v>2.052105010647422</v>
+      </c>
+      <c r="E612" t="n">
+        <v>0.001377085366122866</v>
+      </c>
+      <c r="F612" t="n">
+        <v>0.002825923779909972</v>
+      </c>
+      <c r="G612" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>igp10</t>
+        </is>
+      </c>
+      <c r="B613" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="C613" t="n">
+        <v>0.3032996016160411</v>
+      </c>
+      <c r="D613" t="n">
+        <v>-0.9732996016160411</v>
+      </c>
+      <c r="E613" t="n">
+        <v>0.0006263974910757035</v>
+      </c>
+      <c r="F613" t="n">
+        <v>-0.00060967242851727</v>
+      </c>
+      <c r="G613" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>ipca15</t>
+        </is>
+      </c>
+      <c r="B614" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="C614" t="n">
+        <v>-0.08774248538783777</v>
+      </c>
+      <c r="D614" t="n">
+        <v>-0.1722575146121623</v>
+      </c>
+      <c r="E614" t="n">
+        <v>0.000775977139270922</v>
+      </c>
+      <c r="F614" t="n">
+        <v>-0.0001336678934066647</v>
+      </c>
+      <c r="G614" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>selic_mensal</t>
+        </is>
+      </c>
+      <c r="B615" t="n">
+        <v>-0.9600000000000009</v>
+      </c>
+      <c r="C615" t="n">
+        <v>-0.7773274374272773</v>
+      </c>
+      <c r="D615" t="n">
+        <v>-0.1826725625727236</v>
+      </c>
+      <c r="E615" t="n">
+        <v>0.001526037755814687</v>
+      </c>
+      <c r="F615" t="n">
+        <v>-0.0002787652274373971</v>
+      </c>
+      <c r="G615" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H615" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
